--- a/Data/Piura/noticias_piura_20261019_20261026.xlsx
+++ b/Data/Piura/noticias_piura_20261019_20261026.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -470,10 +470,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>¡Paro total en Sunafil Piura! Inspectores entran a huelga indefinida y revelan preocupante realidad en la región</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Los inspectores de trabajo de la Superintendencia Nacional de Fiscalización Laboral ( Sunafil ) iniciaron una huelga nacional indefinida en todas las regiones del país. La medida de fuerza busca la restitución de sus facultades inspectivas en el sector mype, la actualización de su escala salarial tras 14 años de congelamiento y la mejora de sus condiciones laborales básicas. Puedes Leer | Piura: Producción de mango caería hasta 90% en San Lorenzo En la base regional de Piura , el acatamiento fue del 100 % por parte de los 26 inspectores de trabajo adscritos a los dos sindicatos de la entidad. Durante el desarrollo de la protesta, solo se han mantenido piquetes de retén para la atención exclusiva de emergencias laborales. Sin facultades para fiscalizar la informalidad en las microempresas Uno de los puntos más críticos expuestos por los manifestantes es la pérdida de competencias legales para intervenir en las microempresas, lugar donde se concentra la mayor tasa de informalidad del país. Mario Ramírez Risco , inspector de trabajo y vocero de la base de Sunafil en Piura, explicó que desde julio de 2026 venció la norma que les otorgaba dichas facultades, dejándolos atados de manos frente a las denuncias de los ciudadanos. «Desde julio del 2026, la Superintendencia Nacional de Fiscalización Laboral no puede fiscalizar microempresas y eso es una afectación muy grave para todos los trabajadores de este sector, considerando que la principal informalidad se centra en esos sectores [...] El trabajador de microempresa viene acá, presenta su denuncia, pero no la podemos atender» , advirtió Ramírez Risco. Exigen escala salarial y denuncian falta de uniformes e insumos La plataforma de lucha demanda al Ministerio de Trabajo y Promoción del Empleo, liderado por el ministro Juan Fut , y a la superintendente de Sunafil, Evely Coloma , la implementación de la Ley N° 32486 , la cual aprueba la actualización de la escala remunerativa de la institución, paralizada desde su fundación hace 14 años. «Existe una ley, pero por desidia del gobierno no se está implementando esa ley. Nosotros como principales verificadores del cumplimiento de las leyes, estamos exigiendo ello» , señaló el dirigente regional. A ello se suma el incumplimiento de convenios colectivos, la falta de evaluaciones médicas, la ausencia de Equipos de Protección Personal (EPP) y la falta de entrega de uniformes institucionales desde hace cinco años. «Desde hace 5 años no se nos entregan uniformes de trabajo. Es algo básico, fundamental. Nosotros fiscalizamos eso, que se cumpla en las empresas, pero a nosotros no nos están cumpliendo», enfatizó Ramírez. Déficit de personal e inspectores retirados La dirigencia expuso además el severo déficit operativo que atraviesa la región Piura. Actualmente solo laboran 26 inspectores , cuando se requieren entre 40 y 45 profesionales como mínimo para cubrir la Población Económicamente Activa (PEA) y realizar labores de prevención. Mira También | Piura: padre de familia queda gravemente herido tras caer del segundo piso de su vivienda Dentro de los reclamos también se exige la reincorporación de 40 inspectores retirados a nivel nacional (dos de ellos correspondientes a Piura), así como el respeto integral a los derechos laborales del personal contratado bajo el régimen CAS. Finalmente, los manifestantes indicaron que la huelga continuará de manera firme hasta que el Ejecutivo otorgue respuestas definitivas. «En este momento en Lima nuestra dirigencia central está entablando los diálogos que corresponden (...) no vamos a levantar la huelga hasta no tener soluciones concretas» , puntualizó el vocero de la base Piura.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/paro-total-en-sunafil-piura-inspectores-entran-a-huelga-indefinida-y-revelan-preocupante-realidad-en-la-region/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Resultados ONPE en región Piura al 99.563 %: revisa aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación región Piura según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/resultados-en-piura-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>El Niño: Indecopi orienta a pasajeros de transporte terrestre sobre principales derechos</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Destacó la importancia de verificar el estado de las vías y contratar empresas autorizadas.
 Durante la jornada, se difundió la Guía para consumidores en situaciones de emergencia , una herramienta informativa que reúne los derechos de los pasajeros y recomendaciones para tomar decisiones de consumo informadas.
@@ -485,96 +535,330 @@
 Más en Andina: Casi 4 de cada 10 trabajadores en Perú sienten que 2026 ha sido mejor de lo esperado ?? https://t.co/Oz5He2LYPH https://t.co/m9AwfjaFti (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 25, 2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-nino-indecopi-orienta-a-pasajeros-transporte-terrestre-sobre-principales-derechos-1097319.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Piura: instalan sistema de bombeo en Las Azucenas para acelerar la evacuación de aguas pluviales</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>La Municipalidad Provincial de Piura (MPP) puso en funcionamiento un sistema provisional de bombeo en la cuenca ciega de Las Azucenas, con el objetivo de reducir la acumulación de aguas pluviales durante las lluvias. Esta zona recibe el agua que proviene de los sectores de Avifap e Ignacio Merino, lo que incrementa el riesgo de aniegos cuando se registran precipitaciones intensas. Anteriormente, el agua acumulada podía alcanzar hasta la cintura de una persona y su retiro requería aproximadamente 120 cisternadas, un procedimiento que demandaba varias horas. Con la nueva instalación, la comuna busca agilizar los trabajos de evacuación y disminuir las afectaciones a los vecinos. Dos motobombas permitirán evacuar el agua El sistema está compuesto por un buzón de captación y dos motobombas proporcionadas por el Ministerio de Vivienda, Construcción y Saneamiento. Ambos equipos tienen una capacidad conjunta de evacuación de 200 litros por segundo y permitirán conducir las aguas hacia el SARE Ignacio Merino. El gerente de Desarrollo Territorial, Pedro Ruiz, explicó que también se entregó un manual para garantizar el manejo adecuado de los equipos. Además, se colocaron tuberías de PVC en distintos cruces de vías para facilitar el desplazamiento del agua hacia los puntos de captación. El funcionario precisó que se trata de una solución provisional que permitirá reducir los efectos de las inundaciones. Para el funcionamiento del sistema, se mantendrá una lámina de agua de entre 15 y 20 centímetros que facilite el bombeo. Asimismo, señaló que la operatividad del SARE Ignacio Merino será fundamental para completar la evacuación. Municipalidad pide evitar arrojar basura en las calles Ruiz exhortó a los vecinos a no arrojar residuos en la vía pública, debido a que la basura puede acumularse en las rejillas de captación, bloquear el paso del agua y afectar el funcionamiento de las motobombas. Por su parte, los residentes de Las Azucenas agradecieron la intervención municipal y destacaron las acciones impulsadas por el alcalde Juan Francisco Cevallos para atender los problemas que enfrenta el sector durante la temporada de lluvias.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-instalan-sistema-de-bombeo-en-las-azucenas-para-acelerar-la-evacuacion-de-aguas-pluviales/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>En la medida dispuesta por el Poder Ejecutivo, vía el decreto supremo Nº 020-2026-TR , se declara días no laborables, sujetos a compensación, por la visita del Sumo Pontífice de la Iglesia Católica.
-[Lea también: Chiclayo espera con fe y gran expectativa la visita del papa León XIV ] La medida alcanza a los trabajadores del sector público y privado , de acuerdo con las fechas establecidas para cada ámbito geográfico.
-En el caso de Lambayeque el Gobierno declaró el viernes 13 y sábado 14 de noviembre de 2026 como días no laborables compensables para los trabajadores públicos y privados, debido a las actividades previstas por la visita del papa León XIV a Chiclayo y a la provincia cajamarquina de Santa Cruz.
-La medida se aplica también para las regiones de Cajamarca, La Libertad y Piura , para favorecer la movilización de los devotos y turistas.
-Lea también: Chiclayo quiere convertir visita del Papa en una experiencia religiosa y turística única Al alcanzar estos días no laborables tanto al sector público como al privado, se busca facilitar la participación de los ciudadanos en las actividades vinculadas con la visita del sumo pontífice , prevista del 11 al 16 de noviembre de este año.
-¿Qué días no se trabajará en estas regiones? Viernes 13 de noviembre: Día no laborable compensable para trabajadores de los sectores público y privado de Lambayeque, Cajamarca, La Libertad y Piura.
-Sábado 14 de noviembre: Segundo día no laborable compensable en las cuatr regiones.
-¿Son feriados o días no laborables? Es importante precisar que no son feriados nacionales, sino días no laborables sujetos a compensación.
-Esto significa que las horas dejadas de trabajar deberán recuperarse posteriormente, según las disposiciones establecidas en el decreto.
-- Sector público: las horas no trabajadas deberán compensarse dentro de los diez días inmediatos posteriores o en la oportunidad que establezca el titular de cada entidad.
-[Lea también: Visita del papa León XIV: 100,000 devotos asistirán a misa que se celebrará en Santa Cruz ] - Sector privado: el empleador y los trabajadores deberán acordar cómo se recuperarán las horas.
-Si no existe acuerdo, el empleador determinará la forma de compensación.
-- Servicios esenciales: las entidades públicas y empresas privadas comprendidas en las actividades indispensables deberán adoptar medidas para garantizar la continuidad de los servicios a la población.
-¿Qué otras regiones tendrán días no laborables? El decreto también establece disposiciones especiales para Lima, la Provincia Constitucional del Callao, Cusco y Ucayali.
-En Lima y el Callao, los días no laborables serán el 11 y 12 de noviembre, desde la 1:00 p.
-m.
-hasta la medianoche, y el 16 de noviembre durante toda la jornada.
-En Cusco y Ucayali, el 15 de noviembre será día no laborable únicamente para el sector privado.
-Por último, la disposición precisa que se busca facilitar la participación ciudadana y contribuir a la organización de las actividades previstas durante la visita papal.
-Más en Andina: El Gobierno prorrogó por 60 días, a partir del 28 de octubre, el estado de emergencia en los distritos de Tambopata, Inambari, Las Piedras y Laberinto, de la provincia de Tambopata, y en los distritos de Madre de Dios y Huepetuhe, de la provincia de Manu, en Madre de Dios.?? https://t.co/2iAHhacRpS (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 25, 2026</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-visita-del-papa-leon-xiv-dias-seran-no-laborables-lambayeque-y-cajamarca-1097062.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>¡Elecciones anuladas! Piura irá a nueva votación tras grave atentado contra material electoral en San Juan de Bigote</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>El Jurado Electoral Especial (JEE) de Morropón emitió la Resolución N.° 01104-2026-JEE-MORR/JNE , mediante la cual declaró formalmente nula la votación realizada el pasado 4 de octubre de 2026 en las veintitrés (23) mesas de sufragio del distrito de San Juan de Bigote , en la región Piura. La decisión se toma tras constatar graves irregularidades, disturbios y la pérdida de la cadena de custodia del material electoral. Puedes Leer | Piura: instalan sistema de bombeo en Las Azucenas para acelerar la evacuación de aguas pluviales ¿Qué pasó el día de las elecciones en San Juan de Bigote? De acuerdo con los informes de la Oficina Descentralizada de Procesos Electorales (ODPE) de Morropón y de la Coordinación de Fiscalización, la jornada transcurría en el único local de votación del distrito —la institución educativa José Carlos Mariátegui— cuando, alrededor de las 19:30 horas, personas ajenas al recinto irrumpieron violentamente durante el proceso de escrutinio. Los hechos de violencia obligaron al personal electoral y a los fiscalizadores a replegarse y resguardarse en el segundo piso del colegio. Tras restablecerse parcialmente el orden, se constató que las aulas habían quedado sin vigilancia y que el material electoral de las 23 mesas (que agrupaba a 6,710 electores hábiles) se encontraba disperso, fragmentado, roto y, en algunos casos, destruido. Imposibilidad de recuperar los votos y cadena de custodia rota En cumplimiento a mandatos previos del Jurado Nacional de Elecciones (JNE), la ODPE intentó aplicar los mecanismos de recuperación de resultados bajo el artículo 310 de la Ley Orgánica de Elecciones y evaluar un posible recuento de votos a partir de las 25 cajas de material recuperado con apoyo del Ministerio Público. Sin embargo, se determinó lo siguiente: No existían ejemplares de actas electorales válidas ni completas que permitieran reconstruir los resultados de las cuatro elecciones (regional, provincial y distrital). Las actas halladas carecían de datos de escrutinio o se encontraban rotas y siniestradas. Se declaró improcedente el recuento de cédulas debido a que la cadena de custodia se rompió durante las horas en que el material quedó expuesto sin control ni supervisión de las autoridades. Mira También | Diputado Castillo pide que gobernador rinda cuentas en comisión de Congreso ¿Qué sucederá ahora y cómo afecta al proceso de segunda vuelta en Piura? Ante la imposibilidad material y jurídica de rescatar la voluntad popular expresada en las urnas de dicha circunscripción, el JEE de Morropón declaró siniestradas las actas electorales del distrito y dispuso poner el caso en conocimiento del JNE. Una vez que la resolución quede firme, el Jurado Nacional de Elecciones deberá convocar a Elecciones Municipales Complementarias en San Juan de Bigote, donde los ciudadanos volverán a las urnas únicamente para elegir a sus autoridades distritales bajo nuevas condiciones de seguridad. Por otro lado, respecto al desarrollo general de las elecciones 2026 en Piura y los procesos en marcha —incluyendo la definición de una eventual segunda vuelta regional —, las autoridades electorales continuarán con el cómputo oficial en las demás jurisdicciones donde los comicios se desarrollaron con normalidad, deslindando este conflicto focalizado estrictamente al ámbito distrital de San Juan de Bigote.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/elecciones-anuladas-piura-ira-a-nueva-votacion-tras-grave-atentado-contra-material-electoral-en-san-juan-de-bigote/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B6" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fenómeno El Niño: Tumbes y Piura esperan lluvias de hasta 40 litros por m² hoy lunes 26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Según el aviso meteorológico N.º 435, en la costa interior de Piura se esperan lluvias de moderada a fuerte intensidad, mientras que en la sierra las precipitaciones serán de ligera a moderada intensidad.
+Estos eventos estarán acompañados de descargas eléctricas y ráfagas de viento cercanas a los 40 kilómetros por hora.
+????? #Aviso #MINAM #SENAMHI El 26 de octubre, continuarán las precipitaciones en la costa norte y sierra.? Estas precipitaciones estarán acompañadas de descargas eléctricas y ráfagas de viento.?? https://t.co/PaMlOv6Igp https://t.co/YofTj5FYWS — Senamhi (@Senamhiperu) October 25, 2026 El organismo, adscrito al Ministerio del Ambiente (Minam), recomendó a la población extremar las precauciones, mantenerse informada sobre la evolución de las condiciones meteorológicas y seguir las indicaciones de las autoridades.
+Lea también: Fenómeno El Niño en Piura: lluvias intensas inundan viviendas y arrastran lodo en Ayabaca ¿Cuánto lloverá este lunes 26 de octubre? El pronóstico del Senamhi establece los siguientes acumulados de precipitación para la jornada: Lea también: El Niño: lluvias se intensificarán desde noviembre y podrían alcanzar los 300 mm al día Costa norte: entre 4 y 40 mm/día, sierra norte: entre 10 y 25 mm/día, sierra centro: entre 8 y 15 mm/día, sierra sur: entre 6 y 24 mm/día.
+Nota de Prensa N.° 348-2026 | El @indeciperu recomienda medidas de preparación ante precipitaciones en la costa norte y sierra.
+Más información ?? https://t.co/SbBcdQSqO6 — COEN - INDECI (@COENPeru) October 26, 2026 En la sierra norte también se prevé la caída de granizo en localidades situadas por encima de los 2,800 metros sobre el nivel del mar.
+Las precipitaciones podrían presentarse junto con tormentas eléctricas y fuertes ráfagas de viento.
+Asimismo, el Senamhi no descarta la presencia de lloviznas en distritos próximos al litoral de la costa centro y sur.
+¿Qué regiones serán afectadas por las lluvias? El aviso meteorológico comprende provincias de 16 departamentos del país, desde la costa norte hasta la sierra sur y la selva alta.
+En el norte, el pronóstico incluye las siguientes provincias: Tumbes: Contralmirante Villar, Tumbes y Zarumilla; Piura: Ayabaca, Huancabamba, Morropón, Paita, Piura, Sullana y Talara; Lambayeque: Ferreñafe y Lambayeque; Cajamarca: Cajabamba, Cajamarca, Celendín, Chota, Cutervo, Hualgayoc, Jaén, San Ignacio, San Marcos, San Miguel, San Pablo y Santa Cruz.
+Asimismo, Amazonas: Chachapoyas y Luya; La Libertad: Bolívar, Gran Chimú, Otuzco, Pataz, Sánchez Carrión y Santiago de Chuco; y San Martín: Mariscal Cáceres y Tocache.
+En la zona centro del país, las precipitaciones alcanzarán provincias de Áncash, Huánuco, Junín, Pasco y Huancavelica.
+En el sur, el pronóstico comprende provincias de Apurímac, Ayacucho, Cusco y Puno, donde se esperan precipitaciones de acuerdo con los rangos previstos para la sierra.
+Senamhi recomienda extremar precauciones Ante la previsión de precipitaciones y fenómenos meteorológicos de considerable magnitud, el Senamhi exhortó a la población a mantenerse atenta a las actualizaciones del pronóstico y cumplir las recomendaciones de las autoridades.
+Las lluvias acompañadas de descargas eléctricas, granizo y ráfagas de viento pueden generar condiciones peligrosas, por lo que se recomienda evitar la exposición durante las tormentas y mantenerse informados a través de los canales oficiales.
+Más en Andina: ????? Las intensas lluvias del domingo 25 de octubre inundaron viviendas y arrastraron lodo por calles de Ayabaca, en la sierra de Piura.
+También se reportaron pequeños deslizamientos.
+Las familias esperan la evaluación de daños y medidas de prevención.
+?? https://t.co/7Jl4S9tBTc https://t.co/6g7FDovKi9 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 26, 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-fenomeno-nino-tumbes-y-piura-esperan-lluvias-hasta-40-litros-m²-hoy-lunes-26-1097363.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>¿Por qué 15 de noviembre será no laborable solo para el sector privado en Cusco y Ucayali?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A diferencia de otras regiones comprendidas en el Decreto Supremo N.° 020-2026-TR publicado por el Gobierno con motivo de la visita del papa León XIV al Perú, la disposición establece que los trabajadores del sector público de Cusco y Ucayali no están incluidos en este beneficio.
+La medida busca facilitar la participación de la población y trabajadores en las actividades vinculadas con la visita del sumo pontífice, prevista del 11 al 16 de noviembre de 2026.
+[Lea también: Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca? ] La norma establece que el día no laborable del 15 de noviembre corresponde únicamente al sector privado en ambas regiones, donde se desarrollarán actividades relacionadas con la visita papal, debido a que la mayoría de trabajadores del sector público descansa esa fecha.
+¿Cómo se aplicará el día no laborable en Cusco y Ucayali? De acuerdo con el decreto supremo, los centros laborales del sector privado podrán acogerse a la medida previo acuerdo entre el empleador y los trabajadores.
+Si no se alcanza un consenso, corresponderá al empleador tomar la decisión.
+Asimismo, las horas dejadas de trabajar deberán recuperarse según lo que establezca el acuerdo entre ambas partes.
+Si no existe acuerdo sobre la compensación, el empleador determinará cómo se recuperarán.
+[Lea también: León XIV en Cusco: 130,000 fieles recibirán al papa en Sacsayhuamán y la Plaza de Armas ] No se trata de un feriado nacional, sino de un día no laborable sujeto a compensación de horas.
+¿Qué regiones tendrán días no laborables para el sector público y privado? El Decreto Supremo N.° 020-2026-TR establece diferentes fechas no laborables según el ámbito geográfico y el régimen laboral.
+En Lima y la Provincia Constitucional del Callao, los días no laborables serán el 11 y 12 de noviembre, desde la 1:00 p.
+m.
+hasta la medianoche, y el 16 de noviembre durante toda la jornada, tanto para el sector público como para el privado.
+En Cajamarca, La Libertad, Lambayeque y Piura, la medida regirá el 13 y 14 de noviembre para los trabajadores de ambos sectores.
+En cambio, en Cusco y Ucayali, el día no laborable será el 15 de noviembre y estará dirigido exclusivamente al sector privado.
+Servicios esenciales deberán mantener sus operaciones La norma también contempla disposiciones para garantizar la continuidad de las actividades económicas y los servicios indispensables para la población.
+Entre ellos figuran los servicios de salud, transporte, electricidad, agua, telecomunicaciones, seguridad, hospedaje, restaurantes y entidades financieras , entre otros.
+Las empresas comprendidas en estas actividades podrán determinar qué puestos de trabajo deberán continuar operando durante los días no laborables, a fin de asegurar la atención a los ciudadanos.
+La visita del papa León XIV al Perú constituye un acontecimiento de especial trascendencia espiritual, histórica y social, según los considerandos del decreto, que establece facilidades laborales diferenciadas para las regiones comprendidas en el recorrido del pontífice.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-por-15-noviembre-sera-no-laborable-solo-para-sector-privado-cusco-y-ucayali-1097083.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fenómeno El Niño en Piura: lluvias intensas inundan viviendas y arrastran lodo en Ayabaca</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Videos difundidos por vecinos en redes sociales muestran la fuerza de la corriente, que arrastró barro y material suelto por distintas vías e ingresó a algunos domicilios y establecimientos comerciales.
+También se reportaron pequeños deslizamientos y acumulación de material arcilloso en las vías de acceso a la ciudad.
+Barro y problemas de drenaje en las calles En la calle San Sebastián, ubicada en el barrio Sur, la corriente de agua arrastró barro y material suelto.
+Mientras tanto, vecinos del barrio El Cerro expresaron su preocupación por la situación de la calle Vallejo, donde, según denunciaron, las obras llevan más de cuatro meses de intervención y persisten zanjas abiertas y problemas de drenaje.
+Los residentes temen que nuevas precipitaciones agraven las afectaciones en las viviendas y vías urbanas, especialmente en los sectores donde el agua no logra evacuar adecuadamente.
+Vecinos esperan respuesta de las autoridades Ante la emergencia, los pobladores esperan que las autoridades evalúen los daños, identifiquen a las familias afectadas y adopten medidas para reducir los riesgos si continúan las lluvias.
+El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) había advertido sobre la posibilidad de precipitaciones de moderada a fuerte intensidad en la sierra de Piura, con acumulados de hasta 30 milímetros, según la información proporcionada.
+Se recomienda a la población mantenerse informada mediante los canales oficiales y evitar cruzar calles inundadas, corrientes de agua o zonas expuestas a posibles deslizamientos.
+Más en Andina:</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-fenomeno-nino-piura-lluvias-intensas-inundan-viviendas-y-arrastran-lodo-ayabaca-1097355.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lluvias en el norte del Perú: noticias de precipitaciones en Piura, Tumbes y Trujillo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/peru/piura-y-el-norte-del-peru-bajo-lluvias-intensas-ultimas-noticias-alerta-por-el-nino-e-informe-del-coen-en-vivo-lbposting-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Solo el 2,7% de la población en riesgo recibió las dos dosis de la vacuna contra el dengue</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>La noticia a fines de julio era que el Perú había comenzado a recibir los lotes de las más de 400 mil vacunas contra el dengue que compró. El ministro de Salud, Luis Dyer, posó al lado del cargamento que traía miles de dosis listas para comenzar a ser aplicadas. Casi tres meses después de ese momento, el panorama es desolador y la situación, cada vez más alarmante. Hay preocupación porque, en lo que va del año, los casos de dengue han duplicado la cifra registrada en 2025. Además, las cifras que dejó esta enfermedad endémica en 2023 y 2024 fueron catastróficas: más de 700 personas murieron durante esos dos años, con el norte del país como la zona más afectada. Las recientes lluvias en el norte han activado aún más las alarmas. Las calles inundadas, los aniegos y el agua empozada en distintas zonas favorecen la proliferación del zancudo Aedes aegypti, transmisor del dengue. A ello se suma el calor de las últimas semanas, que favorece la reproducción del mosquito y puede aumentar su capacidad de transmitir la enfermedad. En un escenario de Fenómeno El Niño que será “muy fuerte o sin precedentes”, según la Organización Meteorológica Mundial, los casos podrían seguir aumentando. Una vacunación a paso de tortuga En las cifras que brinda el Ministerio de Salud, a través de Reunis (Repositorio Único Nacional de Información en Salud), los datos tampoco son muy alentadores. En cuanto al avance de cobertura de primeras dosis, apenas se llega al 30,8%, y los niños de 10 años son quienes más se han vacunado. En el caso de las segundas dosis, solo se han aplicado 7.391, lo que se traduce en un avance de cobertura del 2,7% de la población objetivo. La meta del Ministerio de Salud era vacunar con ambas dosis a 271.935 personas. Y esto, claramente, no ha ocurrido. La población objetivo está conformada por personas de entre 10 y 20 años que viven en zonas con mayor riesgo frente a la enfermedad. En Lima, comprende los distritos de San Juan de Lurigancho, Independencia, Carabayllo y San Martín de Porres; en la costa norte, las regiones de Tumbes, Piura, Lambayeque y La Libertad; y en la selva, la región San Martín y la provincia de Maynas, en Loreto. Para el doctor César Munayco, jefe del Centro Nacional de Epidemiología, Prevención y Control de Enfermedades (CDC Perú), sí hay algunas localidades que registran un buen avance. “Una zona a la que le va bien es Tumbes, y estamos un poco retrasados en Loreto y en Ucayali. Se están haciendo las estrategias en colegios y algunos puntos de vacunación para que la población pueda vacunarse”, señaló el médico. “Yo creo que es importante resaltar que son vacunas gratuitas y seguras, pero la decisión está en la persona”, indicó. Mientras que, para la directora ejecutiva de la Dirección de Inmunizaciones del Minsa, Margarita Yanamango Contreras, “algunos consideran que las vacunas no son importantes y que, por el contrario, producen enfermedad. Sin embargo, las molestias posvacunales son normales y se dan porque el sistema inmunológico está creando los anticuerpos específicos (defensas)”. Además, ante la próxima llegada de más de un millón de vacunas contra el dengue, la experta instó a la población a acudir a los puntos de vacunación y completar el esquema. “Las personas no completan las segundas dosis porque se olvidan y porque asumen que con una dosis es suficiente”, advirtió. Hoy, los esfuerzos para llegar a más población objetivo son insuficientes y no están articulados. Existe un vacunatorio grande en San Juan de Lurigancho al que la población de Lima debe acudir si quiere inmunizarse. Mientras que en EsSalud, en Lince, la afluencia de personas que llegan a vacunarse contra el dengue es mínima. En las regiones, el panorama no cambia mucho. En Piura, por ejemplo, se están realizando campañas para llegar a más personas y acercarse a las cifras esperadas. Edward Pozo, jefe de la Oficina de Inteligencia Sanitaria de la Red Asistencial Piura de EsSalud, nos cuenta: “Nos dotaron de 2.500 vacunas y ya hemos administrado el 50% dentro del grupo etario de 10 a 20 años. Además, estamos haciendo campañas intensas en Morropón, Bajo Piura y Sullana para también administrar la vacuna. Una vez acabemos ese monto, vamos a solicitar más (al Ministerio de Salud)”. Así funciona la vacuna Qdenga, del laboratorio Takeda, es una vacuna tetravalente que se administra en dos dosis. Entre la primera y la segunda debe transcurrir un periodo de tres meses para garantizar su efectividad y completar el esquema de inmunización. En Perú se aplica a niños y adolescentes de entre 10 y 20 años, de acuerdo con las recomendaciones de especialistas del sector Salud. Puede causar efectos secundarios como dolor de cabeza, fatiga o fiebre, pero estos suelen desaparecer entre uno y tres días después. El Ministerio de Salud ha señalado que la vacuna contra el dengue es segura y que protege a miles de niños y adolescentes desde 2024, cuando comenzó a aplicarse. El Niño, una amenaza latente Es inminente y hasta sobreentendido que el fenómeno El Niño, proyectado para noviembre de 2026 y los primeros meses de 2027, será intenso y afectará de manera directa a nuestro país. Y aunque hoy ya parece que estamos tarde para cualquier medida de prevención, todo esfuerzo por contener los embates de este evento climático suma. Como ocurrió con el Niño Costero en 2017 o el ciclón Yaku en 2023, los fenómenos climáticos afectan a varias regiones del Perú: la costa norte, la selva central y también la capital. Es allí donde aparecen enfermedades endémicas como el dengue, la leptospirosis y otras. En las proyecciones, el director del CDC del Ministerio de Salud, César Munayco, señala que el peor escenario es que se presenten epidemias como las ocurridas en 2023 y 2024. En ambos años se registraron más de 250 mil casos anuales de dengue y la cifra de fallecidos llegó a 444 en 2023 y a 261 en 2024. Las regiones más afectadas en esa época fueron Piura, Lambayeque, La Libertad y Lima. En este 2026, todo es atípico. Normalmente, el dengue es una enfermedad con un comportamiento estacional, pero este año, debido al fenómeno El Niño, “hemos empezado muy temprano con los casos. El zancudo se vuelve más eficiente en transmitir la enfermedad. Y el dengue, como la temperatura permanece más tiempo elevada, hace que el riesgo sea mucho mayor y haya más casos, como ahora”, indicó Munayco. Una inminente crisis sanitaria La Organización Panamericana de la Salud (OPS), en sus previsiones, ha pedido al personal médico peruano calcular que el 4,5% de la población podría enfermarse de dengue. Luego habría que distinguir entre los tipos de esta enfermedad: hay casos en los que ni siquiera se presentan signos de alarma y el paciente puede ser atendido en su casa sin ningún problema, pero hay otros en los que puede requerir hospitalización o ser trasladado a una unidad de cuidados intensivos (UCI). Allí es donde entra a tallar qué tan listo está el sistema sanitario para un escenario como este. ¿Cuántas camas, médicos, personal de enfermería, técnicos y medicamentos se necesitan de acuerdo con la condición del paciente? En 2023 se vivió un escenario como ese y hay situaciones que no deberían repetirse, sobre todo por las limitaciones que mostró la respuesta del sistema de salud ante aquella crisis. “Los esfuerzos del sistema de salud están enfocados en reducir la mortalidad”, señala César Munayco. “Lamentablemente, los casos va a ser bien complicado reducirlos, porque se requiere a un ejército de personas para abordar ese tema”, añadió. Además, el médico hizo una comparación de cómo afectó el dengue al país en 2023 y 2024: “Si bien en el 2024 hubo más casos, el número de fallecidos se redujo. Esto porque se intervino en capacitación al personal, enviando infectólogos con experiencia a las zonas nuevas en ser afectadas, como Ica y Áncash”. Lo importante es que la población que detecte signos de alarma pueda acudir rápidamente a los servicios de salud. Aquí, cada minuto cuenta. No hay primera sin segunda La vacuna contra el dengue no abunda ni está disponible para todos. El Perú ha podido adquirir un lote importante de dosis debido a la exposición que tendrá ante la llegada del fenómeno El Niño. El grupo etario al que se le está administrando esta vacuna es el de personas de 10 a 20 años, por recomendación de la Organización Mundial de la Salud (OMS). Pero es más importante aún entender y dimensionar la importancia de la segunda dosis. Solo así se puede completar el esquema de inmunización contra el dengue. El intervalo entre una y otra dosis es de tres meses y, en este escenario, en el que es inminente que aumenten los contagios de dengue, vacunarse es primordial. Que el desconocimiento, el miedo o la incertidumbre por los posibles efectos de una vacuna no pongan en duda su efectividad. El Ministerio de Salud debe reforzar los puntos de vacunación, preparar más brigadas y llegar cada vez a más lugares y a más personas que puedan ser inmunizadas. Hasta aquí, la estrategia de vacunación no ha funcionado, pero aún hay tiempo de enmendar y corregir lo que no se está haciendo bien. Solo en este año, hay más de 70 muertes por dengue. Está en manos de los responsables del sector Salud evitar que esta cifra aumente de manera trágica. IMPORTANTE En Lima, el ministerio de Salud es el que lidera la aplicación de la vacuna contra el dengue a los residentes del distrito de San Juan de Lurigancho. Para recibir la primera o segunda dosis, se debe acudir a los centros de salud del Minsa en SJL, presentar el documento que acredite la edad entre 10 y 20 años y que residen en el distrito. En los colegios, los menores deberán presentar un consentimiento firmado por el padre, madre o apoderado. El Ministerio de Salud informará sobre cualquir zona nueva de intervencióny establecimientos que colocarán la vacuna. Mientras que en EsSalud pueden acudir al vacunatorio Playa Miller, para inmunizarse contra otras enfermedades infecciosas, como la fiebre amarilla.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/lima/sucesos/solo-el-27-de-la-poblacion-en-riesgo-recibio-las-dos-dosis-de-la-vacuna-contra-el-dengue-apuesplan-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Piura: Producción de mango caería hasta 90% en San Lorenzo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>La producción de mango en el valle de San Lorenzo podría desplomarse hasta en un 90 % debido a las alteraciones climáticas asociadas al Fenómeno El Niño (FEN). Así lo advirtió Miguel Castillo Vera, presidente de la Junta de Usuarios de San Lorenzo, quien señaló que las elevadas temperaturas registradas durante los últimos meses han perjudicado la floración de este cultivo, considerado uno de los principales motores económicos del valle piurano. El dirigente explicó que una hectárea de mango, que normalmente produce entre 3 mil y 5 mil jabas, podría rendir apenas entre 50 y 100 durante la presente campaña. “El impacto ya lo tenemos, ya lo vivimos», expresó Castillo Vera, al señalar que los agricultores han realizado inversiones para estimular la floración, pero sin obtener los resultados esperados para la presente campaña de la fruta.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-produccion-de-mango-caeria-hasta-90-en-san-lorenzo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Piura: Paralización de puente deja indefensa a población en Cura Mori</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Los pobladores del caserío Santa Rosa se encuentran en constante estado de preocupación ante la paralización de la obra del puente de ingreso a su localidad. PUEDES LEER ► A la cárcel dos sujetos por ultrajar a menores: sentenciados a 20 y 35 años de prisión Esta infraestructura es la principal vía de tránsito y evacuación frente a probables precipitaciones pluviales o la amenaza del fenómeno El Niño. La suspensión de los trabajos responde a la necesidad de modificar el expediente técnico y corregir el diseño inicial. El presidente de la Comisión de Regantes de Puyuntala, Óscar Huidobro Castillo, explicó que el puente debe quedar entre 40 y 50 centímetros por encima del nivel de la pista. Esta readecuación técnica es indispensable para evitar que el caudal del canal, cargado de maleza, residuos sólidos y animales muertos, cause severos taponamientos y desbordes hacia el sector Pedregal. Actualmente, la comisión debe desembolsar 1,000 soles mensuales para contratar personal que retire manualmente la basura de la zona. Atendiendo las demandas de vecinos y transportistas, la dirigencia acordó también desplazar la ubicación del puente unos metros aguas arriba, evitando así comprometer la caseta de agua potable existente y prevenir accidentes. Ante la ausencia de un desvío oficial acondicionado por las autoridades, Huidobro facilitó maquinaria de su propiedad para habilitar provisionalmente un camino de servicio. Respecto al estancamiento de los trabajos, el dirigente aclaró que la oficina del Programa Subsectorial de Irrigaciones (PSI) en Piura funciona como mesa de partes, mientras que la aprobación final depende de Lima.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-paralizacion-de-puente-deja-indefensa-a-poblacion-en-cura-mori/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Piura: padre de familia queda gravemente herido tras caer del segundo piso de su vivienda</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Un padre de familia resultó gravemente herido luego de caer desde el segundo piso de su vivienda mientras realizaba trabajos de mantenimiento en el techo para proteger su inmueble ante la posible llegada del Fenómeno El Niño. El accidente ocurrió en la urbanización La Planicie, cuarta etapa, en el distrito de Veintiséis de Octubre, en Piura. La víctima fue identificada como Jhon Carlos Cortez Calle, quien acondicionaba la cobertura de su casa cuando perdió el equilibrio y cayó al pavimento. El fuerte impacto alertó a sus familiares, quienes solicitaron ayuda de inmediato. Serenazgo y SAMU auxiliaron al herido Tras recibir la alerta, agentes de Serenazgo de Veintiséis de Octubre acudieron al inmueble para brindarle los primeros auxilios y resguardar el lugar mientras llegaba el personal médico. Posteriormente, una ambulancia del Sistema de Atención Médica de Urgencia (SAMU) llegó a la vivienda para estabilizar al afectado y trasladarlo al hospital Santa Rosa de Piura. En el establecimiento de salud, el personal médico diagnosticó al paciente traumatismos múltiples de gravedad y una fractura en la pierna derecha. Debido a las lesiones, quedó en el área de observación, donde sería sometido a exámenes adicionales para descartar posibles complicaciones internas. Recomiendan tomar precauciones al realizar trabajos en altura Ante este tipo de accidentes, las autoridades locales exhortaron a la población a adoptar medidas de seguridad al efectuar reparaciones en sus viviendas, especialmente cuando se trata de trabajos en techos o zonas elevadas. Asimismo, recomendaron utilizar equipos de protección adecuados para reducir el riesgo de caídas y lesiones durante las labores de acondicionamiento de los inmuebles frente a posibles eventos climáticos.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-padre-de-familia-queda-gravemente-herido-tras-caer-del-segundo-piso-de-su-vivienda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ministro de Vivienda: estamos haciendo un trabajo titánico para enfrentar fenómeno El Niño</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>En declaraciones a RPP , señaló que llegó a la región Arequipa para liderar 11 intervenciones de su sector en la limpieza y descolmatación de cauces y quebradas en la provincia de Arequipa, cinco intervenciones en la provincia de La Unión y 10 intervenciones en la provincia de Caravelí.
+Lea también: Fenómeno El Niño: EsSalud vacuna a escolares de Piura ante el dengue y otras enfermedades Arnillas González agregó que la Comisión Nacional de Gestión del Riesgo del Fenómeno El Niño (FEN) entregó a su sector 55 puntos a nivel nacional, de los cuales 24 se encuentran en la región Arequipa.
+"Como Gobierno estamos limpiando 536 cauces a nivel nacional y en total hemos identificado 1,900; el resto de cauces los estamos trabajando con empresas privadas, a través de obras por impuestos y servicios por impuestos.
+Entonces, estamos haciendo un trabajo titánico para que el Perú pueda soportar de la mejor manera al fenómeno que viene", dijo.
+Arnillas González recordó que la alerta de un fenómeno de El Niño extraordinario se dio en febrero del 2026.
+Sin embargo, el ministro lamentó que no se hizo ninguna obra hasta finales de julio.
+Lea también: ¿Qué semejanzas y diferencias tienen los fenómenos El Niño Costero y El Niño global? Sector Vivienda en emergencia El ministro Arnillas González anunció que el día de hoy, a través de un decreto supremo, se ha declarado en situación de emergencia a los sectores de Vivienda, Urbanismo y Desarrollo Urbano y Saneamiento .
+Según la norma, se busca solucionar las condiciones críticas que afectan el acceso de la población a soluciones integrales de vivienda y urbanismo; así como, el acceso, la calidad, la continuidad, la confiabilidad y la sostenibilidad de los servicios de agua potable y saneamiento.
+Lea también: Fenómeno El Niño: todo lo que debes saber del bono anunciado por el Gobierno "Tenemos 15 millones de peruanos que no tienen desagüe en el país y nueve millones que no tienen servicio de agua potable.
+Por eso hemos declarado el sector en emergencia para reorganizarlo profundamente y sacar una normativa de un funcionamiento del ministerio acorde con esta emergencia y superarlo a nivel nacional", expresó.
+Exhortación a población Además, Arnillas González coincidió con el ministro de Salud, Luis Dyer, al recomendar a los peruanos prepararse para lo peor por El Niño y exhortó a tomar conciencia si se vive en zonas de riesgo.
+"Aprovecho para decirle a la población que aún vive dentro de las torrenteras, que piensen en su vida; lo importante acá es salvar vidas humanas.
+Ellos mismos tienen que tomar la decisión de salir de las torrenteras cuanto antes.
+No van a esperar que empiece el fenómeno El Niño o que el agua esté encima para salir", manifestó.
+Más en Andina: ?? ¿Qué tipo de peligros naturales provoca el Fenómeno El Niño (FEN) en las regiones de Perú? https://t.co/sXJUHwb0qs https://t.co/2fGwCdPKqW (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 24, 2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-ministro-vivienda-estamos-haciendo-un-trabajo-titanico-para-enfrentar-fenomeno-nino-1097281.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>BCR: se acelera crecimiento de la construcción y PBI no primario crece 4.3% en agosto</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Señaló que en el mes de análisis el PBI no primario se expandió 4.3% sustentado en la aceleración del crecimiento de la construcción y el comercio.
 En contraste, continuó, el PBI primario se contrajo 0.9% por la menor actividad de la pesca, la minería metálica y los hidrocarburos.
@@ -603,229 +887,27 @@
 Más en Andina: Casi 4 de cada 10 trabajadores en Perú sienten que 2026 ha sido mejor de lo esperado ?? https://t.co/Oz5He2LYPH https://t.co/m9AwfjaFti (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 25, 2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-bcr-se-acelera-crecimiento-de-construccion-y-pbi-no-primario-crece-43-agosto-1097294.aspx</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ministro de Vivienda: estamos haciendo un trabajo titánico para enfrentar fenómeno El Niño</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>En declaraciones a RPP , señaló que llegó a la región Arequipa para liderar 11 intervenciones de su sector en la limpieza y descolmatación de cauces y quebradas en la provincia de Arequipa, cinco intervenciones en la provincia de La Unión y 10 intervenciones en la provincia de Caravelí.
-Lea también: Fenómeno El Niño: EsSalud vacuna a escolares de Piura ante el dengue y otras enfermedades Arnillas González agregó que la Comisión Nacional de Gestión del Riesgo del Fenómeno El Niño (FEN) entregó a su sector 55 puntos a nivel nacional, de los cuales 24 se encuentran en la región Arequipa.
-"Como Gobierno estamos limpiando 536 cauces a nivel nacional y en total hemos identificado 1,900; el resto de cauces los estamos trabajando con empresas privadas, a través de obras por impuestos y servicios por impuestos.
-Entonces, estamos haciendo un trabajo titánico para que el Perú pueda soportar de la mejor manera al fenómeno que viene", dijo.
-Arnillas González recordó que la alerta de un fenómeno de El Niño extraordinario se dio en febrero del 2026.
-Sin embargo, el ministro lamentó que no se hizo ninguna obra hasta finales de julio.
-Lea también: ¿Qué semejanzas y diferencias tienen los fenómenos El Niño Costero y El Niño global? Sector Vivienda en emergencia El ministro Arnillas González anunció que el día de hoy, a través de un decreto supremo, se ha declarado en situación de emergencia a los sectores de Vivienda, Urbanismo y Desarrollo Urbano y Saneamiento .
-Según la norma, se busca solucionar las condiciones críticas que afectan el acceso de la población a soluciones integrales de vivienda y urbanismo; así como, el acceso, la calidad, la continuidad, la confiabilidad y la sostenibilidad de los servicios de agua potable y saneamiento.
-Lea también: Fenómeno El Niño: todo lo que debes saber del bono anunciado por el Gobierno "Tenemos 15 millones de peruanos que no tienen desagüe en el país y nueve millones que no tienen servicio de agua potable.
-Por eso hemos declarado el sector en emergencia para reorganizarlo profundamente y sacar una normativa de un funcionamiento del ministerio acorde con esta emergencia y superarlo a nivel nacional", expresó.
-Exhortación a población Además, Arnillas González coincidió con el ministro de Salud, Luis Dyer, al recomendar a los peruanos prepararse para lo peor por El Niño y exhortó a tomar conciencia si se vive en zonas de riesgo.
-"Aprovecho para decirle a la población que aún vive dentro de las torrenteras, que piensen en su vida; lo importante acá es salvar vidas humanas.
-Ellos mismos tienen que tomar la decisión de salir de las torrenteras cuanto antes.
-No van a esperar que empiece el fenómeno El Niño o que el agua esté encima para salir", manifestó.
-Más en Andina: ?? ¿Qué tipo de peligros naturales provoca el Fenómeno El Niño (FEN) en las regiones de Perú? https://t.co/sXJUHwb0qs https://t.co/2fGwCdPKqW (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 24, 2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-ministro-vivienda-estamos-haciendo-un-trabajo-titanico-para-enfrentar-fenomeno-nino-1097281.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>¿Por qué 15 de noviembre será no laborable solo para el sector privado en Cusco y Ucayali?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A diferencia de otras regiones comprendidas en el Decreto Supremo N.° 020-2026-TR publicado por el Gobierno con motivo de la visita del papa León XIV al Perú, la disposición establece que los trabajadores del sector público de Cusco y Ucayali no están incluidos en este beneficio.
-La medida busca facilitar la participación de la población y trabajadores en las actividades vinculadas con la visita del sumo pontífice, prevista del 11 al 16 de noviembre de 2026.
-[Lea también: Visita del papa León XIV: ¿qué días serán no laborables en Lambayeque y Cajamarca? ] La norma establece que el día no laborable del 15 de noviembre corresponde únicamente al sector privado en ambas regiones, donde se desarrollarán actividades relacionadas con la visita papal, debido a que la mayoría de trabajadores del sector público descansa esa fecha.
-¿Cómo se aplicará el día no laborable en Cusco y Ucayali? De acuerdo con el decreto supremo, los centros laborales del sector privado podrán acogerse a la medida previo acuerdo entre el empleador y los trabajadores.
-Si no se alcanza un consenso, corresponderá al empleador tomar la decisión.
-Asimismo, las horas dejadas de trabajar deberán recuperarse según lo que establezca el acuerdo entre ambas partes.
-Si no existe acuerdo sobre la compensación, el empleador determinará cómo se recuperarán.
-[Lea también: León XIV en Cusco: 130,000 fieles recibirán al papa en Sacsayhuamán y la Plaza de Armas ] No se trata de un feriado nacional, sino de un día no laborable sujeto a compensación de horas.
-¿Qué regiones tendrán días no laborables para el sector público y privado? El Decreto Supremo N.° 020-2026-TR establece diferentes fechas no laborables según el ámbito geográfico y el régimen laboral.
-En Lima y la Provincia Constitucional del Callao, los días no laborables serán el 11 y 12 de noviembre, desde la 1:00 p.
-m.
-hasta la medianoche, y el 16 de noviembre durante toda la jornada, tanto para el sector público como para el privado.
-En Cajamarca, La Libertad, Lambayeque y Piura, la medida regirá el 13 y 14 de noviembre para los trabajadores de ambos sectores.
-En cambio, en Cusco y Ucayali, el día no laborable será el 15 de noviembre y estará dirigido exclusivamente al sector privado.
-Servicios esenciales deberán mantener sus operaciones La norma también contempla disposiciones para garantizar la continuidad de las actividades económicas y los servicios indispensables para la población.
-Entre ellos figuran los servicios de salud, transporte, electricidad, agua, telecomunicaciones, seguridad, hospedaje, restaurantes y entidades financieras , entre otros.
-Las empresas comprendidas en estas actividades podrán determinar qué puestos de trabajo deberán continuar operando durante los días no laborables, a fin de asegurar la atención a los ciudadanos.
-La visita del papa León XIV al Perú constituye un acontecimiento de especial trascendencia espiritual, histórica y social, según los considerandos del decreto, que establece facilidades laborales diferenciadas para las regiones comprendidas en el recorrido del pontífice.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-por-15-noviembre-sera-no-laborable-solo-para-sector-privado-cusco-y-ucayali-1097083.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Piura: padre de familia queda gravemente herido tras caer del segundo piso de su vivienda</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Un padre de familia resultó gravemente herido luego de caer desde el segundo piso de su vivienda mientras realizaba trabajos de mantenimiento en el techo para proteger su inmueble ante la posible llegada del Fenómeno El Niño. El accidente ocurrió en la urbanización La Planicie, cuarta etapa, en el distrito de Veintiséis de Octubre, en Piura. La víctima fue identificada como Jhon Carlos Cortez Calle, quien acondicionaba la cobertura de su casa cuando perdió el equilibrio y cayó al pavimento. El fuerte impacto alertó a sus familiares, quienes solicitaron ayuda de inmediato. Serenazgo y SAMU auxiliaron al herido Tras recibir la alerta, agentes de Serenazgo de Veintiséis de Octubre acudieron al inmueble para brindarle los primeros auxilios y resguardar el lugar mientras llegaba el personal médico. Posteriormente, una ambulancia del Sistema de Atención Médica de Urgencia (SAMU) llegó a la vivienda para estabilizar al afectado y trasladarlo al hospital Santa Rosa de Piura. En el establecimiento de salud, el personal médico diagnosticó al paciente traumatismos múltiples de gravedad y una fractura en la pierna derecha. Debido a las lesiones, quedó en el área de observación, donde sería sometido a exámenes adicionales para descartar posibles complicaciones internas. Recomiendan tomar precauciones al realizar trabajos en altura Ante este tipo de accidentes, las autoridades locales exhortaron a la población a adoptar medidas de seguridad al efectuar reparaciones en sus viviendas, especialmente cuando se trata de trabajos en techos o zonas elevadas. Asimismo, recomendaron utilizar equipos de protección adecuados para reducir el riesgo de caídas y lesiones durante las labores de acondicionamiento de los inmuebles frente a posibles eventos climáticos.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-padre-de-familia-queda-gravemente-herido-tras-caer-del-segundo-piso-de-su-vivienda/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Solo el 2,7% de la población en riesgo recibió las dos dosis de la vacuna contra el dengue</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>La noticia a fines de julio era que el Perú había comenzado a recibir los lotes de las más de 400 mil vacunas contra el dengue que compró. El ministro de Salud, Luis Dyer, posó al lado del cargamento que traía miles de dosis listas para comenzar a ser aplicadas. Casi tres meses después de ese momento, el panorama es desolador y la situación, cada vez más alarmante. Hay preocupación porque, en lo que va del año, los casos de dengue han duplicado la cifra registrada en 2025. Además, las cifras que dejó esta enfermedad endémica en 2023 y 2024 fueron catastróficas: más de 700 personas murieron durante esos dos años, con el norte del país como la zona más afectada. Las recientes lluvias en el norte han activado aún más las alarmas. Las calles inundadas, los aniegos y el agua empozada en distintas zonas favorecen la proliferación del zancudo Aedes aegypti, transmisor del dengue. A ello se suma el calor de las últimas semanas, que favorece la reproducción del mosquito y puede aumentar su capacidad de transmitir la enfermedad. En un escenario de Fenómeno El Niño que será “muy fuerte o sin precedentes”, según la Organización Meteorológica Mundial, los casos podrían seguir aumentando. Una vacunación a paso de tortuga En las cifras que brinda el Ministerio de Salud, a través de Reunis (Repositorio Único Nacional de Información en Salud), los datos tampoco son muy alentadores. En cuanto al avance de cobertura de primeras dosis, apenas se llega al 30,8%, y los niños de 10 años son quienes más se han vacunado. En el caso de las segundas dosis, solo se han aplicado 7.391, lo que se traduce en un avance de cobertura del 2,7% de la población objetivo. La meta del Ministerio de Salud era vacunar con ambas dosis a 271.935 personas. Y esto, claramente, no ha ocurrido. La población objetivo está conformada por personas de entre 10 y 20 años que viven en zonas con mayor riesgo frente a la enfermedad. En Lima, comprende los distritos de San Juan de Lurigancho, Independencia, Carabayllo y San Martín de Porres; en la costa norte, las regiones de Tumbes, Piura, Lambayeque y La Libertad; y en la selva, la región San Martín y la provincia de Maynas, en Loreto. Para el doctor César Munayco, jefe del Centro Nacional de Epidemiología, Prevención y Control de Enfermedades (CDC Perú), sí hay algunas localidades que registran un buen avance. “Una zona a la que le va bien es Tumbes, y estamos un poco retrasados en Loreto y en Ucayali. Se están haciendo las estrategias en colegios y algunos puntos de vacunación para que la población pueda vacunarse”, señaló el médico. “Yo creo que es importante resaltar que son vacunas gratuitas y seguras, pero la decisión está en la persona”, indicó. Mientras que, para la directora ejecutiva de la Dirección de Inmunizaciones del Minsa, Margarita Yanamango Contreras, “algunos consideran que las vacunas no son importantes y que, por el contrario, producen enfermedad. Sin embargo, las molestias posvacunales son normales y se dan porque el sistema inmunológico está creando los anticuerpos específicos (defensas)”. Además, ante la próxima llegada de más de un millón de vacunas contra el dengue, la experta instó a la población a acudir a los puntos de vacunación y completar el esquema. “Las personas no completan las segundas dosis porque se olvidan y porque asumen que con una dosis es suficiente”, advirtió. Hoy, los esfuerzos para llegar a más población objetivo son insuficientes y no están articulados. Existe un vacunatorio grande en San Juan de Lurigancho al que la población de Lima debe acudir si quiere inmunizarse. Mientras que en EsSalud, en Lince, la afluencia de personas que llegan a vacunarse contra el dengue es mínima. En las regiones, el panorama no cambia mucho. En Piura, por ejemplo, se están realizando campañas para llegar a más personas y acercarse a las cifras esperadas. Edward Pozo, jefe de la Oficina de Inteligencia Sanitaria de la Red Asistencial Piura de EsSalud, nos cuenta: “Nos dotaron de 2.500 vacunas y ya hemos administrado el 50% dentro del grupo etario de 10 a 20 años. Además, estamos haciendo campañas intensas en Morropón, Bajo Piura y Sullana para también administrar la vacuna. Una vez acabemos ese monto, vamos a solicitar más (al Ministerio de Salud)”. Así funciona la vacuna Qdenga, del laboratorio Takeda, es una vacuna tetravalente que se administra en dos dosis. Entre la primera y la segunda debe transcurrir un periodo de tres meses para garantizar su efectividad y completar el esquema de inmunización. En Perú se aplica a niños y adolescentes de entre 10 y 20 años, de acuerdo con las recomendaciones de especialistas del sector Salud. Puede causar efectos secundarios como dolor de cabeza, fatiga o fiebre, pero estos suelen desaparecer entre uno y tres días después. El Ministerio de Salud ha señalado que la vacuna contra el dengue es segura y que protege a miles de niños y adolescentes desde 2024, cuando comenzó a aplicarse. El Niño, una amenaza latente Es inminente y hasta sobreentendido que el fenómeno El Niño, proyectado para noviembre de 2026 y los primeros meses de 2027, será intenso y afectará de manera directa a nuestro país. Y aunque hoy ya parece que estamos tarde para cualquier medida de prevención, todo esfuerzo por contener los embates de este evento climático suma. Como ocurrió con el Niño Costero en 2017 o el ciclón Yaku en 2023, los fenómenos climáticos afectan a varias regiones del Perú: la costa norte, la selva central y también la capital. Es allí donde aparecen enfermedades endémicas como el dengue, la leptospirosis y otras. En las proyecciones, el director del CDC del Ministerio de Salud, César Munayco, señala que el peor escenario es que se presenten epidemias como las ocurridas en 2023 y 2024. En ambos años se registraron más de 250 mil casos anuales de dengue y la cifra de fallecidos llegó a 444 en 2023 y a 261 en 2024. Las regiones más afectadas en esa época fueron Piura, Lambayeque, La Libertad y Lima. En este 2026, todo es atípico. Normalmente, el dengue es una enfermedad con un comportamiento estacional, pero este año, debido al fenómeno El Niño, “hemos empezado muy temprano con los casos. El zancudo se vuelve más eficiente en transmitir la enfermedad. Y el dengue, como la temperatura permanece más tiempo elevada, hace que el riesgo sea mucho mayor y haya más casos, como ahora”, indicó Munayco. Una inminente crisis sanitaria La Organización Panamericana de la Salud (OPS), en sus previsiones, ha pedido al personal médico peruano calcular que el 4,5% de la población podría enfermarse de dengue. Luego habría que distinguir entre los tipos de esta enfermedad: hay casos en los que ni siquiera se presentan signos de alarma y el paciente puede ser atendido en su casa sin ningún problema, pero hay otros en los que puede requerir hospitalización o ser trasladado a una unidad de cuidados intensivos (UCI). Allí es donde entra a tallar qué tan listo está el sistema sanitario para un escenario como este. ¿Cuántas camas, médicos, personal de enfermería, técnicos y medicamentos se necesitan de acuerdo con la condición del paciente? En 2023 se vivió un escenario como ese y hay situaciones que no deberían repetirse, sobre todo por las limitaciones que mostró la respuesta del sistema de salud ante aquella crisis. “Los esfuerzos del sistema de salud están enfocados en reducir la mortalidad”, señala César Munayco. “Lamentablemente, los casos va a ser bien complicado reducirlos, porque se requiere a un ejército de personas para abordar ese tema”, añadió. Además, el médico hizo una comparación de cómo afectó el dengue al país en 2023 y 2024: “Si bien en el 2024 hubo más casos, el número de fallecidos se redujo. Esto porque se intervino en capacitación al personal, enviando infectólogos con experiencia a las zonas nuevas en ser afectadas, como Ica y Áncash”. Lo importante es que la población que detecte signos de alarma pueda acudir rápidamente a los servicios de salud. Aquí, cada minuto cuenta. No hay primera sin segunda La vacuna contra el dengue no abunda ni está disponible para todos. El Perú ha podido adquirir un lote importante de dosis debido a la exposición que tendrá ante la llegada del fenómeno El Niño. El grupo etario al que se le está administrando esta vacuna es el de personas de 10 a 20 años, por recomendación de la Organización Mundial de la Salud (OMS). Pero es más importante aún entender y dimensionar la importancia de la segunda dosis. Solo así se puede completar el esquema de inmunización contra el dengue. El intervalo entre una y otra dosis es de tres meses y, en este escenario, en el que es inminente que aumenten los contagios de dengue, vacunarse es primordial. Que el desconocimiento, el miedo o la incertidumbre por los posibles efectos de una vacuna no pongan en duda su efectividad. El Ministerio de Salud debe reforzar los puntos de vacunación, preparar más brigadas y llegar cada vez a más lugares y a más personas que puedan ser inmunizadas. Hasta aquí, la estrategia de vacunación no ha funcionado, pero aún hay tiempo de enmendar y corregir lo que no se está haciendo bien. Solo en este año, hay más de 70 muertes por dengue. Está en manos de los responsables del sector Salud evitar que esta cifra aumente de manera trágica. IMPORTANTE En Lima, el ministerio de Salud es el que lidera la aplicación de la vacuna contra el dengue a los residentes del distrito de San Juan de Lurigancho. Para recibir la primera o segunda dosis, se debe acudir a los centros de salud del Minsa en SJL, presentar el documento que acredite la edad entre 10 y 20 años y que residen en el distrito. En los colegios, los menores deberán presentar un consentimiento firmado por el padre, madre o apoderado. El Ministerio de Salud informará sobre cualquir zona nueva de intervencióny establecimientos que colocarán la vacuna. Mientras que en EsSalud pueden acudir al vacunatorio Playa Miller, para inmunizarse contra otras enfermedades infecciosas, como la fiebre amarilla.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/lima/sucesos/solo-el-27-de-la-poblacion-en-riesgo-recibio-las-dos-dosis-de-la-vacuna-contra-el-dengue-apuesplan-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Lluvias en el norte del Perú: noticias de precipitaciones en Piura, Tumbes y Trujillo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/peru/piura-y-el-norte-del-peru-bajo-lluvias-intensas-ultimas-noticias-alerta-por-el-nino-e-informe-del-coen-en-vivo-lbposting-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Piura: Producción de mango caería hasta 90% en San Lorenzo</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>La producción de mango en el valle de San Lorenzo podría desplomarse hasta en un 90 % debido a las alteraciones climáticas asociadas al Fenómeno El Niño (FEN). Así lo advirtió Miguel Castillo Vera, presidente de la Junta de Usuarios de San Lorenzo, quien señaló que las elevadas temperaturas registradas durante los últimos meses han perjudicado la floración de este cultivo, considerado uno de los principales motores económicos del valle piurano. El dirigente explicó que una hectárea de mango, que normalmente produce entre 3 mil y 5 mil jabas, podría rendir apenas entre 50 y 100 durante la presente campaña. “El impacto ya lo tenemos, ya lo vivimos», expresó Castillo Vera, al señalar que los agricultores han realizado inversiones para estimular la floración, pero sin obtener los resultados esperados para la presente campaña de la fruta.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-produccion-de-mango-caeria-hasta-90-en-san-lorenzo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Piura: Paralización de puente deja indefensa a población en Cura Mori</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Los pobladores del caserío Santa Rosa se encuentran en constante estado de preocupación ante la paralización de la obra del puente de ingreso a su localidad. PUEDES LEER ► A la cárcel dos sujetos por ultrajar a menores: sentenciados a 20 y 35 años de prisión Esta infraestructura es la principal vía de tránsito y evacuación frente a probables precipitaciones pluviales o la amenaza del fenómeno El Niño. La suspensión de los trabajos responde a la necesidad de modificar el expediente técnico y corregir el diseño inicial. El presidente de la Comisión de Regantes de Puyuntala, Óscar Huidobro Castillo, explicó que el puente debe quedar entre 40 y 50 centímetros por encima del nivel de la pista. Esta readecuación técnica es indispensable para evitar que el caudal del canal, cargado de maleza, residuos sólidos y animales muertos, cause severos taponamientos y desbordes hacia el sector Pedregal. Actualmente, la comisión debe desembolsar 1,000 soles mensuales para contratar personal que retire manualmente la basura de la zona. Atendiendo las demandas de vecinos y transportistas, la dirigencia acordó también desplazar la ubicación del puente unos metros aguas arriba, evitando así comprometer la caseta de agua potable existente y prevenir accidentes. Ante la ausencia de un desvío oficial acondicionado por las autoridades, Huidobro facilitó maquinaria de su propiedad para habilitar provisionalmente un camino de servicio. Respecto al estancamiento de los trabajos, el dirigente aclaró que la oficina del Programa Subsectorial de Irrigaciones (PSI) en Piura funciona como mesa de partes, mientras que la aprobación final depende de Lima.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/piura-paralizacion-de-puente-deja-indefensa-a-poblacion-en-cura-mori/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Piura: desarrollan campaña de atención en diversas especialidades en hospital Cayetano</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Esto se realizará hasta el 31 de octubre, a través de la estrategia Hospital Perú de la Gerencia de Oferta Flexible de Essalud, se informó.
 Esta jornada incluye consultas en medicina familiar, medicina interna, medicina general, ginecología, oftalmología, otorrinolaringología, odontología y psicología.
@@ -836,79 +918,153 @@
 En este contexto, y ante la inminente presencia del Fenómeno El Niño, se fortalecerá la inmunización a través de brigadas itinerantes, más puntos de vacunación y monitoreo de los avances para cerrar las brechas en la región.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-piura-desarrollan-campana-atencion-diversas-especialidades-hospital-cayetano-1097313.aspx</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Piura: instalan sistema de bombeo en Las Azucenas para acelerar la evacuación de aguas pluviales</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>La Municipalidad Provincial de Piura (MPP) puso en funcionamiento un sistema provisional de bombeo en la cuenca ciega de Las Azucenas, con el objetivo de reducir la acumulación de aguas pluviales durante las lluvias. Esta zona recibe el agua que proviene de los sectores de Avifap e Ignacio Merino, lo que incrementa el riesgo de aniegos cuando se registran precipitaciones intensas. Anteriormente, el agua acumulada podía alcanzar hasta la cintura de una persona y su retiro requería aproximadamente 120 cisternadas, un procedimiento que demandaba varias horas. Con la nueva instalación, la comuna busca agilizar los trabajos de evacuación y disminuir las afectaciones a los vecinos. Dos motobombas permitirán evacuar el agua El sistema está compuesto por un buzón de captación y dos motobombas proporcionadas por el Ministerio de Vivienda, Construcción y Saneamiento. Ambos equipos tienen una capacidad conjunta de evacuación de 200 litros por segundo y permitirán conducir las aguas hacia el SARE Ignacio Merino. El gerente de Desarrollo Territorial, Pedro Ruiz, explicó que también se entregó un manual para garantizar el manejo adecuado de los equipos. Además, se colocaron tuberías de PVC en distintos cruces de vías para facilitar el desplazamiento del agua hacia los puntos de captación. El funcionario precisó que se trata de una solución provisional que permitirá reducir los efectos de las inundaciones. Para el funcionamiento del sistema, se mantendrá una lámina de agua de entre 15 y 20 centímetros que facilite el bombeo. Asimismo, señaló que la operatividad del SARE Ignacio Merino será fundamental para completar la evacuación. Municipalidad pide evitar arrojar basura en las calles Ruiz exhortó a los vecinos a no arrojar residuos en la vía pública, debido a que la basura puede acumularse en las rejillas de captación, bloquear el paso del agua y afectar el funcionamiento de las motobombas. Por su parte, los residentes de Las Azucenas agradecieron la intervención municipal y destacaron las acciones impulsadas por el alcalde Juan Francisco Cevallos para atender los problemas que enfrenta el sector durante la temporada de lluvias.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-instalan-sistema-de-bombeo-en-las-azucenas-para-acelerar-la-evacuacion-de-aguas-pluviales/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Escolares peruanos presentan 172 inventos en el concurso “Inventores del Futuro" 2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Los inventos peruanos presentados por los estudiantes abordan desafíos socioambientales y tecnológicos cruciales, distribuidas a lo largo de nueve áreas temáticas principales.
+El área de mayor concentración corresponde al cuidado del medioambiente y la ecoeficiencia , sector que agrupa al 24 % del total de las invenciones registrada s.
+Dentro de este eje destacan proyectos focalizados en procesos de reciclaje, el aprovechamiento integral de residuos orgánicos y técnicas avanzadas para el tratamiento de agua, incluyendo desarrollos como bioplásticos e insumos biodegradables.
+A esta prioridad ambiental le siguen las energías renovables , con un 11 % de los proyectos orientados al diseño de sistemas solares, biodigestores y la obtención de biocombustibles.
+Por su parte, la agricultura sostenible concentra un 10 % de las iniciativas mediante el desarrollo de bioinsecticidas, esquemas de riego inteligente y sistemas de alerta temprana ante heladas.
+En esa misma proporción del 10 %, la rama de nutrición y alimentos reúne propuestas técnicas diseñadas para combatir y prevenir la anemia infantil en las comunidades vulnerables.
+La atención a las necesidades sanitarias y de seguridad ciudadana también tiene un protagonismo destacado en el certamen.
+Las invenciones dedicadas a la salud y la medicina abarcan el 9 % de las postulaciones , mientras que la prevención de riesgos concentra un 8 % a través de prototipos de sismógrafos, detectores de fugas de gas y sistemas de alerta previa ante la ocurrencia de huaicos.
+Asimismo, el rubro de educación y tecnologías digitales representa el 8 % de los trabajos, seguido por la construcción sostenible con un 5 % y el desarrollo de tecnologías de inclusión para personas con discapacidad con un 5 %.
+El concurso refleja una amplia representatividad geográfica y demográfica, convocando a un total de 381 estudiantes de diversas regiones del país .
+El certamen destaca por una destacada presencia femenina, donde el 56 % del total de participantes son alumnas inventoras.
+La estructura organizativa de los proyectos muestra que el 74 % de las invenciones fueron elaboradas mediante equipos colaborativos de hasta tres integrantes, en tanto que el 26 % restante optó por postulaciones de carácter individual.
+La capital concentra el mayor volumen con un 26 % de los proyectos provenientes de Lima, seguida por la región Piura con el 12 %, la Provincia Constitucional del Callao con el 9 % y la región La Libertad con el 8 %.
+El proceso de inscripción y juzamiento ha sido estructurado en dos categorías educativas según el nivel escolar: la Primera Categoría comprende a estudiantes desde el cuarto grado de primaria hasta el primer año de secundaria, mientras que la Segunda Categoría abarca a los alumnos matriculados entre el segundo y el quinto año de educación secundaria.
+Del 8 al 30 de octubre, el comité técnico examina detalladamente la totalidad de los proyectos inscritos bajo tres criterios fundamentales: la novedad de la invención a nivel mundial, las ventajas técnicas demostradas frente a las soluciones ya existentes en el mercado o en la literatura científica, y la efectividad del invento para resolver problemas concretos o atender necesidades sociales desatendidas.
+Como resultado de esta etapa de evaluación inicial, se seleccionará un máximo de cinco finalistas por cada una de las dos categorías competitivas.
+Los escolares cuyos proyectos resulten seleccionados como finalistas ingresarán a la etapa de sustentación, la cual se desarrollará del 5 al 16 de noviembre.
+Durante este periodo, los equipos deberán elaborar un video explicativo detallado y realizar la defensa oral de su invento ante un jurado calificador especializado.
+El proceso culminará con la ceremonia oficial de premiación programada para el 26 de noviembre de 2026.
+Los galardones previstos para el concurso se otorgan en alianza y con la colaboración de la Universidad Peruana Unión (UPeU).
+Cada uno de los escolares ganadores y sus respectivos docentes asesores recibirán una tablet y un diploma de honor; del mismo modo, las instituciones educativas a las que representan serán reconocidas oficialmente mediante la entrega de un trofeo institucional y un diploma de distinción.
+Toda la información correspondiente a las bases del concurso, cronogramas y requerimientos adicionales se encuentra disponible a través del portal web oficial del Indecopi.
+Revisa más noticias sobre ciencia, tecnología e innovación en la Agencia Andina y escucha historias inspiradoras en Andina Podcast.
+Más en Andina: ???? ¡Descarga en Google Play la renovada app de Andina! https://t.co/tsQ0Psvp80 ?? Integra videos, podcasts informativos y otros contenidos multimedia ??? Funciones extra: lectura en voz alta, búsqueda por voz, modo oscuro y más.
+¡Ya disponible! pic.twitter.com/lgWCtjpdSk (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) January 26, 2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-escolares-peruanos-presentan-172-inventos-el-concurso-inventores-del-futuro-2026-1097330.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>El Comercio</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Piura podría enfrentar lluvias más fuertes y sigue sin drenaje pluvial: ¿cómo funciona y por qué la obra lleva 10 años pendiente?</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Piura corre el riesgo de quedar inundada ante las fuertes lluvias que podrían registrarse en las próximas semanas por el Fenómeno El Niño. La región aún no cuenta con un sistema integral de drenaje pluvial, pese a que el proyecto fue planteado hace casi 10 años. El riesgo de no contar con una red de drenaje pluvial quedó en evidencia hace unos días, cuando las lluvias registradas entre el 19 y 20 de octubre afectaron al menos nueve puntos de Piura, pese a que las precipitaciones alcanzaron entre 6 y 7 milímetros. Días antes, el 24 de septiembre, lluvias inusuales en varias ciudades de la región ya habían encendido las alertas sobre lo que podría ocurrir en las próximas semanas. Los sistemas de drenaje pluvial que debían implementarse en localidades de Piura como Piura ciudad, Catacaos, Castilla, 26 de Octubre, Paita y Sullana no se han concretado debido a que recién se encuentran en fase de diseño, indicó el periodista Ralph Zapata, director del portal Norte Sostenible. “Hasta el momento no hay drenaje que esté listo, no está construido ninguno, casi todos están en diseño. En Piura se iban a elaborar los drenajes de Piura ciudad, Catacaos, Castilla, 26 de Octubre, Paita, Sullana y Talara”, señaló Zapata. “En Sullana, el proyecto está bien retrasado, al igual que en Piura, ya que solo están en diseño. En Catacaos, Castilla y 26 de Octubre no hay nada, por eso la ciudades se inundan cada vez que llueve”, agregó. Explicó que las autoridades solo han avanzado en drenaje pluvial de Talara, el cual ha sido ejecutado por etapas, pero que aún no se concluye el proyecto integral. Zapata indicó que la construcción de drenajes pluviales se incluyó en el plan integral de la Autoridad para la Reconstrucción con Cambios (ARCC), tras el impacto del Fenómeno El Niño de 2017, ya que causó inundaciones en varias regiones del norte del país. Sin embargo, el proyecto luego a la Autoridad Nacional de Infraestructura (ANIN), pero sin mayores avances porque, según dijo, se le ha recortado el presupuesto y por la poca capacidad económica de las empresas que participan en las licitaciones de Talara y Sullana, lo que ha conllevado a incumplimiento de contratos y de cronogramas, incluso los casos se han resueltos en arbitrajes. “En el 2017 Piura se inundó porque hubo mucha lluvia y porque se desbordó el río. Si llueve en estos días, ocurrirá lo mismo. La ciudad se inundará porque no tiene drenaje, no tiene salida (el agua de la lluvia), hay cuencas ciegas, que son depresiones donde se empoza el agua y solo se puede sacar con motobombas. Las ciudades del norte son vulnerables por la falta de drenaje”, refirió. Si bien el plan integral de un drenaje pluvial para Piura no se ejecuta, el Gobierno Regional de Piura ha desarrollado un drenaje pluvial solo para el Centro Histórico de la ciudad norteña, que incluye la Plaza de Armas y calles aledañas, pero la iniciativa ha tenido retrasos, pues debería estar culminado para mediados de este año, sin embargo, se ha pospuesto para junio del 2027. Las recientes lluvias generaron que el agua se empozara en las zanjas abiertas de dicha obra. “El proyecto ha sido cuestionado por vecinos porque ha perjudicado a negocios y debió ser terminado a mediados de este año, pero se ha retrasado por diversas interferencias”, aseveró. Por otra parte, Zapata remarcó que en otras ciudades del norte del país, como Tumbes, Trujillo y Chiclayo, tampoco se ha terminado de construir obras de drenaje pluvial, situación que las coloca, según advirtió, en situación de vulnerabilidad. El diputado Eduardo Castillo, representante de Piura, cuestionó que el proyecto de drenaje pluvial en la región norteña no cuenta con expediente técnico y que la ejecución recién comenzaría, de acuerdo con lo informado por la ANIN, en el 2028. Resaltó que el Gobierno haya aumentado la capacidad del río Piura tras descolmatarlo en varios puntos. “Lamentablemente, el expediente técnico del drenaje pluvial a cargo de ANIN se encuentra en 0%. Lo único que tenemos es un perfil ya terminado al 100%, colgado en el Banco de Inversiones y que arroja que EL proyecto de Piura no tiene expediente técnico”, afirmó Castillo a El Comercio. Explicó que el proyecto se encuentra a cargo del ANIN debido a que el monto de la inversión supera los mil millones de soles. En ese contexto, señaló que la obra en su conjunto demandará una inversión de 7 mil millones de soles, por lo que, según le informó dicha entidad, le corresponde al Ministerio de Economía y Finanzas (MEF) gestionar un préstamo ante el Banco Interamericano de Desarrollo (BID). Remarcó que actualmente en las localidades de Talara y Sullana solo hay un avance de obra física del drenaje pluvial del 10% y 7%, respectivamente, pese a que se trata de las zonas, junto a Piura, más vulnerables de la región norteña. Advirtió que la ciudad de Piura terminó inundada hace unos días con una lluvia de 7 milímetros y que las motobombas de las autoridades regionales y locales no estaban operativas, por lo que la situación sería peor, ya que se espera precipitaciones de 50 milímetros hasta diciembre del 2026, para luego pasar a lluvias fuertes de 150 milímetros en enero y febrero del próximo año. Remarcó que la iniciativa para darle solución a la vulnerabilidad de Piura contempla, además de los drenajes pluviales, la implementación de una salida al mar del río Piura. “No sirve tener un drenaje pluvial si la caja hidráulica del río Piura solamente aguantará 4 mil metros cúbicos”, afirmó. A la falta de un drenaje pluvial en Piura, se suma un problema más: las denominadas cuencas ciegas, donde se acumula el agua de las lluvias pero que no cuenta con una salida natural hacia un dren, río o canal. Ante ello, el director de Seguridad y Defensa Nacional del Ministerio de Vivienda, Renato Ameri, indicó que se han desplegado 26 motobombas de gran capacidad para evacuar el agua en la región norteña. “Las cuencas ciegas son aquellos lugares donde se almacena el agua y no tienen una descarga natural. Por la topología de Piura, existen depresiones que no tienen salida”, refirió. “Como no tienen una salida natural a un río, dren, un canal hay que evacuar las aguas, por lo que el MVCS ha distribuido maquinaria de alta potencia, como motobombas de ocho y seis pulgadas, que evacúan aguas entre 100 y 120 litros por segundo”, agregó.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://elcomercio.pe/lima/sucesos/piura-podria-enfrentar-lluvias-mas-fuertes-y-sigue-sin-drenaje-pluvial-por-que-la-obra-lleva-10-anos-pendiente-apuesplan-noticia/</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Piura: ANA inicia trabajos de descolmatación en río Piura en Curamori ante El Niño</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>La intervención busca mejorar las condiciones del cauce y preparar la zona ante posibles crecidas del río durante la temporada de lluvias, como parte de las acciones que impulsa el Gobierno para fortalecer la capacidad de respuesta de la población y proteger sus medios de vida frente al Fenómeno El Niño.
 Estas acciones forman parte de los esfuerzos del sector Agricultura para fortalecer la preparación ante el Fenómeno El Niño y avanzar en la ejecución de trabajos que contribuyan a reducir la vulnerabilidad de las zonas expuestas a inundaciones.
 La ANA continuará con el seguimiento de las labores para verificar el avance de la intervención y contribuir a una adecuada gestión de los recursos hídricos, en beneficio de las familias de Curamori y de la población de la región Piura.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-piura-ana-inicia-trabajos-descolmatacion-rio-piura-curamori-ante-nino-1097211.aspx</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Piura: Vivienda otorga certificación ambiental para proyecto de 105 asentamientos humanos</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Mediante la Resolución Directoral N.° 116-2026-VIVIENDA/VMCS-DGAA, esta aprobación otorga la certificación ambiental al proyecto del Programa Nacional de Saneamiento Urbano (PNSU), con lo que se da un paso fundamental para avanzar hacia su ejecución con criterios de sostenibilidad y adecuada gestión ambiental.
 El proyecto beneficiará a 105 asentamientos humanos de Piura, Castilla y Veintiséis de Octubre con servicios básicos de calidad, contribuyendo a reducir las brechas de saneamiento y mejorar la calidad de vida de la población.
@@ -916,59 +1072,27 @@
 De esta manera, el Ministerio de Vivienda reafirma su compromiso de impulsar la infraestructura de saneamiento sostenible, la protección del ambiente y el acceso a agua potable y saneamiento de calidad para más familias del norte del país.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-piura-vivienda-otorga-certificacion-ambiental-para-proyecto-105-asentamientos-humanos-1097218.aspx</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fenómeno El Niño: EsSalud vacuna a escolares de Piura ante el dengue y otras enfermedades</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>La actividad, desarrollada por la Red Asistencial Piura de EsSalud , en coordinación con la Dirección Regional de Salud (Diresa) Piura y el sector Educación, permitió acercar los servicios de inmunización a la comunidad educativa y promover la prevención desde las aulas.
-Durante la jornada se administraron vacunas contra el dengue, el virus del papiloma humano (VPH) y la influenza , de acuerdo con las edades, indicaciones y esquemas de vacunación correspondientes.
-Prevención ante la temporada de lluvias Las lluvias intensas y la acumulación de agua pueden favorecer la proliferación del mosquito Aedes aegypti , transmisor del dengue, por lo que resulta fundamental fortalecer las medidas preventivas y la protección de la población.
-En ese contexto, el gerente de la Red Asistencial Piura de EsSalud, Dr.
-José Augusto Albines Trelles, destacó la importancia de llevar los servicios de salud a los colegios y fortalecer el trabajo conjunto entre instituciones para proteger oportunamente a la población infantil.
-Asimismo, recordó que la vacunación debe complementarse con medidas de prevención en los hogares, como eliminar recipientes que acumulen agua, mantener tapados los depósitos y evitar la formación de criaderos de mosquitos.
-Trabajo articulado para proteger a las escolares La jornada fue organizada por la Estrategia de Inmunizaciones y Cadena de Frío de EsSalud Piura, que cuenta con un almacén especializado para garantizar la adecuada conservación de las vacunas y respaldar las campañas de inmunización programadas.
-Con estas acciones, EsSalud reafirma su compromiso de acercar los servicios preventivos a la población, promover la vacunación oportuna y fortalecer el trabajo articulado para proteger la salud de las niñas y sus familias.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-fenomeno-nino-essalud-vacuna-a-escolares-piura-ante-dengue-y-otras-enfermedades-1097232.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>¿Qué hace un gestor cultural y dónde puede trabajar? Aquí cinco sectores a tomar en cuenta</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Un gestor cultural puede diseñar proyectos, administrar recursos, coordinar equipos y establecer alianzas entre instituciones, artistas, empresas y comunidades.
 Su trabajo consiste en desarrollar iniciativas que permitan promover la cultura, preservar el patrimonio y facilitar el acceso de las personas a diversas expresiones culturales.
@@ -1001,27 +1125,27 @@
 Más en Andina: ??Ciberseguridad se convierte en barrera clave para crecimiento digital de las pymes https://t.co/LFbfWVPgc0 https://t.co/pxUCVZihZo (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 24, 2026</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-que-hace-un-gestor-cultural-y-donde-puede-trabajar-aqui-cinco-sectores-a-tomar-cuenta-1097233.aspx</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Conadis reconoce a Pensión 65 por mejorar la salud visual de 483 000 adultos mayores</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>La distinción se otorgó en el marco del Concurso de Buenas Prácticas de Gestión Inclusiva 2026 “Inclusión y Discapacidad” , que reconoce experiencias innovadoras y sostenibles orientadas a eliminar barreras y promover la inclusión de las personas con discapacidad.
 En la categoría Salud, Pensión 65 obtuvo el segundo puesto gracias a esta iniciativa, que, hasta julio de 2026, permitió atender a más de 483 300 adultos mayores con presbicia, mediante tamizajes visuales y la entrega gratuita de lentes para ver de cerca y lentes de sol.
@@ -1033,27 +1157,27 @@
 Esta iniciativa se desarrolla con el apoyo de la organización no gubernamental MSH-Perú, en el marco de un convenio de cooperación vigente.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-conadis-reconoce-a-pension-65-mejorar-salud-visual-483-000-adultos-mayores-1097253.aspx</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>46319</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Piura: Angola busca fortalecer lazos culturales con la comunidad afroperuana de Yapatera</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>La delegación, encabezada por el agregado cultural adjunto de Angola, Luandino Alves de Carvalho, conoció el patrimonio histórico de Yapatera mediante visitas a la ex fábrica de azúcar y al Museo Afroperuano.
 También participó en presentaciones de cumananas, muestras de gastronomía tradicional y demostraciones de artesanía local.
@@ -1063,116 +1187,16 @@
 La visita buscó impulsar el intercambio de conocimientos y contribuir a la valoración de la identidad cultural de Yapatera.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-piura-angola-busca-fortalecer-lazos-culturales-con-comunidad-afroperuana-yapatera-1097200.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Neyra pide labor articulada ante emergencia por El Niño</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>El gobernador Luis Neyra León reafirmó que su gestión continuará apoyando las acciones de respuesta ante las lluvias y promoviendo el trabajo coordinado entre instituciones para atender las zonas afectadas. “Aquí no se trata de echarse la culpa, se trata de poner el hombro para sacar adelante esta emergencia”, manifestó Neyra, al señalar que la atención de las precipitaciones requiere la participación articulada de los gobiernos locales, regional y nacional. Precisó que la operación de los sistemas de drenaje pluvial corresponde al Ministerio de Vivienda, la Municipalidad de Piura y la Municipalidad de Castilla, de acuerdo con sus respectivas competencias. No obstante, aseguró que continuará brindando apoyo</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/neyra-pide-labor-articulada-ante-emergencia-por-el-nino/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Desvío de río por Sechura afectaría drenaje pluvial, asegura especialista</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>El ingeniero Neptalí Saavedra Ruiz informó que desviar el río Piura por Sechura siguiendo la ruta del río Loco, dren 1308 y dren Sechura, no solo inundaría varios centros poblados, sino también afectaría el drenaje pluvial de toda la ciudad capital. Destacó que existen varios sistemas de drenaje que culminan en el dren Sechura, en especial el canal vía que empieza en la Av. Bayóvar y recoge agua de lluvia de un gran sector de la urbe. “Si esto (dren Sechura) se convierte en río el tirante hidráulico de estas zonas va a aumentar y el agua que ingresa por gravedad ya no va a poder salir y podría haber un efecto contrario. Probablemente, el agua de todos los drenes va a ingresar a la ciudad”, sostuvo en una exposición en la Municipalidad de Sechura. En ese sentido, consideró que la mejor opción es continuar con la salida del río por Chutuque rumbo hacia Reventazón.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/desvio-de-rio-por-sechura-afectaria-drenaje-pluvial-asegura-especialista/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Reconteo de votos en Bigote define pase a la segunda vuelta</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>La Oficina Nacional de Procesos Electorales (ONPE) acabó ayer de contar las actas observadas de la elección regional, quedando pendientes las 23 actas del distrito de San Juan de Bigote. Al 99.56% de los resultados, el candidato a gobernador de Podemos, Guillermo La Torre logró 178 mil 702 votos y el postulante de Somos Perú, Santiago Paz, llegó a 177 mil 545 votos. De esta manera, la diferencia entre ambos aspirantes a gobernador quedó en 1 mil 157 votos. No hay reconteo Sin embargo, el camino para definir quién pasa a la segunda vuelta con Reynaldo Hilbck (APP) es todavía complicado Según el abogado de Alianza para el Progreso (APP), Juan Carlos Álamo, ayer se inició recién la apertura de cajas lacradas con el material que la Fiscalía recuperó de las mesas del colegio José Carlos Mariátegui, luego de los hechos de violencia del 4 de octubre. Tras la resolución de Jurado Nacional de Elecciones (JNE), el abogado explica que se trata de una primera etapa de visualización del estado del material, sin que aún se autorice el reconteo. Precisamente, ayer entre las 9:00 am y pasadas las 3:00 pm solo se había visualizado el contenido de tres cajas de igual número de mesas de sufragio. En la mesa 071823 se contabilizaron 202 cédulas marcadas, 85 cédulas no usadas y 28 actas. En la caja de la mesa 071824 se hallaron 230 cédulas marcadas y 27 actas. La apertura de cajas con los “restos electorales” estuvo a cargo de la Oficina Descentralizada de Procesos Electorales (ODPE) de Morropón. Hubo presencia de personeros, fiscalizadores del JNE y fiscalía. Una vez revisados, se armaron cajas solo con cédulas por cada mesa. Este material será enviado al JEE Morropón. ¿Son auténticas? Sobre el tema, el abogado Álamo explicó que el reconteo de votos no será inmediato como se piensa. Señala que el JEE Morropón puede solicitar informes y hacer indagaciones para determinar si hubo garantía o no de que no se haya manipulado el material electoral antes de ser lacrado por Fiscalía. “El JNE señala que se debe aperturar todas las actuaciones necesarias para saber si el material electoral tiene la autenticidad, integridad y trazabilidad de los documentos”, comentó Álamo. En base a esas indagaciones se determinará si esas cédulas se podrán utilizar en el reconteo. “El JEE va a tener que solicitar informes sobre cómo se ha realizado el cuidado del material. Se puede indagar sobre qué pasó con el material antes de la intervención de la Fiscalía. Se puede valer de registros audividuales, de los informes de la Policía y Fuerzas Armadas. Con todo esto, tomará la decisión”, expresó.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/reconteo-de-votos-en-bigote-define-pase-a-la-segunda-vuelta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>46319</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Diputado Castillo pide que gobernador rinda cuentas en comisión de Congreso</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>El diputado Eduardo Castillo solicitó a la Comisión de Modernización de la Gestión del Estado y Contraloría del Congreso, que cite al gobernador Luis Neyra Léon para que explique qué labores de mitigación hizo ante el anunciado fenómeno El Niño. “Hasta ahora no puede nombrar un solo trabajo de mitigación o de prevención desde que inició el año hasta el día de hoy. No lo digo yo, sino que lo dice la Contraloría en dos informes que he pedido. El gerente de Contraloría nos informa que el 20%, que pudo gastar para temas de prevención sí los gastó, pero no en prevención. Es importante que el gobernador, antes de que se vaya a su casas, de respuesta”, dijo. Resaltó que Neyra como primer ciudadano de la región tiene que dar explicaciones sobre el gasto hecho en prevención y de sus acciones como cabeza de la plataforma regional de Defensa Civil. “Queremos saber si ha solicitado algún requerimiento [de presupuesto] en el estado de emergencia”, manifestó Castillo. Recordó que hasta antes del ingreso de la presidenta Keiko Fujimori no había trabajos de descolmatación en el río Piura. “Antes del ingreso de la señora presidenta no se movió un solo metro cúbico de arena del río cuando es nuestro principal riesgo en la ciudad. En febrero llevé a los técnicos [del ANA y Senamhi] y se sabía que se tenían las características de un fenómeno El Niño. ¿En qué se preocupó el gobernador desde ese día hasta el día de hoy?, criticó el parlamentario de Fuerza Popular por la región Piura.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/diputado-castillo-pide-que-gobernador-rinda-cuentas-en-comision-de-congreso/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -1180,17 +1204,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piura: ANA inicia trabajos de descolmatación en río Piura en Curamori ante El Niño</t>
+          <t>Fenómeno El Niño: EsSalud vacuna a escolares de Piura ante el dengue y otras enfermedades</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>La Autoridad Nacional del Agua (ANA) inició el 20 de octubre los trabajos de limpieza, descolmatación y conformación de bordo con material propio del cauce del río Piura, en el sector Chato Chico, distrito de Curamori, provincia y departamento de Piura. La intervención busca mejorar las condiciones del cauce y preparar la zona ante posibles crecidas del río durante la temporada de lluvias, como parte de las acciones que impulsa el Gobierno para fortalecer la capacidad de respuesta de la población y proteger sus medios de vida frente al Fenómeno El Niño. Estas acciones forman parte de los esfuerzos del sector Agricultura para fortalecer la preparación ante el Fenómeno El Niño y avanzar en la ejecución de trabajos que contribuyan a reducir la vulnerabilidad de las zonas expuestas a inundaciones. La ANA continuará con el seguimiento de las labores para verificar el avance de la intervención y contribuir a una adecuada gestión de los recursos hídricos, en beneficio de las familias de Curamori y de la población de la región Piura.</t>
+          <t>La actividad, desarrollada por la Red Asistencial Piura de EsSalud , en coordinación con la Dirección Regional de Salud (Diresa) Piura y el sector Educación, permitió acercar los servicios de inmunización a la comunidad educativa y promover la prevención desde las aulas.
+Durante la jornada se administraron vacunas contra el dengue, el virus del papiloma humano (VPH) y la influenza , de acuerdo con las edades, indicaciones y esquemas de vacunación correspondientes.
+Prevención ante la temporada de lluvias Las lluvias intensas y la acumulación de agua pueden favorecer la proliferación del mosquito Aedes aegypti , transmisor del dengue, por lo que resulta fundamental fortalecer las medidas preventivas y la protección de la población.
+En ese contexto, el gerente de la Red Asistencial Piura de EsSalud, Dr.
+José Augusto Albines Trelles, destacó la importancia de llevar los servicios de salud a los colegios y fortalecer el trabajo conjunto entre instituciones para proteger oportunamente a la población infantil.
+Asimismo, recordó que la vacunación debe complementarse con medidas de prevención en los hogares, como eliminar recipientes que acumulen agua, mantener tapados los depósitos y evitar la formación de criaderos de mosquitos.
+Trabajo articulado para proteger a las escolares La jornada fue organizada por la Estrategia de Inmunizaciones y Cadena de Frío de EsSalud Piura, que cuenta con un almacén especializado para garantizar la adecuada conservación de las vacunas y respaldar las campañas de inmunización programadas.
+Con estas acciones, EsSalud reafirma su compromiso de acercar los servicios preventivos a la población, promover la vacunación oportuna y fortalecer el trabajo articulado para proteger la salud de las niñas y sus familias.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-ana-inicia-trabajos-de-descolmatacion-en-rio-piura-en-curamori-ante-el-nino/</t>
+          <t>https://andina.pe/agencia/noticia-fenomeno-nino-essalud-vacuna-a-escolares-piura-ante-dengue-y-otras-enfermedades-1097232.aspx</t>
         </is>
       </c>
     </row>
@@ -1230,17 +1261,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>El Niño: Defensoría exige parar destrucción de calles en Piura ante inicio de lluvias</t>
+          <t>Diputado Castillo pide que gobernador rinda cuentas en comisión de Congreso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>La Defensoría del Pueblo en Piura demandó a la empresa contratista a cargo de las pistas y drenaje del centro, a detener la apertura de más frentes de trabajo debido al inicio de las lluvias. “[El pedido es que] no abran más calles por las lluvias y que traten de cerrar y concluir los trabajos que se han aperturado para evitar el congestionamiento y que tampoco haya contingencia en plenas lluvias”, indicó el representante de la oficina defensorial en Piura, Walter Galecio Gonzáles. Así lo señaló luego de la reunión de trabajo que sostuvieron esta semana con funcionarios de la comuna, la empresa contratista, Fiscalía, Gobierno Regional, Policía y Senamhi. Sin embargo, el acuerdo de no abrir más calles no será definitivo, en vista que dependerá de los informes del Senamhi. “Esta decisión estará estrictamente sujeta a las recomendaciones e informes diarios que el Senamhi remita a la Municipalidad y al Gobierno Regional sobre las condiciones climáticas”, se lee en parte del acuerdo. Acuerdo Cabe indicar que no es el primer compromiso que asume la empresa contratista con las autoridades. Meses atrás se acordó que solo se abrirían más frentes de trabajo hasta el 30 de agosto, tomando en cuenta que les toma tres meses para colocar el afirmado y concluir con la pavimentación de concreto. Pese a ello, estas semanas se abrieron las calles Huancavelica e Ica. El temor es que una lluvia intensa arrastre la tierra de estas zonas y colmate el sistema de drenaje de la plazuela Tres Culturas. “No deben abrir frentes mientras esté lloviendo. Ese día [martes] en plena lluvia estaban trabajando”, destacó Galecio. Señalización De otro lado, Galecio también señaló que se debe mejorar la señalización y establecer horarios de ingreso de la maquinaria pesada para evitar el congestionamiento vehicular. “En la inspección también participó la Policía para ver el tema de la señalización y la dirección de ingreso de los vehículos. Hemos pedido ver el tema del ingreso de las mototaxi. Ya se aperturó la avenida Don Bosco y la Sullana y eso debería ayudar a que no ingresen por el centro de la ciudad”, enfatizó Galecio. De otro lado, en la reunión de autoridades también se recomendó medidas de prevención para evitar colapso de postes. En vista de ello se pidió el apuntalamiento inmediato de un poste ubicado en el cruce de la calle Tacna con Callao, que estaba en riesgo de caerse. Asimismo, se acordó reuniones semanales para evaluar los avances de las obras y nuevos riesgos que se presenten con el periodo lluvioso.</t>
+          <t>El diputado Eduardo Castillo solicitó a la Comisión de Modernización de la Gestión del Estado y Contraloría del Congreso, que cite al gobernador Luis Neyra Léon para que explique qué labores de mitigación hizo ante el anunciado fenómeno El Niño. “Hasta ahora no puede nombrar un solo trabajo de mitigación o de prevención desde que inició el año hasta el día de hoy. No lo digo yo, sino que lo dice la Contraloría en dos informes que he pedido. El gerente de Contraloría nos informa que el 20%, que pudo gastar para temas de prevención sí los gastó, pero no en prevención. Es importante que el gobernador, antes de que se vaya a su casas, de respuesta”, dijo. Resaltó que Neyra como primer ciudadano de la región tiene que dar explicaciones sobre el gasto hecho en prevención y de sus acciones como cabeza de la plataforma regional de Defensa Civil. “Queremos saber si ha solicitado algún requerimiento [de presupuesto] en el estado de emergencia”, manifestó Castillo. Recordó que hasta antes del ingreso de la presidenta Keiko Fujimori no había trabajos de descolmatación en el río Piura. “Antes del ingreso de la señora presidenta no se movió un solo metro cúbico de arena del río cuando es nuestro principal riesgo en la ciudad. En febrero llevé a los técnicos [del ANA y Senamhi] y se sabía que se tenían las características de un fenómeno El Niño. ¿En qué se preocupó el gobernador desde ese día hasta el día de hoy?, criticó el parlamentario de Fuerza Popular por la región Piura.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/defensoria-exige-parar-destruccion-de-calles-en-piura-ante-inicio-de-lluvias/</t>
+          <t>https://eltiempo.pe/local/diputado-castillo-pide-que-gobernador-rinda-cuentas-en-comision-de-congreso/</t>
         </is>
       </c>
     </row>
@@ -1251,39 +1282,189 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tenga cuidado con el uso de máscaras tóxicas en Halloween</t>
+          <t>Desvío de río por Sechura afectaría drenaje pluvial, asegura especialista</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Se acerca la tradicional fiesta de Halloween y los niños y adolescentes deben tener mucho cuidado para evitar el uso de máscaras tóxicas que podrían desencadenar alergias y males cutáneos, entre otros cuadros clínicos. Frente a este panorama, la Segunda Fiscalía de Prevención del Delito de Piura y otras autoridades realizaron un operativo multisectorial orientado a salvaguardar la vida y la salud de la población. El resultado del operativo dejó el saldo de 278 máscaras de Halloween decomisadas por la autoridad sanitaria tras verificar que no contaban con el rotulado sanitario exigido por ley INSPECCIONAN CINCO TIENDAS La fiscal provincial Berena Ballesteros Vigil, con el apoyo de la Policía Nacional, así como de inspectores de la Dirección Regional de Salud (Diresa) y de las municipalidades correspondientes, inspeccionó cinco establecimientos comerciales ubicados en los distritos de Castilla y Veintiséis de Octubre dedicados a la venta de disfraces, máscaras y accesorios alegóricos. Durante la revisión, las autoridades incautaron los productos debido a que sus empaques carecían del Registro Nacional y la Autorización Sanitaria emitidos por la Digesa, además de omitir datos clave como el nombre del importador, código de origen, advertencias de edad, medidas preventivas de uso y recomendaciones ante emergencias. EXHORTACIÓN Finalmente, la representante del Ministerio Público exhortó a los propietarios de los negocios a expender exclusivamente productos que cumplan con la normativa sanitaria vigente, recordando que la comercialización de artículos informales representa un peligro directo para la salud de los menores de edad.</t>
+          <t>El ingeniero Neptalí Saavedra Ruiz informó que desviar el río Piura por Sechura siguiendo la ruta del río Loco, dren 1308 y dren Sechura, no solo inundaría varios centros poblados, sino también afectaría el drenaje pluvial de toda la ciudad capital. Destacó que existen varios sistemas de drenaje que culminan en el dren Sechura, en especial el canal vía que empieza en la Av. Bayóvar y recoge agua de lluvia de un gran sector de la urbe. “Si esto (dren Sechura) se convierte en río el tirante hidráulico de estas zonas va a aumentar y el agua que ingresa por gravedad ya no va a poder salir y podría haber un efecto contrario. Probablemente, el agua de todos los drenes va a ingresar a la ciudad”, sostuvo en una exposición en la Municipalidad de Sechura. En ese sentido, consideró que la mejor opción es continuar con la salida del río por Chutuque rumbo hacia Reventazón.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/tenga-cuidado-con-el-uso-de-mascaras-toxicas-en-halloween/</t>
+          <t>https://eltiempo.pe/local/desvio-de-rio-por-sechura-afectaria-drenaje-pluvial-asegura-especialista/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Reconteo de votos en Bigote define pase a la segunda vuelta</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>La Oficina Nacional de Procesos Electorales (ONPE) acabó ayer de contar las actas observadas de la elección regional, quedando pendientes las 23 actas del distrito de San Juan de Bigote. Al 99.56% de los resultados, el candidato a gobernador de Podemos, Guillermo La Torre logró 178 mil 702 votos y el postulante de Somos Perú, Santiago Paz, llegó a 177 mil 545 votos. De esta manera, la diferencia entre ambos aspirantes a gobernador quedó en 1 mil 157 votos. No hay reconteo Sin embargo, el camino para definir quién pasa a la segunda vuelta con Reynaldo Hilbck (APP) es todavía complicado Según el abogado de Alianza para el Progreso (APP), Juan Carlos Álamo, ayer se inició recién la apertura de cajas lacradas con el material que la Fiscalía recuperó de las mesas del colegio José Carlos Mariátegui, luego de los hechos de violencia del 4 de octubre. Tras la resolución de Jurado Nacional de Elecciones (JNE), el abogado explica que se trata de una primera etapa de visualización del estado del material, sin que aún se autorice el reconteo. Precisamente, ayer entre las 9:00 am y pasadas las 3:00 pm solo se había visualizado el contenido de tres cajas de igual número de mesas de sufragio. En la mesa 071823 se contabilizaron 202 cédulas marcadas, 85 cédulas no usadas y 28 actas. En la caja de la mesa 071824 se hallaron 230 cédulas marcadas y 27 actas. La apertura de cajas con los “restos electorales” estuvo a cargo de la Oficina Descentralizada de Procesos Electorales (ODPE) de Morropón. Hubo presencia de personeros, fiscalizadores del JNE y fiscalía. Una vez revisados, se armaron cajas solo con cédulas por cada mesa. Este material será enviado al JEE Morropón. ¿Son auténticas? Sobre el tema, el abogado Álamo explicó que el reconteo de votos no será inmediato como se piensa. Señala que el JEE Morropón puede solicitar informes y hacer indagaciones para determinar si hubo garantía o no de que no se haya manipulado el material electoral antes de ser lacrado por Fiscalía. “El JNE señala que se debe aperturar todas las actuaciones necesarias para saber si el material electoral tiene la autenticidad, integridad y trazabilidad de los documentos”, comentó Álamo. En base a esas indagaciones se determinará si esas cédulas se podrán utilizar en el reconteo. “El JEE va a tener que solicitar informes sobre cómo se ha realizado el cuidado del material. Se puede indagar sobre qué pasó con el material antes de la intervención de la Fiscalía. Se puede valer de registros audividuales, de los informes de la Policía y Fuerzas Armadas. Con todo esto, tomará la decisión”, expresó.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/reconteo-de-votos-en-bigote-define-pase-a-la-segunda-vuelta/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>El Niño: Defensoría exige parar destrucción de calles en Piura ante inicio de lluvias</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>La Defensoría del Pueblo en Piura demandó a la empresa contratista a cargo de las pistas y drenaje del centro, a detener la apertura de más frentes de trabajo debido al inicio de las lluvias. “[El pedido es que] no abran más calles por las lluvias y que traten de cerrar y concluir los trabajos que se han aperturado para evitar el congestionamiento y que tampoco haya contingencia en plenas lluvias”, indicó el representante de la oficina defensorial en Piura, Walter Galecio Gonzáles. Así lo señaló luego de la reunión de trabajo que sostuvieron esta semana con funcionarios de la comuna, la empresa contratista, Fiscalía, Gobierno Regional, Policía y Senamhi. Sin embargo, el acuerdo de no abrir más calles no será definitivo, en vista que dependerá de los informes del Senamhi. “Esta decisión estará estrictamente sujeta a las recomendaciones e informes diarios que el Senamhi remita a la Municipalidad y al Gobierno Regional sobre las condiciones climáticas”, se lee en parte del acuerdo. Acuerdo Cabe indicar que no es el primer compromiso que asume la empresa contratista con las autoridades. Meses atrás se acordó que solo se abrirían más frentes de trabajo hasta el 30 de agosto, tomando en cuenta que les toma tres meses para colocar el afirmado y concluir con la pavimentación de concreto. Pese a ello, estas semanas se abrieron las calles Huancavelica e Ica. El temor es que una lluvia intensa arrastre la tierra de estas zonas y colmate el sistema de drenaje de la plazuela Tres Culturas. “No deben abrir frentes mientras esté lloviendo. Ese día [martes] en plena lluvia estaban trabajando”, destacó Galecio. Señalización De otro lado, Galecio también señaló que se debe mejorar la señalización y establecer horarios de ingreso de la maquinaria pesada para evitar el congestionamiento vehicular. “En la inspección también participó la Policía para ver el tema de la señalización y la dirección de ingreso de los vehículos. Hemos pedido ver el tema del ingreso de las mototaxi. Ya se aperturó la avenida Don Bosco y la Sullana y eso debería ayudar a que no ingresen por el centro de la ciudad”, enfatizó Galecio. De otro lado, en la reunión de autoridades también se recomendó medidas de prevención para evitar colapso de postes. En vista de ello se pidió el apuntalamiento inmediato de un poste ubicado en el cruce de la calle Tacna con Callao, que estaba en riesgo de caerse. Asimismo, se acordó reuniones semanales para evaluar los avances de las obras y nuevos riesgos que se presenten con el periodo lluvioso.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/defensoria-exige-parar-destruccion-de-calles-en-piura-ante-inicio-de-lluvias/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Piura: ANA inicia trabajos de descolmatación en río Piura en Curamori ante El Niño</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>La Autoridad Nacional del Agua (ANA) inició el 20 de octubre los trabajos de limpieza, descolmatación y conformación de bordo con material propio del cauce del río Piura, en el sector Chato Chico, distrito de Curamori, provincia y departamento de Piura. La intervención busca mejorar las condiciones del cauce y preparar la zona ante posibles crecidas del río durante la temporada de lluvias, como parte de las acciones que impulsa el Gobierno para fortalecer la capacidad de respuesta de la población y proteger sus medios de vida frente al Fenómeno El Niño. Estas acciones forman parte de los esfuerzos del sector Agricultura para fortalecer la preparación ante el Fenómeno El Niño y avanzar en la ejecución de trabajos que contribuyan a reducir la vulnerabilidad de las zonas expuestas a inundaciones. La ANA continuará con el seguimiento de las labores para verificar el avance de la intervención y contribuir a una adecuada gestión de los recursos hídricos, en beneficio de las familias de Curamori y de la población de la región Piura.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-ana-inicia-trabajos-de-descolmatacion-en-rio-piura-en-curamori-ante-el-nino/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Neyra pide labor articulada ante emergencia por El Niño</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>El gobernador Luis Neyra León reafirmó que su gestión continuará apoyando las acciones de respuesta ante las lluvias y promoviendo el trabajo coordinado entre instituciones para atender las zonas afectadas. “Aquí no se trata de echarse la culpa, se trata de poner el hombro para sacar adelante esta emergencia”, manifestó Neyra, al señalar que la atención de las precipitaciones requiere la participación articulada de los gobiernos locales, regional y nacional. Precisó que la operación de los sistemas de drenaje pluvial corresponde al Ministerio de Vivienda, la Municipalidad de Piura y la Municipalidad de Castilla, de acuerdo con sus respectivas competencias. No obstante, aseguró que continuará brindando apoyo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/neyra-pide-labor-articulada-ante-emergencia-por-el-nino/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gestión</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>El Niño: Tumbes soportará lluvias extremas hasta el 25 de octubre, según Senamhi</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>En las últimas horas, decenas de hogares y distritos han sido afectados por las lluvias intensas en Tumbes, como parte de la antesala al fenómeno El Niño. El Senamhi prevé que las precipitaciones extremas continúen hasta el domingo 25 de octubre. Estas lluvias intensas estarán presentes en parte de la costa norte del país, y estarán acompañadas de descargas eléctricas y ráfagas de viento cercanas a los 40 kilómetros por hora. Desde el Ministerio de Defensa señalaron que se colocarán 750 sacos de arena en calles del barrio Bellavista, cerca del río Tumbes, para proteger las viviendas ante posibles aniegos e inundaciones por lluvias. El comandante general de la 1.ª Brigada de Infantería de Tumbes, general Luis César Núñez, detalló que también se limpiarán los canales de desfogue para agilizar la evacuación de las aguas pluviales hacia el río Tumbes y así minimizar los riesgos de inundaciones. Según reportes de Canal N, las precipitaciones comenzaron en la madrugada del jueves, registrándose la más fuerte en Zarumilla —donde hubo truenos y relámpagos—. El Senamhi precisó que el día será extremadamente lluvioso en localidades como La Cruz, Matapalo y Papayal, principalmente. Piura, otra región norteña golpeada por las lluvias propias del fenómeno El Niño, recibió al ministro de Salud, Luis Dyer, como parte de una campaña de prevención ante el dengue debido a las aguas empozadas. Dyer adelantó que se dispondrá de 1 millón 100,000 vacunas para prevenir el dengue en las regiones afectadas por las lluvias. “Tenemos 72 mil casos de dengue: 68 mil ya se dieron de alta”, subrayó a los medios de comunicación. El titular del Minsa aclaró que su cartera garantizará el abastecimiento de medicamentos a pesar de los bloqueos de carreteras e inundaciones por las lluvias, sea por puentes aéreos y marítimos. Cabe añadir que el Senamhi mantiene la vigilancia hidrometeorológica permanente en el norte del país. “Esta labor comprende el monitoreo de las condiciones meteorológicas, así como el seguimiento de la operatividad de las estaciones y sus sistemas de transmisión de información”, añadieron.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://gestion.pe/peru/fenomeno-el-nino-lluvias-intensas-inundan-calles-de-tumbes-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>“El aliviadero sí se va a hacer”: ministros no se ponen de acuerdo sobre Chutuque</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Siguen pasando los días y hasta la fecha no se decide por dónde y cuándo se iniciarán los trabajos para la salida definitiva de las aguas del río Piura. El miércoles último en Piura, al ser consultado si se mantenía en pie la propuesta de darle salida al río por Cristo Nos Valga, el ministro de Desarrollo Agrario y Riego, Marco Vinelli, respondió: “Eso lo vamos a ir resolviéndolo en los siguientes días, se está preparando para que la maquinaria esté allá trabajando”. Sin embargo, luego se abstuvo de dar más declaraciones del tema. Mientras tanto, ayer el ministro de Defensa Rafael Belaúnde, sorprendió con otra declaración. “El aliviadero es lo que se va hacer, es para lo que nos da el tiempo ahora...el aliviadero sí se va hacer”, señaló el ministro tras participar de la sesión de la Comisión de Defensa que convocó ayer el Senado en el Cuartel General del Ejército.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/el-aliviadero-si-se-va-a-hacer-ministros-no-se-ponen-de-acuerdo-sobre-chutuque/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B35" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Televisión pública: comentario a «Señal de cambio» del IRTP</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Por eso, es saludable cuando las cabezas de las instituciones públicas se preocupan en que estos documentos trasciendan, sean escritos con un lenguaje accesible y estilo claro, por comunicadores con oficio, para que lleguen a la mayor cantidad de ciudadanos.
 Ya que, finalmente, es a la sociedad a quien se le rinde cuentas.
@@ -1318,27 +1499,27 @@
 92.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-television-publica-comentario-a-«senal-cambio»-del-irtp-1097076.aspx</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B36" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Reniec atenderá hoy sábado 24 de octubre en más de 100 sedes a nivel nacional</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>El horario de atención en dichas sedes habilitadas es diferenciado.
 Por ese motivo, la institución insta a los ciudadanos a revisar la lista de oficinas y horarios antes de acudir a una de estas.
@@ -1363,27 +1544,27 @@
 Más en Andina: ??Conoce el horario de ingreso, documentos a llevar y objetos prohibidos en el examen de admisión UNMSM 2027-I https://t.co/5ER16JNGrc https://t.co/NB1gltZIet (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-reniec-atendera-hoy-sabado-24-octubre-mas-100-sedes-a-nivel-nacional-1097137.aspx</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Presidente del Congreso constató obras para impulsar agro y prevenir inundaciones en Piura</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>El presidente del Congreso, Miguel Ángel Torres (@mikitorresfp), acompañado por diputados, el gobernador regional de Piura, Luis Neyra, y el jefe de la Autoridad Nacional de Infraestructura (ANIN), Hernán Yaipén, realizó una visita de inspección a las obras del canal Miguel Checa, en Sullana, Piura, a fin de conocer los alcances del proyecto, los avances de ejecución y las medidas de prevención ante el fenómeno El Niño.?? Nota completa: https://t.co/leBDMLG0ne — Congreso del Perú ???? (@congresoperu) October 23, 2026 Durante la visita, realizada con el jefe de la Autoridad Nacional de Infraestructura (ANIN), Hernán Yaipén Aréstegui, inspeccionó el avance de estas intervenciones que, en conjunto, beneficiarán a más de 350 mil habitantes y contribuirán a la seguridad y resiliencia de la población frente a posibles emergencias.
 Lee también: [ Senado: aprueban reglamento para elección de magistrados del Tribunal Constitucional ] También participaron en la actividad los diputados César Revilla Villanueva y María Luisa Silupú Inga (Fuerza Popular), el gobernador regional de Piura, Luis Neyra León.
@@ -1409,27 +1590,27 @@
 Con estas obras, la ANIN ratifica su compromiso de ejecutar infraestructura prioritaria para Piura, asegurando mejores condiciones para el desarrollo agrícola y la preparación de las ciudades ante precipitaciones intensas.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidente-del-congreso-constato-obras-para-impulsar-agro-y-prevenir-inundaciones-piura-1097148.aspx</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B38" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Comisión de Infraestructura: Sunass expone resultados de supervisión en la costa norte</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>En la sesión, presidida por el diputado Luis Quispe Candia (Buen Gobierno), la comisión recibió al gerente general de la Superintendencia Nacional de Servicios de Saneamiento (Sunass), Manuel Muñoz Quiroz, quien expuso los resultados de las labores de supervisión en Tumbes, Piura, Lambayeque, La Libertad y Áncash.
 El representante de la Sunass informó que, de un total de 135 infraestructuras evaluadas –entre captaciones, pozos, reservorios y estaciones de bombeo–, 101 presentan vulnerabilidades con riesgo crítico.
@@ -1441,27 +1622,27 @@
 ?? https://t.co/OfhzcJn6JV (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-comision-infraestructura-sunass-expone-resultados-supervision-la-costa-norte-1097149.aspx</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Conoce las sedes en el Perú de la hackatón Desafío Space Apps 2026 de la NASA</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Durante este evento, los equipos trabajan para crear soluciones inspiradas en los objetivos de exploración más ambiciosos de la NASA, haciendo uso de los datos abiertos y gratuitos de la agencia.
 Este desafío anual, que suele ser conocido como un hackatón, es una experiencia intensiva y colaborativa de resolución de problemas, en la que los participantes abordan desafíos del mundo real sobre diversos temas planteados por expertos de la NASA.
@@ -1478,27 +1659,27 @@
 ¡Ya disponible! pic.twitter.com/lgWCtjpdSk (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) January 26, 2026</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-conoce-las-sedes-el-peru-de-hackaton-desafio-space-apps-2026-de-nasa-1097150.aspx</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Luisa Ramos de Borja: “la historia tiene que tener un sitio especial en nuestras vidas”</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>El espectáculo gratuito “Gloria a Grau: recital musical de música cívico patriótico” se desarrollará el jueves 29, a las 7 p.
 m., en el auditorio “Hernán Torres” del Centro Cultural Cayetano (Av.
@@ -1547,184 +1728,9 @@
 - Se cumplen veinte años desde que Luisa Ramos y Lucas Borja publicaron el disco Gloria a Grau , que incluyó 10 canciones, entre recopilaciones y aportes que escucharemos el jueves 29 y donde también incluyeron una versión del Himno de la Marina de Guerra del Perú, de Francisco Quiroz Tafur.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-luisa-ramos-borja-historia-tiene-tener-un-sitio-especial-nuestras-vidas-1097153.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>“El aliviadero sí se va a hacer”: ministros no se ponen de acuerdo sobre Chutuque</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Siguen pasando los días y hasta la fecha no se decide por dónde y cuándo se iniciarán los trabajos para la salida definitiva de las aguas del río Piura. El miércoles último en Piura, al ser consultado si se mantenía en pie la propuesta de darle salida al río por Cristo Nos Valga, el ministro de Desarrollo Agrario y Riego, Marco Vinelli, respondió: “Eso lo vamos a ir resolviéndolo en los siguientes días, se está preparando para que la maquinaria esté allá trabajando”. Sin embargo, luego se abstuvo de dar más declaraciones del tema. Mientras tanto, ayer el ministro de Defensa Rafael Belaúnde, sorprendió con otra declaración. “El aliviadero es lo que se va hacer, es para lo que nos da el tiempo ahora...el aliviadero sí se va hacer”, señaló el ministro tras participar de la sesión de la Comisión de Defensa que convocó ayer el Senado en el Cuartel General del Ejército.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/el-aliviadero-si-se-va-a-hacer-ministros-no-se-ponen-de-acuerdo-sobre-chutuque/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>El baile del ministro en Piura, mientras región supera los 13 mil casos de dengue</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Mientras Piura se encuentra en una situación preocupante por el incremento de casos de dengue que a la fecha suman 13.025 en la región, además del reporte de 9 fallecidos, ayer arribó a nuestra ciudad el ministro de Salud, Luis Dyer Fernández. Pero llamó la atención de los piuranos a sumarse a una coreografía de un tiktok con escolares como parte del “Cumbión de la Vacunación”, una campaña preventiva impulsada junto con la Fundación Romero para promover la inmunización y sensibilizar a la población. Al ser consultado sobre la propuesta de especialistas que se considere ampliar a los niños en la campaña de vacunación ya que actualmente está dirigida a personas de 10 a 20 años, el ministro indicó que por ahora se trabajará con lo reglamentado. El ministro llegó hasta la I.E. Mariscal Castilla, donde anunció una nueva compra de más de 1,100,000 dosis de la vacuna contra el dengue.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/el-baile-del-ministro-en-piura-mientras-region-supera-los-13-mil-casos-de-dengue/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Estas son las normas legales más importantes del viernes 23 de octubre de 2026</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Congreso de la República Resolución Legislativa del Senado de la República que elige a tres miembros del directorio del Banco Central de Reserva del Perú .
-Resolución Legislativa 002-2026-2027-S El Senado de la República, en uso de las facultades, ha resuelto elegir a los señores Oswaldo Molina Campodónico, José Ricardo Stok Capella y Juan José Marthans León miembros del directorio del Banco Central de Reserva del Perú.
-Presidencia del Consejo de Ministros Dejan sin efecto la resolución suprema que autorizó viaje de ministro de Desarrollo Agrario y Riego.
-Resolución Suprema 301-2026-PCM Se deja sin efecto la Resolución Suprema 294-2026-PCM, que autorizó el viaje del ministro de Estado en el despacho de Desarrollo Agrario y Riego, Marco Antonio Vinelli Ruiz, a la ciudad de Panamá, República de Panamá, del 21 al 23 de octubre de 2026, para participar en el evento denominado “Diálogo regional de política: construyendo sistemas agroalimentarios productivos y resilientes”.
-Ministerio de Comercio Exterior y Turismo Aprueban el Plan Nacional de Orden Turístico 2026-2031.
-Resolución Ministerial 383-2026-Mincetur Se aprueba el Plan Nacional de Orden Turístico 2026-2031, el cual tiene como objetivo general fortalecer las condiciones para el desarrollo de la actividad turística en los destinos turísticos priorizados, mediante la implementación articulada de acciones sectoriales orientadas a su gestión y desarrollo, seguridad y formalización.
-Su finalidad es contribuir al fortalecimiento de la competitividad de la actividad turística, mediante la generación de condiciones favorables para el desarrollo turístico de dichos destinos.
-Ministerio de Economía y Finanzas Aprueban el instrumento denominado “Estrategia de gestión financiera del riesgo de desastres”.
-Resolución Ministerial 485-2026-EF/52 Se aprueba la “Estrategia de gestión dinanciera del riesgo de desastres”, con la finalidad de fortalecer la capacidad financiera del Estado ante la ocurrencia de desastres.
-Su implementación se financia con cargo al presupuesto institucional de las entidades involucradas, sin demandar recursos adicionales al Tesoro Público.
-Ministerio de Trabajo y Promoción del Empleo Declaran días no laborables compensables por la visita de su santidad el papa León XIV al Perú.
-Decreto Supremo 020-2026-TR El Gobierno declaró días no laborables sujetos a compensación para el sector público y privado en Lima y Callao, Cajamarca, La Libertad, Lambayeque, Piura, Cusco y Ucayali, con motivo de la visita oficial de su santidad el papa León XIV a nuestro país.
-La medida busca facilitar la asistencia y participación de la ciudadanía en los eventos multitudinarios y actividades pastorales programadas durante la estancia del sumo pontífice, declarada previamente de interés nacional.
-Si deseas acceder al boletín Normas Legales haz clic aquí.
-Más en Andina: La presidenta de la república, Keiko Fujimori, destacó la culminación de la excavación de las estaciones de la línea 2 y del ramal de la Línea 4 del Metro de Lima y Callao, como parte de la construcción del primer sistema del metro subterráneo del país.??https://t.co/yukF5fk0Pj https://t.co/7waz0oFpVs (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 22, 2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-estas-son-las-normas-legales-mas-importantes-del-viernes-23-octubre-2026-1097046.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Más de un millón 300 mil piuranos serán afectados si no se liberan cuencas ciegas</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>La jefa de la Sunass Piura, Irina Palomino Távara, advirtió que, de registrarse el “Mega Niño” anunciado y si las cuencas ciegas no son atendidas de forma oportuna, más de un millón 300 mil piuranos podrían verse afectados con el suministro del agua potable. Por ello hizo un llamado a las autoridades, entre ellas del sector Vivienda, para que puedan replantear sus estrategias y liberen las cuencas ciegas en periodos cortos. “Definitivamente, si no hay este soporte de liberación de las cuencas ciegas, el sistema de agua potable va a ser totalmente vulnerable y en riesgo; y no solamente hablamos de los sectores que por ahora paralizaron que fueron: sector pozo Dalias, pozo Néstor Martos, Santa Margarita, Vicús y reservorio Lourdes: podemos hablar de una totalidad del sistema en Piura, Castilla o en todo el ámbito de EPS Grau que la población se van a ver afectada”, indicó en referencia a las zonales que cubre EPS Grau: Piura, Talara, Sullana, Paita y Chulucanas. “Las personas que van a estar en riesgo ya no van a ser unas miles conexiones sino que todas las personas del ámbito de Grau [EPS] que son más de un millón 300 mil personas van a estar en riesgo”, indicó. MILES DE AFECTADOS En el caso del pozo Los Algarrobos -que abastece a Bello Horizonte, Educadores, partes altas del asentamiento Los Algarrobos e Ignacio Merino, y se encuentra en reparación hasta el 28 de octubre-, la funcionara indicó que ha solicitado a EPS Grau celeridad en los trabajos, toda vez que ya es reiterativo el problema que afecta 7,140 conexiones. Informó que esta recurrencia también se registra en el A. H. Santa Julia con la afectación de 490 conexiones por la baja presión. En Los Médanos, la falta de agua afecta 563 conexiones; mientras que en El Alto la población ya tiene más de 20 días sin agua afectando 1,906 conexiones. Adelantó que la dirección de Fiscalización de Sunass ha iniciado un proceso y puede conllevar a fuertes sanciones económicas. Agregó que la empresa ya tiene un acumulado de multas de S/10 millones, mayormente por interrupción del servicio.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/mas-de-un-millon-300-mil-piuranos-seran-afectados-si-no-se-liberan-cuencas-ciegas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Gobierno declara días no laborables por visita del Papa León XIV al Perú</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>La medida, publicada en el boletín Normas Legales del Diario Oficial El Peruano, alcanza a los trabajadores del sector público y privado, de acuerdo con las fechas establecidas para cada ámbito geográfico, tal como se detalla a continuación: Sector público Departamento y fecha declarada no laborable Lima • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Provincia Constitucional del Callao • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Cajamarca, La Libertad, Lambayeque y Piura • 13 y 14 de noviembre de 2026 Sector privado Departamento y fecha declarada no laborable Lima • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Provincia Constitucional del Callao • 11 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 12 de noviembre de 2026, desde las 13:00 hasta las 24:00 horas • 16 de noviembre de 2026 Cajamarca, La Libertad, Lambayeque y Piura • 13 y 14 de noviembre de 2026 Cusco • 15 de noviembre de 2026 Ucayali • 15 de noviembre de 2026 A diferencia de un feriado, que otorga descanso remunerado sin recuperación de horas, el día no laborable compensable exige recuperar las horas dejadas de trabajar.
-En el sector privado, acogerse a esta medida requiere un acuerdo entre el empleador y los trabajadores; si no lo hay, decide el empleador.
-Lee también Papa León XIV en Perú: helicóptero de la FAP acompañará sus traslados en el norte Visita de trascendencia espiritual, histórica y social El decreto -que lleva las rúbricas de la presidenta Keiko Fujimori; del presidente del Consejo de Ministros, Luis Galarreta; y del titular de Trabajo Juan Sheput- señala que la visita del pontífice, prevista del 11 al 16 de noviembre de 2026, constituye un acontecimiento de especial trascendencia espiritual, histórica y social para el país.
-También indica que la medida busca facilitar la asistencia de las personas a los eventos y reuniones vinculados con la visita.
-¿Como se recuperarán las horas dejadas de trabajar? Respecto a la recuperación de las horas no trabajadas, en el sector público estas deberán compensarse dentro de los 10 días posteriores o en la oportunidad que establezca el titular de cada entidad.
-En el sector privado, el acuerdo entre el empleador y los trabajadores deberá establecer cómo se recuperarán las horas; a falta de consenso, la decisión corresponderá al empleador.
-Lee también Papa León XIV: cardenal de Lima habla sobre itinerario de Sumo Pontífice tras cirugía Servicios indispensables La norma también dispone que las entidades públicas comprendidas en las jurisdicciones señaladas adopten las medidas necesarias para garantizar la continuidad de los servicios públicos indispensables para la comunidad durante los días no laborables.
-Asimismo, las empresas privadas que brindan actividades económicas de especial relevancia para la comunidad podrán determinar los puestos de trabajo excluidos de la medida.
-Esto comprende los servicios sanitarios y de salubridad, limpieza y saneamiento; electricidad, agua, desagüe, gas y combustible; sepelios; comunicaciones y telecomunicaciones; transporte, pesca, puertos, aeropuertos y terrapuertos; establecimientos de hospedaje que reciban y atiendan huéspedes; restaurantes; seguridad, custodia y vigilancia; empresas del sistema financiero y otros servicios financieros; traslado de valores y expendio de víveres y alimentos.
-Más en Andina: ATU realizará feria para informar los beneficios de ampliar carril de bus en Av.
-Arequipa.
-La cita es este domingo 25 y en ella se explicará cómo gestionar el VAPP para acceder a las cocheras.??https://t.co/n2Idy2parG https://t.co/KXDDp86noE (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 23, 2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-gobierno-declara-dias-no-laborables-visita-del-papa-leon-xiv-al-peru-1097045.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>46318</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Facultades ayudan, pero no resuelven el problema de planificación de obras en Piura</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Se aprobaron las facultades legislativas al Poder Ejecutivo en materia de lucha contra la criminalidad y la prevención frente al Fenómeno de El Niño. Entre los puntos aprobados están la ayuda humanitaria directa del Instituto Nacional de Defensa Civil (INDECI) durante los primeros 15 días de una emergencia, el uso de Obras por Impuestos para reducir el riesgo de desastres y la expropiación de predios. Con ello, vale la pena preguntarse cómo va la ejecución de la inversión pública en Piura y qué cambios cabría esperar antes de que acabe el año. Este año la inversión pública en estos dos frentes ha avanzado de manera desigual. Según el Ministerio de Economía y Finanzas (MEF), el dinero para obras de seguridad ciudadana del Gobierno Regional y las municipalidades pasó de S/ 6.9 millones al empezar el año a S/ 51.6 millones al cierre de septiembre, es decir, se multiplicó por 7.5. Sin embargo, el Gobierno Regional ha gastado apenas el 8.1% de lo que tiene asignado en esas obras, mientras que las municipalidades llevan 68.3%. En prevención frente a desastres, el dinero para obras bajó de S/ 55.2 a S/ 49.8 millones y la ejecución llega a la mitad (49.0%). En ese descenso pesa el drenaje pluvial del cercado de la ciudad de Piura, cuyo presupuesto pasó de S/ 43.1 millones a S/ 14.4 millones entre enero y septiembre, un recorte de dos tercios. Es menos dinero para una obra clave justo cuando el Comité Multisectorial ENFEN, que mantiene la alerta de El Niño costero, prevé que su magnitud extraordinaria se mantenga hasta enero de 2027 y que haya lluvias por encima de lo normal en la costa norte entre octubre y diciembre. A este rezago se suman las obras paralizadas, que no son solo de seguridad o prevención, pero ilustran el panorama de la inversión en Piura. El Gobierno Regional y las municipalidades suman 73 obras paralizadas en todos los sectores, con un saldo de inversión de S/ 531 millones. Ninguna se detuvo por falta de terreno o interferencias, que son los casos que buscan evitar las nuevas reglas de expropiación; casi todas (69, el 95%) se detuvieron por causas que las medidas aprobadas no buscan resolver, principalmente incumplimiento de contrato (42 obras, con S/ 416 millones) y controversias o arbitrajes (14 obras). Entre las paralizadas figuran 22 obras de la “Reconstrucción con Cambios”, el plan posterior al Niño Costero de 2017, con S/ 324 millones de saldo. La pregunta de fondo es si estas facultades corregirán lo que hasta ahora ha fallado. Las medidas aprobadas sí ayudan: agilizan la ayuda humanitaria en emergencias, abren una vía de financiamiento con Obras por Impuestos y facilitan la compra de terrenos. Pero no cambian cómo se programan, presupuestan y supervisan las obras. Y como el Ejecutivo tendría hasta 90 días calendario para emitir los decretos, es poco probable que modifiquen el rezago en lo que resta de 2026. Los problemas de Piura se parecen más a fallas de programación del gasto y de gestión de contratos: más de 8 de cada 10 soles de las obras de seguridad se incorporaron después de iniciado el año, la obra de drenaje clave perdió dos tercios de su presupuesto cuando se acerca El Niño y 42 obras se detuvieron por incumplimiento de contrato. Esperamos que las autoridades regionales y municipales que asumirán en 2027 aprendan de lo ocurrido y mejoren la programación y la gestión de las obras desde el primer día de su mandato.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/facultades-ayudan-pero-no-resuelven-el-problema-de-planificacion-de-obras-en-piura/</t>
         </is>
       </c>
     </row>
@@ -1739,24 +1745,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Resultados ONPE en región Piura al 99.430 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+          <t>¿Piura está preparada para afrontar los efectos del Fenómeno El Niño?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación región Piura según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Ahora mismo los piuranos transitan entre calles inundadas, obras inconclusas y un sofocante calor que se entremezcla con nubes de polvo que anuncian la llegada de las enfermedades respiratorias. Esta fotografía no es nueva. Se trata de una imagen repetida en cada periodo lluvioso, en cada llegada del Fenómeno El Niño (FEN). La provincia tiene 340 cuencas ciegas, lo que indica no solo las particularidades del terreno, sino la falta de planificación en el desarrollo urbanístico desde hace décadas. Por ello, cuenta con un deficiente sistema de drenaje pluvial que hoy se apoya en los Sistemas Alternativos de Recolección y Evacuación de Aguas de Lluvia (SARE), pero que aún están en periodo de prueba. Al mismo tiempo, existe población que vive en zonas de drenaje natural o en lugares que imposibilitan trabajar en el cauce del río Piura. Aunque no son todos los motivos de la crisis piurana, sí brindan un panorama de la complejidad del problema y de la necesidad de señalar múltiples responsables: autoridades de distintas gestiones y de distintos niveles de gobierno, líderes políticos y mediáticos, organizaciones sociales con intereses particulares y la ausencia de una cultura de prevención instalada en los usos y costumbres de la ciudadanía. La crisis es más histórica que coyuntural, y se ha visto potenciada por la inestabilidad política de los últimos años. Pero el panorama actual no solo es preocupante por los efectos de las lluvias, sino porque se ha instalado en la ciudadanía la sensación de incertidumbre. Evidenciar que los actores políticos, mediáticos y civiles están buscando responsables únicos no contribuye a disminuir el miedo. Estamos asistiendo a la instrumentalización política del FEN, en medio del fragor de la campaña por la segunda vuelta al Gobierno Regional, y la búsqueda de legitimidad social por parte del Gobierno nacional. Es momento de retomar los matices, las explicaciones técnicas, y pedir la colaboración de los distintos niveles de gobierno, de la academia, los colegios profesionales, los colectivos civiles y el empresariado. Ante la inminente tragedia se requiere dejar el enfrentamiento y estar disponibles para la cooperación. La historia siempre es sabía y nos enseñará, más adelante, quien hizo bien y quien se equivocó. Por el contrario, si la incertidumbre se convierte en miedo, se romperá el conectivo social, cada quien buscará salvarse individualmente y no podremos estar unidos. Las lluvias golpean nuevamente Piura y ponen en evidencia las limitaciones para enfrentar sus graves consecuencias frente a la llegada del fenómeno de El Niño. Cuando faltan previsión, eficiencia y eficacia en las acciones, la población y sus actividades productivas quedan expuestas y los daños pueden multiplicarse. Piura necesita que las intervenciones prioritarias se ejecuten antes de que las lluvias se intensifiquen. En ese contexto, un riesgo que requiere atención inmediata es el dique de La Mariposa, ubicado aguas arriba de la represa de Los Ejidos. Un análisis técnico elaborado por el hidrólogo César Alvarado advierte sobre la necesidad urgente de intervenir esta estructura, de aproximadamente 700 metros de longitud y tres metros de altura. Según los modelamientos incluidos en dicho análisis, ante caudales extraordinarios del orden de los 4.000 m³/s, el estado actual del dique podría comprometer su capacidad para contener el agua y causar el desvío de unos 350 m³/s hacia La Mariposa y Los Ejidos de Huan, con un posible alcance al casco urbano de Piura. Este escenario tendría graves consecuencias socioeconómicas para la ciudad. Ante esta advertencia, el directorio de la Cámara de Comercio y Producción de Piura convocó a Víctor Garrido Lecca, presidente del Proyecto Especial Chira Piura (PECHP), responsable de la custodia y mantenimiento de esa infraestructura. La entidad asumió el compromiso de evaluar la situación y plantear medidas técnicas de refuerzo. Hacemos un llamado a las autoridades del Gobierno Central, a los organismos técnicos y a la población colindante para que brinden facilidades y sumen esfuerzos en apoyo al PECHP. La acción oportuna, la gestión inteligente y el trabajo técnico riguroso son la única vía para resguardar la vida, la economía y el futuro de Piura.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/resultados-en-piura-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+          <t>https://elcomercio.pe/opinion/columnistas/cara-y-sello-piura-esta-preparada-para-afrontar-los-efectos-del-fenomeno-el-nino-fernando-huaman-flores-y-javier-bereche-alvarez-noticia/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1764,24 +1770,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>¿Piura está preparada para afrontar los efectos del Fenómeno El Niño?</t>
+          <t>Más de un millón 300 mil piuranos serán afectados si no se liberan cuencas ciegas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ahora mismo los piuranos transitan entre calles inundadas, obras inconclusas y un sofocante calor que se entremezcla con nubes de polvo que anuncian la llegada de las enfermedades respiratorias. Esta fotografía no es nueva. Se trata de una imagen repetida en cada periodo lluvioso, en cada llegada del Fenómeno El Niño (FEN). La provincia tiene 340 cuencas ciegas, lo que indica no solo las particularidades del terreno, sino la falta de planificación en el desarrollo urbanístico desde hace décadas. Por ello, cuenta con un deficiente sistema de drenaje pluvial que hoy se apoya en los Sistemas Alternativos de Recolección y Evacuación de Aguas de Lluvia (SARE), pero que aún están en periodo de prueba. Al mismo tiempo, existe población que vive en zonas de drenaje natural o en lugares que imposibilitan trabajar en el cauce del río Piura. Aunque no son todos los motivos de la crisis piurana, sí brindan un panorama de la complejidad del problema y de la necesidad de señalar múltiples responsables: autoridades de distintas gestiones y de distintos niveles de gobierno, líderes políticos y mediáticos, organizaciones sociales con intereses particulares y la ausencia de una cultura de prevención instalada en los usos y costumbres de la ciudadanía. La crisis es más histórica que coyuntural, y se ha visto potenciada por la inestabilidad política de los últimos años. Pero el panorama actual no solo es preocupante por los efectos de las lluvias, sino porque se ha instalado en la ciudadanía la sensación de incertidumbre. Evidenciar que los actores políticos, mediáticos y civiles están buscando responsables únicos no contribuye a disminuir el miedo. Estamos asistiendo a la instrumentalización política del FEN, en medio del fragor de la campaña por la segunda vuelta al Gobierno Regional, y la búsqueda de legitimidad social por parte del Gobierno nacional. Es momento de retomar los matices, las explicaciones técnicas, y pedir la colaboración de los distintos niveles de gobierno, de la academia, los colegios profesionales, los colectivos civiles y el empresariado. Ante la inminente tragedia se requiere dejar el enfrentamiento y estar disponibles para la cooperación. La historia siempre es sabía y nos enseñará, más adelante, quien hizo bien y quien se equivocó. Por el contrario, si la incertidumbre se convierte en miedo, se romperá el conectivo social, cada quien buscará salvarse individualmente y no podremos estar unidos. Las lluvias golpean nuevamente Piura y ponen en evidencia las limitaciones para enfrentar sus graves consecuencias frente a la llegada del fenómeno de El Niño. Cuando faltan previsión, eficiencia y eficacia en las acciones, la población y sus actividades productivas quedan expuestas y los daños pueden multiplicarse. Piura necesita que las intervenciones prioritarias se ejecuten antes de que las lluvias se intensifiquen. En ese contexto, un riesgo que requiere atención inmediata es el dique de La Mariposa, ubicado aguas arriba de la represa de Los Ejidos. Un análisis técnico elaborado por el hidrólogo César Alvarado advierte sobre la necesidad urgente de intervenir esta estructura, de aproximadamente 700 metros de longitud y tres metros de altura. Según los modelamientos incluidos en dicho análisis, ante caudales extraordinarios del orden de los 4.000 m³/s, el estado actual del dique podría comprometer su capacidad para contener el agua y causar el desvío de unos 350 m³/s hacia La Mariposa y Los Ejidos de Huan, con un posible alcance al casco urbano de Piura. Este escenario tendría graves consecuencias socioeconómicas para la ciudad. Ante esta advertencia, el directorio de la Cámara de Comercio y Producción de Piura convocó a Víctor Garrido Lecca, presidente del Proyecto Especial Chira Piura (PECHP), responsable de la custodia y mantenimiento de esa infraestructura. La entidad asumió el compromiso de evaluar la situación y plantear medidas técnicas de refuerzo. Hacemos un llamado a las autoridades del Gobierno Central, a los organismos técnicos y a la población colindante para que brinden facilidades y sumen esfuerzos en apoyo al PECHP. La acción oportuna, la gestión inteligente y el trabajo técnico riguroso son la única vía para resguardar la vida, la economía y el futuro de Piura.</t>
+          <t>La jefa de la Sunass Piura, Irina Palomino Távara, advirtió que, de registrarse el “Mega Niño” anunciado y si las cuencas ciegas no son atendidas de forma oportuna, más de un millón 300 mil piuranos podrían verse afectados con el suministro del agua potable. Por ello hizo un llamado a las autoridades, entre ellas del sector Vivienda, para que puedan replantear sus estrategias y liberen las cuencas ciegas en periodos cortos. “Definitivamente, si no hay este soporte de liberación de las cuencas ciegas, el sistema de agua potable va a ser totalmente vulnerable y en riesgo; y no solamente hablamos de los sectores que por ahora paralizaron que fueron: sector pozo Dalias, pozo Néstor Martos, Santa Margarita, Vicús y reservorio Lourdes: podemos hablar de una totalidad del sistema en Piura, Castilla o en todo el ámbito de EPS Grau que la población se van a ver afectada”, indicó en referencia a las zonales que cubre EPS Grau: Piura, Talara, Sullana, Paita y Chulucanas. “Las personas que van a estar en riesgo ya no van a ser unas miles conexiones sino que todas las personas del ámbito de Grau [EPS] que son más de un millón 300 mil personas van a estar en riesgo”, indicó. MILES DE AFECTADOS En el caso del pozo Los Algarrobos -que abastece a Bello Horizonte, Educadores, partes altas del asentamiento Los Algarrobos e Ignacio Merino, y se encuentra en reparación hasta el 28 de octubre-, la funcionara indicó que ha solicitado a EPS Grau celeridad en los trabajos, toda vez que ya es reiterativo el problema que afecta 7,140 conexiones. Informó que esta recurrencia también se registra en el A. H. Santa Julia con la afectación de 490 conexiones por la baja presión. En Los Médanos, la falta de agua afecta 563 conexiones; mientras que en El Alto la población ya tiene más de 20 días sin agua afectando 1,906 conexiones. Adelantó que la dirección de Fiscalización de Sunass ha iniciado un proceso y puede conllevar a fuertes sanciones económicas. Agregó que la empresa ya tiene un acumulado de multas de S/10 millones, mayormente por interrupción del servicio.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/opinion/columnistas/cara-y-sello-piura-esta-preparada-para-afrontar-los-efectos-del-fenomeno-el-nino-fernando-huaman-flores-y-javier-bereche-alvarez-noticia/</t>
+          <t>https://eltiempo.pe/local/mas-de-un-millon-300-mil-piuranos-seran-afectados-si-no-se-liberan-cuencas-ciegas/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gestión</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -1789,17 +1795,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>El Niño: Tumbes soportará lluvias extremas hasta el 25 de octubre, según Senamhi</t>
+          <t>El baile del ministro en Piura, mientras región supera los 13 mil casos de dengue</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>En las últimas horas, decenas de hogares y distritos han sido afectados por las lluvias intensas en Tumbes, como parte de la antesala al fenómeno El Niño. El Senamhi prevé que las precipitaciones extremas continúen hasta el domingo 25 de octubre. Estas lluvias intensas estarán presentes en parte de la costa norte del país, y estarán acompañadas de descargas eléctricas y ráfagas de viento cercanas a los 40 kilómetros por hora. Desde el Ministerio de Defensa señalaron que se colocarán 750 sacos de arena en calles del barrio Bellavista, cerca del río Tumbes, para proteger las viviendas ante posibles aniegos e inundaciones por lluvias. El comandante general de la 1.ª Brigada de Infantería de Tumbes, general Luis César Núñez, detalló que también se limpiarán los canales de desfogue para agilizar la evacuación de las aguas pluviales hacia el río Tumbes y así minimizar los riesgos de inundaciones. Según reportes de Canal N, las precipitaciones comenzaron en la madrugada del jueves, registrándose la más fuerte en Zarumilla —donde hubo truenos y relámpagos—. El Senamhi precisó que el día será extremadamente lluvioso en localidades como La Cruz, Matapalo y Papayal, principalmente. Piura, otra región norteña golpeada por las lluvias propias del fenómeno El Niño, recibió al ministro de Salud, Luis Dyer, como parte de una campaña de prevención ante el dengue debido a las aguas empozadas. Dyer adelantó que se dispondrá de 1 millón 100,000 vacunas para prevenir el dengue en las regiones afectadas por las lluvias. “Tenemos 72 mil casos de dengue: 68 mil ya se dieron de alta”, subrayó a los medios de comunicación. El titular del Minsa aclaró que su cartera garantizará el abastecimiento de medicamentos a pesar de los bloqueos de carreteras e inundaciones por las lluvias, sea por puentes aéreos y marítimos. Cabe añadir que el Senamhi mantiene la vigilancia hidrometeorológica permanente en el norte del país. “Esta labor comprende el monitoreo de las condiciones meteorológicas, así como el seguimiento de la operatividad de las estaciones y sus sistemas de transmisión de información”, añadieron.</t>
+          <t>Mientras Piura se encuentra en una situación preocupante por el incremento de casos de dengue que a la fecha suman 13.025 en la región, además del reporte de 9 fallecidos, ayer arribó a nuestra ciudad el ministro de Salud, Luis Dyer Fernández. Pero llamó la atención de los piuranos a sumarse a una coreografía de un tiktok con escolares como parte del “Cumbión de la Vacunación”, una campaña preventiva impulsada junto con la Fundación Romero para promover la inmunización y sensibilizar a la población. Al ser consultado sobre la propuesta de especialistas que se considere ampliar a los niños en la campaña de vacunación ya que actualmente está dirigida a personas de 10 a 20 años, el ministro indicó que por ahora se trabajará con lo reglamentado. El ministro llegó hasta la I.E. Mariscal Castilla, donde anunció una nueva compra de más de 1,100,000 dosis de la vacuna contra el dengue.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://gestion.pe/peru/fenomeno-el-nino-lluvias-intensas-inundan-calles-de-tumbes-noticia/</t>
+          <t>https://eltiempo.pe/local/el-baile-del-ministro-en-piura-mientras-region-supera-los-13-mil-casos-de-dengue/</t>
         </is>
       </c>
     </row>
@@ -1814,74 +1820,74 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>La descolmatación no servirá sin adecuado desfogue del río Piura</t>
+          <t>Tenga cuidado con el uso de máscaras tóxicas en Halloween</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>La descolmatación del río Piura se ha dividido en varios tramos de más de 20 kilómetros entre la represa Los Ejidos y aguas abajo del puente Independencia. Sin embargo, a los ojos de los especialistas estos trabajos no aseguran que la ciudad y el Bajo Piura no se vuelvan a inundar, tal y como ocurrió en el año 2017. Para los expertos, el problema de fondo es que aún no se trabaja en la salida del río hacia el mar. En este punto, se ha abierto una nueva polémica por la decisión del gobierno de la presidenta Keiko Fujimori Higuchi de recuperar parte de su salida ancestral por el río Loco cerca de Sechura. Con esta decisión se deja de lado lo que propuso la sociedad civil de Piura a los líderes de los gremios empresariales más importantes del país. Esto consistía en intervenir la zona de Chutuque mediante explosivos y darle al río una salida más fluida hacia la laguna La Niña y desde ahí hacia el mar. Sin embargo, esto no fue tomado en cuenta por el Ministerio de Agricultura que planteó sacar el río por un tramo más corto, como lo era antes de la construcción del dique de la margen derecha. Descolmatación En tanto el tema se define, la descolmatación sigue con problemas. En el primer tramo de 4.85 kilómetros entre la presa Los Ejidos y el puente Bolognesi, la extracción del material fuera del cauce marcha lento en comparación a los trabajos de remoción (descolmatación). Hacia el 15 de septiembre, se había logrado retirar un 53.21% del material del cauce, pero la extracción de la tierra y maleza era de 24.68%. Para inicios de octubre, la remoción de la tierra superó el 60%, pero la eliminación estaba por debajo del 40%. Pese a estos inconvenientes, la Autoridad Nacional del Agua (ANA), entidad a cargo del primer tramo, sostiene que concluiría este frente en la primera semana de noviembre. En la actualidad, laboran con más de 50 equipos de maquinaria pesada, entre los que se incluyen 35 volquetes. Empresa privada Un segundo frente de trabajo se ubica aguas abajo del puente Bolognesi hacia el puente Grau a cargo de la Fundación Romero. Según el ingeniero Andrés Farfán, con esta intervención se podría alcanzar una caja hidráulica que soporte 2.000 m3/seg y la meta es concluir en la primera semana de noviembre. En la zona se aprecian más de 20 volquetes, cinco tractores oruga, tres excavadoras, entre otros vehículos. En tanto, el tramo entre el puente Grau y el puente Independencia está a cargo del Ejército a través del Ministerio de Defensa. La meta es la descolmatación de 11 kilómetros. Según el ministro de Defensa, Rafael Belaunde Llosa, esperan que estos trabajen ayuden a soportar caudales de 3.500 m3/seg. El avance estaría cerca del 50%. Falta más Frente a estos trabajos, el decano del Colegio de Ingenieros de Piura (CIP), Manuel Asmat, señaló que se necesita implementar más turnos y traer más maquinaria, debido a lo impredecible del clima que podría generar un adelanto de las lluvias de “El Niño”. “Continuamos solicitando que se implementen más frentes de trabajo en la medida que el plazo es corto y que el espacio físico es grande. Esto es incierto porque en cualquier momento podría empezar a llover e incluso se habla de la primera semana de noviembre. Hay que aprovechar todo el tiempo que tenemos”, manifestó Asmat. No es suficiente Pese a estos trabajos y despliegue de maquinaria, el decano del CIP consideró que aún no se disminuye el riesgo de sufrir una inundación debido a la falta de desfogue del río. “En su momento, el Ministerio de Agricultura ha indicado que quieren llegar a una caja hidráulica para 3.500 metros cúbicos por segundo y también se habla de caudales extraordinarios de 4.000 m3/seg que vendrían. Por eso se habla de trabajos de mitigación del riesgo y no de una solución definitiva”, indicó. En relación a la salida por el río Loco en Cristo Nos Valga, el decano dijo que frente a las otras alternativas como era Chutuque, era la opción más viable en lo técnico. Sin embargo, no ocurre lo mismo con la viabilidad social. “Es una alternativa viable desde lo técnico y económico, y el plazo no pasa de dos a tres meses para conectar esa salida [con el mar], pero el problema es el componente social. Lamentablemente, mientras no tengamos validación social, ningún proyecto puede ser viable. Esto requiere de una campaña de un año para recién explicar y viabilizar [el proyecto]. Su temor es legítimo y pueden decir por qué les van a enviar el agua si hay otras zonas donde puede salir”, consideró Asmat. En tanto se agrava esta controversia, los trabajos de descolmatación siguen avanzando con la duda sobre dónde saldrá el río. “Mientras no tengamos salida al mar, seguiremos condenados a descolmatar año tras año”, finalizó.</t>
+          <t>Se acerca la tradicional fiesta de Halloween y los niños y adolescentes deben tener mucho cuidado para evitar el uso de máscaras tóxicas que podrían desencadenar alergias y males cutáneos, entre otros cuadros clínicos. Frente a este panorama, la Segunda Fiscalía de Prevención del Delito de Piura y otras autoridades realizaron un operativo multisectorial orientado a salvaguardar la vida y la salud de la población. El resultado del operativo dejó el saldo de 278 máscaras de Halloween decomisadas por la autoridad sanitaria tras verificar que no contaban con el rotulado sanitario exigido por ley INSPECCIONAN CINCO TIENDAS La fiscal provincial Berena Ballesteros Vigil, con el apoyo de la Policía Nacional, así como de inspectores de la Dirección Regional de Salud (Diresa) y de las municipalidades correspondientes, inspeccionó cinco establecimientos comerciales ubicados en los distritos de Castilla y Veintiséis de Octubre dedicados a la venta de disfraces, máscaras y accesorios alegóricos. Durante la revisión, las autoridades incautaron los productos debido a que sus empaques carecían del Registro Nacional y la Autorización Sanitaria emitidos por la Digesa, además de omitir datos clave como el nombre del importador, código de origen, advertencias de edad, medidas preventivas de uso y recomendaciones ante emergencias. EXHORTACIÓN Finalmente, la representante del Ministerio Público exhortó a los propietarios de los negocios a expender exclusivamente productos que cumplan con la normativa sanitaria vigente, recordando que la comercialización de artículos informales representa un peligro directo para la salud de los menores de edad.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/la-descolmatacion-no-servira-sin-adecuado-desfogue-del-rio-piura/</t>
+          <t>https://eltiempo.pe/local/tenga-cuidado-con-el-uso-de-mascaras-toxicas-en-halloween/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Piura ante una tormenta perfecta: El Niño se acerca con el dengue activo y obras aún inconclusas</t>
+          <t>La descolmatación no servirá sin adecuado desfogue del río Piura</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Bastó una lluvia de alrededor de 5 horas para demostrar cada una de las falencias que hay en Piura. Un sistema de drenaje que no funciona, calles inundadas, obras inconclusas y además, el peligro del dengue, una enfermedad que ya ha sabido azotar en la región norteña. ¿Por qué Piura vive en un círculo vicioso en el que solo queda esperar que no suceda lo peor? En 2017, en pleno fenómeno de El Niño Costero, más de 50 fallecidos por el dengue. En 2023, año del ciclón Yaku, casi 80 mil casos y 148 muertos. En este 2026, ya se registran más de 13 mil casos acumulados de dengue y 8 defunciones. El panorama para el 2027 no es muy alentador. Las lluvias producidas en los últimas días solo hicieron poner los ojos otra vez en una región que ya sido bastante afectada por los desastres naturales. En urbanizaciones de Piura, Chulucanas y Catacaos también se vieron calles con aniegos. El Senamhi ya advirtió que las lluvias continuarán en los próximos meses con más frecuencia e intensidad. Y ante esa inminente llegada de un clima inclemente, la pregunta es, ¿qué se está haciendo para contener lo más posible los estragos de un Fenómeno El Niño que se preve catastrófico? El dengue, una gran amenaza Edward Pozo, jefe de inteligencia sanitaria de la red asistencial Piura de Essalud, conversó con El Comercio sobre cómo está la región norteña a semanas del Fenómeno de El Niño y tras esta lluvia que ha sido una especie de aviso de lo que podría venir. En los hospitales, habrá unidades de vigilancia intensiva para el dengue, lugares de atención con insumos médicos y medicamentos. Además, se contratará personal que se va a necesitar durante la emergencia. “Las lluvias han sido un aviso de que nos va a afectar bastante en la salud de Piura”. “Lo que se sabe del dengue, es que por lo menos después de dos semanas del periodo lluvioso, es que empiezan a presentarse ya los casos de dengue, en una situación endémica. Pero Piura ya viene con casos de dengue desde el mes de julio, con brotes activos. Y esto es debido al calor y las altas temperaturas. Estas lluvias recientes lo que hacen es agregar una variable más que va a aumentar el riesgo de mayo cantidad de casos (de dengue)” En cuanto a previsiones y cómo prepararse para lo que se pronostica como un FEN de magnitud “fuerte a extraordinaria”, el biólogo señaló que con la data histórica, se han puesto en el peor escenario posible. “El peor fue el del año 2023 con el ciclón Yaku. Essalud tuvo 35 mil casos de dengue. La OPS en su guía nos ha dicho que calculemos con una tasa de ataque de 4.5 a la población. Es decir, el 4.5% de la población se podría enfermar de dengue”. La vacunación como sistema de defensa “La Diresa da parte de esas vacunas a Essalud, pero quien monitorea esas cifras y avances son ellos. A nosotros, como red asistencial Piura - Essalud, se nos dotó de 2.500 vacunas. Ya más del 50% han sido administradas dentro de asegurados del grupo etario de 10 a 20 años. Y estamos haciendo campañas intensas en Morropón, el Bajo Piura y Sullana. Una vez que tengamos eso cubierto, vamos a solicitar más vacunas” Nancy Jiménez, corresponsal en Piura de América Noticias y Canal N, nos responde sobre la incidencia del dengue en la región: “Piura es una ciudad endémica, totalmente. Ahorita estamos en pleno brote. Hay más de 13 mil casos y 9 fallecidos. De ellos, 4 son menores de edad”. La región ante el Fenómeno El Niño y el dengue, una vez más ¿Qué va a pasar ahora que vienen las lluvias? La vulnerabilidad de zonas muy endémicas o de altas transmisión del dengue, como Chulucanas, Sullana, Piura o Castilla, es porque son las más pobladas y por esto, más propensas a desarrollar brotes de la enfermedad. “Los pueblos jóvenes de estas ciudades, que no tienen servicios básicos, van a tener muchos problemas por la acumulación de agua, y peor aún, para disponer de agua potable para su consumo y su higiene personal. Eso con las lluvias se va a agudizar muchísimo. La disponibilidad de agua potable va a ser bastante difícil. Son mucho más vulnerables a tener dengue y también enfermedades respiratorias, micosis o diarrea, por las mismas condiciones que genera este fenómeno”, señaló Edward Pozo. Así está Piura hoy Cuando estuvimos en Piura hace algunos meses, vimos que varias calles del centro histórico lucían rotas y sin avances visibles en las obras. La gente que transitaba por esa zona solo nos mencionaba “eso está así (roto y en un aparente abandono) desde hace tiempo”. Al respecto, nuestra colega Nancy Jiménez añade: “Piura está totalmente destruida, con las pistas que no se puede ni caminar y no solamente el centro de Piura, sino que en la región, en la ciudad, han iniciado una serie de obras ya al término de la gestión. Cierran una vía, la rompen, cierran otra, la rompen, sin ni siquiera restablecer la que rompieron anteriormente. Según la Cámara de Comercio de Piura, por lo menos el 80% de los negocios de la zona se han visto afectados”. Obras que ya debieron culminarse y que registran avances de menos del 40%, SARES (sistemas de recolección y evacuación de aguas de lluvia) del Ministerio de Vivienda que no han tenido la respuesta esperada por parte de las municipalidades, que debido al cierre de sus gestiones, han descuidado estas funciones. Y no, esto no es un “simulacro en seco” como diría el ministro de Defensa, Rafael Belaúnde, que visitó las zonas afectadas en Piura. La región norteña solo está avisando que no está lista y el tiempo sigue corriendo. El Fenómeno de El Niño y el dengue no esperan.</t>
+          <t>La descolmatación del río Piura se ha dividido en varios tramos de más de 20 kilómetros entre la represa Los Ejidos y aguas abajo del puente Independencia. Sin embargo, a los ojos de los especialistas estos trabajos no aseguran que la ciudad y el Bajo Piura no se vuelvan a inundar, tal y como ocurrió en el año 2017. Para los expertos, el problema de fondo es que aún no se trabaja en la salida del río hacia el mar. En este punto, se ha abierto una nueva polémica por la decisión del gobierno de la presidenta Keiko Fujimori Higuchi de recuperar parte de su salida ancestral por el río Loco cerca de Sechura. Con esta decisión se deja de lado lo que propuso la sociedad civil de Piura a los líderes de los gremios empresariales más importantes del país. Esto consistía en intervenir la zona de Chutuque mediante explosivos y darle al río una salida más fluida hacia la laguna La Niña y desde ahí hacia el mar. Sin embargo, esto no fue tomado en cuenta por el Ministerio de Agricultura que planteó sacar el río por un tramo más corto, como lo era antes de la construcción del dique de la margen derecha. Descolmatación En tanto el tema se define, la descolmatación sigue con problemas. En el primer tramo de 4.85 kilómetros entre la presa Los Ejidos y el puente Bolognesi, la extracción del material fuera del cauce marcha lento en comparación a los trabajos de remoción (descolmatación). Hacia el 15 de septiembre, se había logrado retirar un 53.21% del material del cauce, pero la extracción de la tierra y maleza era de 24.68%. Para inicios de octubre, la remoción de la tierra superó el 60%, pero la eliminación estaba por debajo del 40%. Pese a estos inconvenientes, la Autoridad Nacional del Agua (ANA), entidad a cargo del primer tramo, sostiene que concluiría este frente en la primera semana de noviembre. En la actualidad, laboran con más de 50 equipos de maquinaria pesada, entre los que se incluyen 35 volquetes. Empresa privada Un segundo frente de trabajo se ubica aguas abajo del puente Bolognesi hacia el puente Grau a cargo de la Fundación Romero. Según el ingeniero Andrés Farfán, con esta intervención se podría alcanzar una caja hidráulica que soporte 2.000 m3/seg y la meta es concluir en la primera semana de noviembre. En la zona se aprecian más de 20 volquetes, cinco tractores oruga, tres excavadoras, entre otros vehículos. En tanto, el tramo entre el puente Grau y el puente Independencia está a cargo del Ejército a través del Ministerio de Defensa. La meta es la descolmatación de 11 kilómetros. Según el ministro de Defensa, Rafael Belaunde Llosa, esperan que estos trabajen ayuden a soportar caudales de 3.500 m3/seg. El avance estaría cerca del 50%. Falta más Frente a estos trabajos, el decano del Colegio de Ingenieros de Piura (CIP), Manuel Asmat, señaló que se necesita implementar más turnos y traer más maquinaria, debido a lo impredecible del clima que podría generar un adelanto de las lluvias de “El Niño”. “Continuamos solicitando que se implementen más frentes de trabajo en la medida que el plazo es corto y que el espacio físico es grande. Esto es incierto porque en cualquier momento podría empezar a llover e incluso se habla de la primera semana de noviembre. Hay que aprovechar todo el tiempo que tenemos”, manifestó Asmat. No es suficiente Pese a estos trabajos y despliegue de maquinaria, el decano del CIP consideró que aún no se disminuye el riesgo de sufrir una inundación debido a la falta de desfogue del río. “En su momento, el Ministerio de Agricultura ha indicado que quieren llegar a una caja hidráulica para 3.500 metros cúbicos por segundo y también se habla de caudales extraordinarios de 4.000 m3/seg que vendrían. Por eso se habla de trabajos de mitigación del riesgo y no de una solución definitiva”, indicó. En relación a la salida por el río Loco en Cristo Nos Valga, el decano dijo que frente a las otras alternativas como era Chutuque, era la opción más viable en lo técnico. Sin embargo, no ocurre lo mismo con la viabilidad social. “Es una alternativa viable desde lo técnico y económico, y el plazo no pasa de dos a tres meses para conectar esa salida [con el mar], pero el problema es el componente social. Lamentablemente, mientras no tengamos validación social, ningún proyecto puede ser viable. Esto requiere de una campaña de un año para recién explicar y viabilizar [el proyecto]. Su temor es legítimo y pueden decir por qué les van a enviar el agua si hay otras zonas donde puede salir”, consideró Asmat. En tanto se agrava esta controversia, los trabajos de descolmatación siguen avanzando con la duda sobre dónde saldrá el río. “Mientras no tengamos salida al mar, seguiremos condenados a descolmatar año tras año”, finalizó.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/piura-ante-una-tormenta-perfecta-el-nino-se-acerca-con-el-dengue-activo-y-obras-aun-inconclusas-apuesplan-noticia/</t>
+          <t>https://eltiempo.pe/local/la-descolmatacion-no-servira-sin-adecuado-desfogue-del-rio-piura/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Piura: lluvias intensas con descargas eléctricas seguirán desde hoy hasta el domingo 25 de octubre, según Senamhi</t>
+          <t>Facultades ayudan, pero no resuelven el problema de planificación de obras en Piura</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) emitió el aviso meteorológico N° 430 de nivel naranja sobre lluvias intensas en la región Piura y la costa norte del país. La alerta que incluye posibilidad de descargas eléctricas rige desde el viernes 23 de octubre hasta el domingo 25 de octubre. El fenómeno afectará principalmente a Tumbes y a la costa interior piurana con lluvias de moderada a fuerte intensidad. Asimismo, la sierra norte superior a los 2.800 m.s.n.m. registrará posible caída de granizo durante el evento. Las precipitaciones llegarán acompañadas de descargas eléctricas frecuentes en diversos sectores del norte peruano. Los meteorólogos prevén además ráfagas de viento con velocidades cercanas a los 40 km/h. La costa norte registrará acumulados diarios de lluvia de 2 a 14 mm/día el viernes 23 de octubre. Los valores subirán entre 2 y 15 mm/día el sábado 24 de octubre y alcanzarán hasta 17 mm/día el domingo 25. La sierra norte presentará acumulados de lluvia entre 10 y 23 mm/día durante la primera jornada del aviso. Las cifras máximas en la sierra septentrional ascenderán a 25 mm/día durante el sábado 24 de octubre y el domingo 25 de octubre. Senamhi mantiene una vigilancia hidrometeorológica permanente en Piura ante el registro de lluvias y la presencia de El Niño Costero. El organismo informó que realiza un seguimiento continuo de las estaciones para emitir pronósticos oportunos a las autoridades regionales. La entidad precisó que las lluvias de El Niño Costero muestran una distribución espacial variable en sectores cercanos. Cada estación mide el volumen pluviométrico en su punto específico con procedimientos técnicos bajo estándares internacionales.</t>
+          <t>Se aprobaron las facultades legislativas al Poder Ejecutivo en materia de lucha contra la criminalidad y la prevención frente al Fenómeno de El Niño. Entre los puntos aprobados están la ayuda humanitaria directa del Instituto Nacional de Defensa Civil (INDECI) durante los primeros 15 días de una emergencia, el uso de Obras por Impuestos para reducir el riesgo de desastres y la expropiación de predios. Con ello, vale la pena preguntarse cómo va la ejecución de la inversión pública en Piura y qué cambios cabría esperar antes de que acabe el año. Este año la inversión pública en estos dos frentes ha avanzado de manera desigual. Según el Ministerio de Economía y Finanzas (MEF), el dinero para obras de seguridad ciudadana del Gobierno Regional y las municipalidades pasó de S/ 6.9 millones al empezar el año a S/ 51.6 millones al cierre de septiembre, es decir, se multiplicó por 7.5. Sin embargo, el Gobierno Regional ha gastado apenas el 8.1% de lo que tiene asignado en esas obras, mientras que las municipalidades llevan 68.3%. En prevención frente a desastres, el dinero para obras bajó de S/ 55.2 a S/ 49.8 millones y la ejecución llega a la mitad (49.0%). En ese descenso pesa el drenaje pluvial del cercado de la ciudad de Piura, cuyo presupuesto pasó de S/ 43.1 millones a S/ 14.4 millones entre enero y septiembre, un recorte de dos tercios. Es menos dinero para una obra clave justo cuando el Comité Multisectorial ENFEN, que mantiene la alerta de El Niño costero, prevé que su magnitud extraordinaria se mantenga hasta enero de 2027 y que haya lluvias por encima de lo normal en la costa norte entre octubre y diciembre. A este rezago se suman las obras paralizadas, que no son solo de seguridad o prevención, pero ilustran el panorama de la inversión en Piura. El Gobierno Regional y las municipalidades suman 73 obras paralizadas en todos los sectores, con un saldo de inversión de S/ 531 millones. Ninguna se detuvo por falta de terreno o interferencias, que son los casos que buscan evitar las nuevas reglas de expropiación; casi todas (69, el 95%) se detuvieron por causas que las medidas aprobadas no buscan resolver, principalmente incumplimiento de contrato (42 obras, con S/ 416 millones) y controversias o arbitrajes (14 obras). Entre las paralizadas figuran 22 obras de la “Reconstrucción con Cambios”, el plan posterior al Niño Costero de 2017, con S/ 324 millones de saldo. La pregunta de fondo es si estas facultades corregirán lo que hasta ahora ha fallado. Las medidas aprobadas sí ayudan: agilizan la ayuda humanitaria en emergencias, abren una vía de financiamiento con Obras por Impuestos y facilitan la compra de terrenos. Pero no cambian cómo se programan, presupuestan y supervisan las obras. Y como el Ejecutivo tendría hasta 90 días calendario para emitir los decretos, es poco probable que modifiquen el rezago en lo que resta de 2026. Los problemas de Piura se parecen más a fallas de programación del gasto y de gestión de contratos: más de 8 de cada 10 soles de las obras de seguridad se incorporaron después de iniciado el año, la obra de drenaje clave perdió dos tercios de su presupuesto cuando se acerca El Niño y 42 obras se detuvieron por incumplimiento de contrato. Esperamos que las autoridades regionales y municipales que asumirán en 2027 aprendan de lo ocurrido y mejoren la programación y la gestión de las obras desde el primer día de su mandato.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/piura-lluvias-intensas-con-descargas-electricas-seguiran-desde-hoy-hasta-el-domingo-25-de-octubre-segun-senamhi-apuesplan-ultimas-noticia/</t>
+          <t>https://eltiempo.pe/local/facultades-ayudan-pero-no-resuelven-el-problema-de-planificacion-de-obras-en-piura/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -1889,24 +1895,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Desastre avisado</t>
+          <t>Piura inundada en inicio de El Niño: ¿qué riesgo se prevé para su agricultura y carreteras?</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Según la ingeniera Grinia Ávalos, jefa institucional del Senamhi, las precipitaciones registradas entre el lunes y el martes en Piura corresponden al segundo episodio de lluvias asociado al fenómeno de El Niño (el primero fue el 24 de setiembre y afectó especialmente a Máncora). Esta vez, fueron diversas avenidas y viviendas de la ciudad norteña las que sufrieron las consecuencias del aguacero. Como se sabe, esto es solo el principio del evento que nos golpeará en los próximos meses, pero permite hacerse una idea de la capacidad de respuesta de los distintos estamentos del Estado frente al desafío que tienen por delante. Es sintomático, en ese sentido, que el Congreso haya tardado en aprobar las facultades solicitadas precisamente para lidiar con esta emergencia, mientras la naturaleza ya comienza a causar estragos… En Piura, concretamente, estas primeras lluvias se dan cuando las intervenciones de drenaje y descolmatación no han concluido. Uno de los proyectos pendientes es el drenaje pluvial del centro histórico, a cargo del Gobierno Regional de Piura y cuya ejecución arrastra retrasos, ampliaciones de plazo y adicionales presupuestales. Por el lado de las descolmataciones, se programaron en la región 21 intervenciones que comprenden 49,35 kilómetros de cauces de ríos y quebradas. Y, de acuerdo con información oficial, en el tramo Los Ejidos-Puente Bolognesi, los trabajos registran un avance del 100%, en tanto el volumen de descolmatación alcanza el 85,30%. Sin embargo, los avances reportados no son uniformes en todos los sectores. Las intervenciones en El Milagro-La Encantada y Piedra Negra, por ejemplo, registran avances de solo 27,59% y 20,73%. En lo que concierne a las infraestructuras de servicios básicos, de un total de 135 evaluadas en cinco regiones del norte del país, la Superintendencia Nacional de Servicios de Saneamiento (Sunass) ha identificado 101 de agua potable y saneamiento en riesgo crítico. Ante este escenario, el organismo ha recomendado a las empresas prestadoras de tales servicios activar sus planes de gestión reactiva, garantizar la disponibilidad de grupos electrógenos y equipos de respaldo, así como adoptar medidas de protección de las instalaciones críticas frente a posibles lluvias e inundaciones. La información disponible, en suma, sugiere que, si bien se están tomando acciones preventivas, estas van a resultar insuficientes para capear las dimensiones de la catástrofe climática que tenemos ad portas y cuya llegada conocíamos de meses atrás. Un desastre avisado que, lamentablemente, sí dañará a la gente.</t>
+          <t>Los aniegos e inundaciones que en los dos últimos días afectaron a seis distritos del departamento de Piura parecen ser apenas un anticipo de los desastres de mayor envergadura que trae bajo el brazo el fenómeno de El Niño (FEN) de magnitud extraordinario, a juzgar por proyecciones oficiales. Este fin de semana, la Comisión Encargada del Estudio Nacional del Fenómeno El Niño (Enfen) emitió un nuevo comunicado (N°18) en el que alertó que, para lo que resta del 2026, se irán incrementando las lluvias por encima de lo normal en la costa norte, costa central y la sierra norte occidental, con lluvias localizadas de moderada a fuerte intensidad en el norte. Asimismo, previó que se registren caudales superiores a lo normal, principalmente, desde noviembre, en los ríos Tumbes, Chira, Piura, La Leche y Jequetepeque, en el norte del país; en tanto que las temperaturas del aire alcanzan posibles nuevos récords hasta el verano. Ya el ministro de Salud, Luis Dyer, ha advertido que el fenómeno de El Niño podría provocar una sensación térmica de hasta 45 grados centígrados en el país, aunque ese pronóstico aún está en proceso de verificación. Desde el Servicio Nacional de Meteorología e Hidrología (Senamhi) refirieron que, en efecto, existe la posibilidad de la llegada de episodios de lluvia de mayor intensidad en el norte del país, en la medida que se concrete el acoplamiento del calentamiento del océano y los sistemas atmosféricos. Explicaron que se registró un acumulado de 14.7 litros de agua por metro cuadrado en la localidad de El Partidor, en Piura. Sin embargo, tras el acoplamiento entre el mar y la atmósfera, el volumen de lluvia podría incrementarse en pocas horas hasta 200 litros por metro cuadrado. Esto significa que, pese a los aniegos ya registrados en Piura, las lluvias más extremas todavía están por llegar en esa parte entre lo que resta del 2026 y el verano del 2027. Según el último mapa de escenarios de riesgos por lluvias elaborado por el Centro Nacional de Prevención de Riesgo de Desastres (Cenepred), solo en el departamento de Piura se han identificado 126 puntos críticos por inundaciones que se pueden activar por lluvias sobre lo normal y aumento de caudales de ríos en el próximo verano. Asimismo, se prevé que siete ríos que desembocan en el océano Pacífico tienen perspectivas de caudales sobre lo normal entre enero y febrero del 2027, entre ellos los ríos Tumbes, Chira, Piura, además de los ríos Lambayeque, Jequetepeque, Chicama y Santa, con anomalías sobre lo normal entre 50% a 100%. En base a esa data, el Cenepred identificó que 727 poblados pertenecientes a 16 distritos de la región Piura se encuentran en riesgo muy alto de ser afectados por inundaciones, al igual que 317,730 viviendas que albergan a 1.1 millones de personas, 190 establecimientos de salud y 2,111 locales educativos. En ese mismo nivel de peligro ubica a un total de 229,996 hectáreas de superficie agrícola y 2,501 kilómetros de vías, y una central hidroeléctrica, ubicados en esa misma región. En un segundo escenario de riesgo de nivel alto por inundaciones, el Cenepred ubicó a otro grupo de 816 centros poblados pertenecientes a 24 distritos piuranos, donde se sitúan 197,486 viviendas habitadas por 699,772 personas, además de 132,023 hectáreas agrícolas y 2,716 kilómetros de vías. Ambos escenarios suman un total de 40 distritos, 515,216 viviendas habitadas por 1.8 millones de personas, más 332 establecimientos de salud y 3,485 locales educativos, así como 362,019 hectáreas de cultivo y 5,217 kilómetros de vías en riesgo entre alto y muy alto de ser afectados por inundaciones. Eso significa que el 61.54% del total de distritos de Piura están en riesgo alto y muy alto de ser anegados tras las intensas lluvias, así como el 55.12% de sus centros poblados y el 87.04% de la población de esa región. Asimismo, quiere decir que el 50.04% de su superficie agrícola y el 58.45% de sus carreteras podrían enfrentar también esos mismos niveles de peligro. Por su parte, Geovani Diez, presidente del Gremio de Transportes y Logística (GTL), refirió que las intensas lluvias en Piura provocaron desbordes en carreteras de penetración, pero no provocaron daños de gravedad. De momento, tampoco se afectó el acceso a la Panamericana Norte y no hubo impacto importante al transporte de carga. Sin embargo, refirió que, preocupados por esta situación, sus dirigentes prevén reunirse en las próximas horas con autoridades de Piura para ver el impacto que puede traer el FEN en el transporte de mercancías, en particular las de agroexportación, en ruta al puerto de Paita, dado el riesgo para las vías en zonas como Tambo Grande, Chulucanas, Chalaco, entre otras, que se dañaron en el episodio del 2017. A su turno, Javier Marchese, presidente de la Unión Nacional de Transportistas de Carga en Camiones (UNT-Perú), reclamó que, si bien el Gobierno realiza obras de descolmatación en ríos del norte, no hay proyectos de prevención en zonas como la de Bayóvar (Piura), donde se suelen registrar inundaciones que afectan las carreteras. Carlos León, economista de la Red de Estudios para el Desarrollo (Redes), advirtió que no sólo las lluvias intensas, sino las altas temperaturas que se registran en Piura, van a afectar la cosecha de limón, mango, la palta, los arándanos, entre otros cultivos de agroexportación. A ello le sumó los daños que inundaciones o desbordes pueden causar en la infraestructura de transporte vial en esa región, como sucedió en el FEN del 2017, pues las más vulnerables son las rutas vecinales por donde sale la cosecha de productos de agroexportación que luego se embarcan por el puerto de Paita, así como las rutas desde otras regiones como Lambayeque. En el caso de Lambayeque, a diferencia de Piura, observó que el problema es más bien la escasez de lluvias, que mantiene sus reservorios a un tercio de su capacidad de almacenar agua, lo cual podría poner en riesgo la siguiente campaña agrícola de esa región. En cualquier caso, como los pronósticos del FEN apuntan a mayores impactos en el verano entrante, para el experto, los mayores efectos negativos en la agricultura y la agroexportación en regiones del norte se verán todavía en el 2027.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/opinion/editorial/primeras-lluvias-en-piura-confirman-los-peores-temores-sobre-el-meganino-noticia/</t>
+          <t>https://gestion.pe/economia/piura-riesgo-de-inundaciones-que-trae-el-nino-amenaza-al-87-de-su-poblacion-en-el-verano-noticia/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gestión</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -1914,24 +1920,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Piura inundada en inicio de El Niño: ¿qué riesgo se prevé para su agricultura y carreteras?</t>
+          <t>Ministra de la Mujer: «Piura está hecha un desastre, las calles están en arena; culpa de Madrid y Neyra»</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Los aniegos e inundaciones que en los dos últimos días afectaron a seis distritos del departamento de Piura parecen ser apenas un anticipo de los desastres de mayor envergadura que trae bajo el brazo el fenómeno de El Niño (FEN) de magnitud extraordinario, a juzgar por proyecciones oficiales. Este fin de semana, la Comisión Encargada del Estudio Nacional del Fenómeno El Niño (Enfen) emitió un nuevo comunicado (N°18) en el que alertó que, para lo que resta del 2026, se irán incrementando las lluvias por encima de lo normal en la costa norte, costa central y la sierra norte occidental, con lluvias localizadas de moderada a fuerte intensidad en el norte. Asimismo, previó que se registren caudales superiores a lo normal, principalmente, desde noviembre, en los ríos Tumbes, Chira, Piura, La Leche y Jequetepeque, en el norte del país; en tanto que las temperaturas del aire alcanzan posibles nuevos récords hasta el verano. Ya el ministro de Salud, Luis Dyer, ha advertido que el fenómeno de El Niño podría provocar una sensación térmica de hasta 45 grados centígrados en el país, aunque ese pronóstico aún está en proceso de verificación. Desde el Servicio Nacional de Meteorología e Hidrología (Senamhi) refirieron que, en efecto, existe la posibilidad de la llegada de episodios de lluvia de mayor intensidad en el norte del país, en la medida que se concrete el acoplamiento del calentamiento del océano y los sistemas atmosféricos. Explicaron que se registró un acumulado de 14.7 litros de agua por metro cuadrado en la localidad de El Partidor, en Piura. Sin embargo, tras el acoplamiento entre el mar y la atmósfera, el volumen de lluvia podría incrementarse en pocas horas hasta 200 litros por metro cuadrado. Esto significa que, pese a los aniegos ya registrados en Piura, las lluvias más extremas todavía están por llegar en esa parte entre lo que resta del 2026 y el verano del 2027. Según el último mapa de escenarios de riesgos por lluvias elaborado por el Centro Nacional de Prevención de Riesgo de Desastres (Cenepred), solo en el departamento de Piura se han identificado 126 puntos críticos por inundaciones que se pueden activar por lluvias sobre lo normal y aumento de caudales de ríos en el próximo verano. Asimismo, se prevé que siete ríos que desembocan en el océano Pacífico tienen perspectivas de caudales sobre lo normal entre enero y febrero del 2027, entre ellos los ríos Tumbes, Chira, Piura, además de los ríos Lambayeque, Jequetepeque, Chicama y Santa, con anomalías sobre lo normal entre 50% a 100%. En base a esa data, el Cenepred identificó que 727 poblados pertenecientes a 16 distritos de la región Piura se encuentran en riesgo muy alto de ser afectados por inundaciones, al igual que 317,730 viviendas que albergan a 1.1 millones de personas, 190 establecimientos de salud y 2,111 locales educativos. En ese mismo nivel de peligro ubica a un total de 229,996 hectáreas de superficie agrícola y 2,501 kilómetros de vías, y una central hidroeléctrica, ubicados en esa misma región. En un segundo escenario de riesgo de nivel alto por inundaciones, el Cenepred ubicó a otro grupo de 816 centros poblados pertenecientes a 24 distritos piuranos, donde se sitúan 197,486 viviendas habitadas por 699,772 personas, además de 132,023 hectáreas agrícolas y 2,716 kilómetros de vías. Ambos escenarios suman un total de 40 distritos, 515,216 viviendas habitadas por 1.8 millones de personas, más 332 establecimientos de salud y 3,485 locales educativos, así como 362,019 hectáreas de cultivo y 5,217 kilómetros de vías en riesgo entre alto y muy alto de ser afectados por inundaciones. Eso significa que el 61.54% del total de distritos de Piura están en riesgo alto y muy alto de ser anegados tras las intensas lluvias, así como el 55.12% de sus centros poblados y el 87.04% de la población de esa región. Asimismo, quiere decir que el 50.04% de su superficie agrícola y el 58.45% de sus carreteras podrían enfrentar también esos mismos niveles de peligro. Por su parte, Geovani Diez, presidente del Gremio de Transportes y Logística (GTL), refirió que las intensas lluvias en Piura provocaron desbordes en carreteras de penetración, pero no provocaron daños de gravedad. De momento, tampoco se afectó el acceso a la Panamericana Norte y no hubo impacto importante al transporte de carga. Sin embargo, refirió que, preocupados por esta situación, sus dirigentes prevén reunirse en las próximas horas con autoridades de Piura para ver el impacto que puede traer el FEN en el transporte de mercancías, en particular las de agroexportación, en ruta al puerto de Paita, dado el riesgo para las vías en zonas como Tambo Grande, Chulucanas, Chalaco, entre otras, que se dañaron en el episodio del 2017. A su turno, Javier Marchese, presidente de la Unión Nacional de Transportistas de Carga en Camiones (UNT-Perú), reclamó que, si bien el Gobierno realiza obras de descolmatación en ríos del norte, no hay proyectos de prevención en zonas como la de Bayóvar (Piura), donde se suelen registrar inundaciones que afectan las carreteras. Carlos León, economista de la Red de Estudios para el Desarrollo (Redes), advirtió que no sólo las lluvias intensas, sino las altas temperaturas que se registran en Piura, van a afectar la cosecha de limón, mango, la palta, los arándanos, entre otros cultivos de agroexportación. A ello le sumó los daños que inundaciones o desbordes pueden causar en la infraestructura de transporte vial en esa región, como sucedió en el FEN del 2017, pues las más vulnerables son las rutas vecinales por donde sale la cosecha de productos de agroexportación que luego se embarcan por el puerto de Paita, así como las rutas desde otras regiones como Lambayeque. En el caso de Lambayeque, a diferencia de Piura, observó que el problema es más bien la escasez de lluvias, que mantiene sus reservorios a un tercio de su capacidad de almacenar agua, lo cual podría poner en riesgo la siguiente campaña agrícola de esa región. En cualquier caso, como los pronósticos del FEN apuntan a mayores impactos en el verano entrante, para el experto, los mayores efectos negativos en la agricultura y la agroexportación en regiones del norte se verán todavía en el 2027.</t>
+          <t>Las condiciones de las calles de Piura tras las lluvias volvieron al centro de la discusión política. La ministra de la Mujer, Mara Seminario, cuestionó el estado de las vías y responsabilizó al exalcalde Gabriel Madrid y al gobernador regional, Luis Neyra León, por la situación que, según sus declaraciones, enfrenta la ciudad. “Piura está hecha un desastre, las calles de Piura están en arena”, manifestó la funcionaria en Willax TV al referirse a las consecuencias de las precipitaciones. Durante su intervención, también cuestionó la actuación de las autoridades responsables de la gestión municipal y regional. Ministra cuestiona las calles de Piura tras las lluvias En su pronunciamiento, la ministra señaló que las precipitaciones registradas durante la noche o la madrugada dejaron en evidencia el estado de las vías. Según sus palabras, algunos sectores presentan acumulación de arena y condiciones que dificultan la circulación. “Esto debe ser un lodazal hoy día. ¿Culpa de quién? De un alcalde llamado Gabriel Madrid y de un presidente regional llamado Luis Neyra León”, expresó Mara Seminario. La funcionaria dirigió sus críticas a las autoridades que tienen o tuvieron responsabilidades en la administración pública de la provincia y la región. En particular, cuestionó la gestión de Madrid, exalcalde de Piura, y la de Neyra, quien ocupa el cargo de gobernador regional. Críticas a Gabriel Madrid y Luis Neyra León Durante su intervención, la ministra también hizo referencia a la salida de Gabriel Madrid de la Municipalidad Provincial de Piura y cuestionó la gestión del gobernador regional Luis Neyra León. “El Madrid ya se fue, pero Neyra se va a ir tranquilo a su casa sin haber hecho nada”, sostuvo la funcionaria, en una de las frases más críticas de su pronunciamiento. ¿Qué responsabilidades tienen el Gobierno Regional y la municipalidad? En su declaración, la ministra sostuvo que los gobiernos regionales tienen competencias delegadas de distintos sectores y cuestionó que, a su juicio, la intervención del Gobierno central esté asumiendo gran parte de las acciones necesarias. “La gente se olvida que los gobiernos regionales tienen competencias delegadas de todos los sectores. El Gobierno central está haciendo todo y más”, afirmó. La distribución de responsabilidades entre los niveles de gobierno depende de las competencias establecidas por las normas y de las características de cada intervención. Los municipios tienen funciones vinculadas con la gestión local, mientras que los gobiernos regionales conducen políticas, programas y proyectos dentro de sus atribuciones.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://gestion.pe/economia/piura-riesgo-de-inundaciones-que-trae-el-nino-amenaza-al-87-de-su-poblacion-en-el-verano-noticia/</t>
+          <t>https://eltiempo.pe/local/ministra-de-la-mujer-piura-esta-hecha-un-desastre-las-calles-estan-en-arena-culpa-de-madrid-y-neyra/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gestión</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -1939,24 +1945,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Editorial de Gestión: Las lluvias no esperan</t>
+          <t>Desastre avisado</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Las lluvias de esta semana han vuelto a inundar calles y viviendas de Piura, perjudicar negocios y dificultar el tránsito. Los registros de precipitación varían entre localidades, pero algunos aniegos ocurrieron con acumulados relativamente modestos. Si las primeras lluvias ya provocan estos problemas, ¿qué sucederá cuando llegue el período de mayor intensidad? El Enfen prevé lluvias superiores a lo normal en la costa norte durante los próximos meses y el verano del 2027, así como mayores caudales en varios ríos desde noviembre. También considera más probable que El Niño costero mantenga una magnitud extraordinaria hasta enero. Esta calificación se refiere al calentamiento del mar, no a la intensidad de cada lluvia. Pero la advertencia es suficientemente seria. La vulnerabilidad de Piura tiene explicaciones concretas. Por ejemplo, el proyecto integral de drenaje para Piura, Castilla, Catacaos y Veintiséis de Octubre obtuvo viabilidad recién en junio. El drenaje del centro histórico, a cargo del Gobierno Regional, reporta El Comercio, acumula retrasos. Entretanto, las intervenciones de limpieza y descolmatación avanzan a ritmos distintos. El Colegio de Ingenieros de Piura ha cuestionado expresamente la demora de los proyectos integrales de drenaje pluvial y ha exigido a la Autoridad Nacional de Infraestructura (ANIN) explicar las razones de los retrasos. También pide evaluar técnicamente los sistemas alternativos de evacuación de aguas instalados en el centro de la ciudad, identificar sus deficiencias y acelerar la culminación de las calles intervenidas. El gremio advierte, además, que siguen pendientes reparaciones de defensas ribereñas. Son observaciones que requieren respuestas urgentes de las autoridades. El costo de la imprevisión ya alcanza al comercio y al transporte. La continuidad de las lluvias amenaza además los accesos a zonas agrícolas, la circulación de mercancías y otras actividades productivas. El Gobierno ha desplegado motobombas y sistemas provisionales para evacuar el agua. Son acciones necesarias, pero que no reemplazan la infraestructura pendiente. Tampoco basta con que el Gobierno de Keiko Fujimori atribuya los problemas a gestiones anteriores. La ANIN debe precisar cuándo avanzará el drenaje integral; el Gobierno Regional de Piura, explicar los retrasos de sus obras; y las municipalidades, asegurar el mantenimiento y la respuesta en los puntos críticos. La prevención exige acelerar lo que todavía puede ejecutarse antes del verano. Las lluvias actuales son una advertencia que no se puede desatender.</t>
+          <t>Según la ingeniera Grinia Ávalos, jefa institucional del Senamhi, las precipitaciones registradas entre el lunes y el martes en Piura corresponden al segundo episodio de lluvias asociado al fenómeno de El Niño (el primero fue el 24 de setiembre y afectó especialmente a Máncora). Esta vez, fueron diversas avenidas y viviendas de la ciudad norteña las que sufrieron las consecuencias del aguacero. Como se sabe, esto es solo el principio del evento que nos golpeará en los próximos meses, pero permite hacerse una idea de la capacidad de respuesta de los distintos estamentos del Estado frente al desafío que tienen por delante. Es sintomático, en ese sentido, que el Congreso haya tardado en aprobar las facultades solicitadas precisamente para lidiar con esta emergencia, mientras la naturaleza ya comienza a causar estragos… En Piura, concretamente, estas primeras lluvias se dan cuando las intervenciones de drenaje y descolmatación no han concluido. Uno de los proyectos pendientes es el drenaje pluvial del centro histórico, a cargo del Gobierno Regional de Piura y cuya ejecución arrastra retrasos, ampliaciones de plazo y adicionales presupuestales. Por el lado de las descolmataciones, se programaron en la región 21 intervenciones que comprenden 49,35 kilómetros de cauces de ríos y quebradas. Y, de acuerdo con información oficial, en el tramo Los Ejidos-Puente Bolognesi, los trabajos registran un avance del 100%, en tanto el volumen de descolmatación alcanza el 85,30%. Sin embargo, los avances reportados no son uniformes en todos los sectores. Las intervenciones en El Milagro-La Encantada y Piedra Negra, por ejemplo, registran avances de solo 27,59% y 20,73%. En lo que concierne a las infraestructuras de servicios básicos, de un total de 135 evaluadas en cinco regiones del norte del país, la Superintendencia Nacional de Servicios de Saneamiento (Sunass) ha identificado 101 de agua potable y saneamiento en riesgo crítico. Ante este escenario, el organismo ha recomendado a las empresas prestadoras de tales servicios activar sus planes de gestión reactiva, garantizar la disponibilidad de grupos electrógenos y equipos de respaldo, así como adoptar medidas de protección de las instalaciones críticas frente a posibles lluvias e inundaciones. La información disponible, en suma, sugiere que, si bien se están tomando acciones preventivas, estas van a resultar insuficientes para capear las dimensiones de la catástrofe climática que tenemos ad portas y cuya llegada conocíamos de meses atrás. Un desastre avisado que, lamentablemente, sí dañará a la gente.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://gestion.pe/opinion/editorial-de-gestion-las-lluvias-no-esperan-noticia/</t>
+          <t>https://elcomercio.pe/opinion/editorial/primeras-lluvias-en-piura-confirman-los-peores-temores-sobre-el-meganino-noticia/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -1964,24 +1970,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vecinos exigen motobombas: más de 6000 vecinos de la urb. Miraflores en riesgo de inundación</t>
+          <t>Editorial de Gestión: Las lluvias no esperan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Vecinos de la urbanización Miraflores, en el distrito de Castilla exigen a la municipalidad distrital el mantenimiento del Sistema de evacuación de aguas pluviales y la instalación de motobombas para su funcionamiento; de lo contrario, y de volver a registrarse lluvias como la de los días anteriores existe el riesgo de inundación en la zona. El presidente de la Junta Vecinal Comunal (Juveco) de Miraflores, Maximiliano Flores Cevallos, señaló que las bombas destinadas a este sector aún no han sido instaladas, pese a las reiteradas solicitudes presentadas desde hace varios meses. Por ello, exhortó al alcalde de Castilla, Julio Vásquez Alberca, a disponer las acciones necesarias y no se ponga en riesgo a los más de 6.000 vecinos de dicha urbanización. Agregó que durante las últimas lluvias la municipalidad llevó una bomba pequeña pero solo sirvió para salir de la emergencia.</t>
+          <t>Las lluvias de esta semana han vuelto a inundar calles y viviendas de Piura, perjudicar negocios y dificultar el tránsito. Los registros de precipitación varían entre localidades, pero algunos aniegos ocurrieron con acumulados relativamente modestos. Si las primeras lluvias ya provocan estos problemas, ¿qué sucederá cuando llegue el período de mayor intensidad? El Enfen prevé lluvias superiores a lo normal en la costa norte durante los próximos meses y el verano del 2027, así como mayores caudales en varios ríos desde noviembre. También considera más probable que El Niño costero mantenga una magnitud extraordinaria hasta enero. Esta calificación se refiere al calentamiento del mar, no a la intensidad de cada lluvia. Pero la advertencia es suficientemente seria. La vulnerabilidad de Piura tiene explicaciones concretas. Por ejemplo, el proyecto integral de drenaje para Piura, Castilla, Catacaos y Veintiséis de Octubre obtuvo viabilidad recién en junio. El drenaje del centro histórico, a cargo del Gobierno Regional, reporta El Comercio, acumula retrasos. Entretanto, las intervenciones de limpieza y descolmatación avanzan a ritmos distintos. El Colegio de Ingenieros de Piura ha cuestionado expresamente la demora de los proyectos integrales de drenaje pluvial y ha exigido a la Autoridad Nacional de Infraestructura (ANIN) explicar las razones de los retrasos. También pide evaluar técnicamente los sistemas alternativos de evacuación de aguas instalados en el centro de la ciudad, identificar sus deficiencias y acelerar la culminación de las calles intervenidas. El gremio advierte, además, que siguen pendientes reparaciones de defensas ribereñas. Son observaciones que requieren respuestas urgentes de las autoridades. El costo de la imprevisión ya alcanza al comercio y al transporte. La continuidad de las lluvias amenaza además los accesos a zonas agrícolas, la circulación de mercancías y otras actividades productivas. El Gobierno ha desplegado motobombas y sistemas provisionales para evacuar el agua. Son acciones necesarias, pero que no reemplazan la infraestructura pendiente. Tampoco basta con que el Gobierno de Keiko Fujimori atribuya los problemas a gestiones anteriores. La ANIN debe precisar cuándo avanzará el drenaje integral; el Gobierno Regional de Piura, explicar los retrasos de sus obras; y las municipalidades, asegurar el mantenimiento y la respuesta en los puntos críticos. La prevención exige acelerar lo que todavía puede ejecutarse antes del verano. Las lluvias actuales son una advertencia que no se puede desatender.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/vecinos-exigen-motobombas-mas-de-6000-vecinos-de-la-urb-miraflores-en-riesgo-de-inundacion/</t>
+          <t>https://gestion.pe/opinion/editorial-de-gestion-las-lluvias-no-esperan-noticia/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -1989,24 +1995,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cámara de Comercio y Colegio de Ingenieros exigen intervención inmediata en Chutuque</t>
+          <t>Piura: lluvias intensas con descargas eléctricas seguirán desde hoy hasta el domingo 25 de octubre, según Senamhi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>El presidente de la Cámara de Comercio y Producción de Piura, Javier Bereche, lamentó que hasta la fecha no se inicien los trabajos en la ampliación del canal de Chutuque que pueda evitar una posible inundación y afectación a la población. Señaló que ya no hay tiempo para sacar el tapón rocoso de Chutuque, pero sí abrir el canal de derivación de Chutuque hacia lagunas. Indicó que de no ejecutarse la intervención se podría registrar una catástrofe más adelante. En tanto, el Colegio de Ingenieros emitió un pronunciamiento para exigir acciones concretas y obras urgentes frente al riesgo de inundaciones. Plantean acciones inmediatas en la intervención de Chutuque, reparación de las defensas ribereñas, evaluar la efectividad de los SARE y agilizar la culminación de las calles intervenidas en el centro de la ciudad, entre otras demandas.</t>
+          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) emitió el aviso meteorológico N° 430 de nivel naranja sobre lluvias intensas en la región Piura y la costa norte del país. La alerta que incluye posibilidad de descargas eléctricas rige desde el viernes 23 de octubre hasta el domingo 25 de octubre. El fenómeno afectará principalmente a Tumbes y a la costa interior piurana con lluvias de moderada a fuerte intensidad. Asimismo, la sierra norte superior a los 2.800 m.s.n.m. registrará posible caída de granizo durante el evento. Las precipitaciones llegarán acompañadas de descargas eléctricas frecuentes en diversos sectores del norte peruano. Los meteorólogos prevén además ráfagas de viento con velocidades cercanas a los 40 km/h. La costa norte registrará acumulados diarios de lluvia de 2 a 14 mm/día el viernes 23 de octubre. Los valores subirán entre 2 y 15 mm/día el sábado 24 de octubre y alcanzarán hasta 17 mm/día el domingo 25. La sierra norte presentará acumulados de lluvia entre 10 y 23 mm/día durante la primera jornada del aviso. Las cifras máximas en la sierra septentrional ascenderán a 25 mm/día durante el sábado 24 de octubre y el domingo 25 de octubre. Senamhi mantiene una vigilancia hidrometeorológica permanente en Piura ante el registro de lluvias y la presencia de El Niño Costero. El organismo informó que realiza un seguimiento continuo de las estaciones para emitir pronósticos oportunos a las autoridades regionales. La entidad precisó que las lluvias de El Niño Costero muestran una distribución espacial variable en sectores cercanos. Cada estación mide el volumen pluviométrico en su punto específico con procedimientos técnicos bajo estándares internacionales.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/camara-de-comercio-y-colegio-de-ingenieros-exigen-intervencion-inmediata-en-chutuque/</t>
+          <t>https://elcomercio.pe/peru/piura/piura-lluvias-intensas-con-descargas-electricas-seguiran-desde-hoy-hasta-el-domingo-25-de-octubre-segun-senamhi-apuesplan-ultimas-noticia/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -2014,17 +2020,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Una lluvia de siete milímetros inundó calles y obras, y puso a Piura de cabeza</t>
+          <t>Piura ante una tormenta perfecta: El Niño se acerca con el dengue activo y obras aún inconclusas</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Piura soportó una precipitación de 7 milímetros (mm), según lo informó la jefa del Senamhi, Grinia Ávalos Roldán, y quedó demostrada una vez más la alta vulnerabilidad en que se encuentra la ciudad, que quedó convertida en un desastre con calles y avenidas inundadas, colegios afectados y sectores sin energía eléctrica a raíz de la caída de postes, como se evidenció en la avenida Santa Rosa, en el asentamiento del mismo nombre. Además, fueron reportados árboles caídos, el centro de abastos inundado y centenares de vecinos sin agua por la paralización de pozos, como fue el caso de Las Dalias, Santa Margarita, Néstor Martos, Nuevo Vicús y el reservorio Lourdes. ¿Se imagina qué pasará si el registro de lluvia llega a los 300 mm? Un pronóstico nada exagerado. Y es que el vocero del Senamhi, Nelson Quispe, ya alertó que las lluvias en la costa norte del Perú podrían alcanzar acumulados de hasta 300 milímetros en un solo día durante el verano de 2027, con lo cual urge que el Ejecutivo y las autoridades locales eviten una catástrofe más adelante y los proyectos realmente funcionen de forma oportuna, como el caso de los SARE, para salvaguardar a la población. Bajo el agua Precisamente ayer uno de los puntos críticos que se evidenció como todos los años fue el ingreso a la Urb. Ignacio Merino, el cual quedó totalmente inundado. Lo mismo se evidenció en la intersección de la avenida José Aguilar Santisteban con calle Azucenas. En este punto fue tanta la acumulación del agua que se cerró la zona por completo. Aquí el agua ingresó a algunas viviendas y negocios. Los sectores conocidos como Cinco Esquinas y los Dos Grifos en el distrito Veintiséis de Octubre fueron otros de los puntos más críticos por la acumulación del agua durante el día. Esta situación se hubiera evitado con el funcionamiento oportuno de los SARE (Sistema Alternativo de Recolección y Evacuación de Aguas de Lluvias), hecho que fue cuestionado por algunos dirigentes. Rechazan apertura de más calles en el centro Una comitiva de la Defensoría del Pueblo, encabezada por su jefe Walter Galecio, inspeccionó ayer los trabajos de reconstrucción en el Centro Histórico de Piura, luego de lo cual exhortó al Gobierno Regional y a la Municipalidad de Piura a suspender la apertura de nuevos frentes de trabajo en otras calles y avenidas, en tanto no se culminen las obras ya iniciadas. El defensor del pueblo también solicitó una reunión de emergencia con la plataforma regional de Defensa Civil para coordinar acciones de contingencia que mitiguen el impacto de El Niño. Entrega parcial Sobre las obras del centro de la ciudad, el asesor del GORE, Jesús Moreno, aseguró que ya no se intervendrá más calles. Adelantó que a fin de mes entregarán pavimentadas las calles Cusco y Libertad, y a fines de noviembre, otras 12. Sobre el caso de los puntos críticos de la Av. Sullana (cruce con Avifap y calle Jacaranda), indicó que ANIN los consideró como parte de su intervención. Truenos causan terror en Sullana Una ligera lluvia registrada durante la madrugada del martes sorprendió a la población de Sullana. La precipitación no generó aniegos en la ciudad; sin embargo, la situación fue diferente en Cieneguillo Sur, donde las lluvias estuvieron acompañadas de fuertes truenos que hicieron temer lo peor a los moradores. En esta zona rural, las precipitaciones continuaron hasta después de las nueve de la mañana, generando preocupación entre las familias. Algunos padres optaron por no enviar a sus hijos a los diferentes colegios ubicados en los centros poblados y caseríos que limitan con la provincia de Piura. Chulucanas Mientras tanto, en Chulucanas se registraron lluvias torrenciales. Esta situación obligó a los comerciantes a cerrar el Mercado Modelo. En tanto, varias calles quedaron inundadas por las precipitaciones. Sin agua y con aniegos La Heroica Villa empieza a sentir los efectos de las lluvias registradas, una situación que genera preocupación entre los vecinos ante la posibilidad de que se intensifiquen las precipitaciones por el anunciado fenómeno El Niño. Las primeras dificultades ya se evidencian en calles con problemas de transitabilidad debido a los aniegos que dejaron varios sectores inundados. A ello se suma, la paralización temporal de pozos de agua potable Cayetano Heredia y Monte Sullón por fallas eléctricas debido a las lluvias. Vecinos también reportaron ayer que varias calles donde aún no se ha repuesto el embloquetado presentan serias dificultades para el tránsito vehicular y peatonal. El agua acumulada tras las lluvias de regular intensidad causa complicaciones y vuelve a poner en evidencia la vulnerabilidad de algunas vías del distrito frente a las precipitaciones que perjudican a la población.</t>
+          <t>Bastó una lluvia de alrededor de 5 horas para demostrar cada una de las falencias que hay en Piura. Un sistema de drenaje que no funciona, calles inundadas, obras inconclusas y además, el peligro del dengue, una enfermedad que ya ha sabido azotar en la región norteña. ¿Por qué Piura vive en un círculo vicioso en el que solo queda esperar que no suceda lo peor? En 2017, en pleno fenómeno de El Niño Costero, más de 50 fallecidos por el dengue. En 2023, año del ciclón Yaku, casi 80 mil casos y 148 muertos. En este 2026, ya se registran más de 13 mil casos acumulados de dengue y 8 defunciones. El panorama para el 2027 no es muy alentador. Las lluvias producidas en los últimas días solo hicieron poner los ojos otra vez en una región que ya sido bastante afectada por los desastres naturales. En urbanizaciones de Piura, Chulucanas y Catacaos también se vieron calles con aniegos. El Senamhi ya advirtió que las lluvias continuarán en los próximos meses con más frecuencia e intensidad. Y ante esa inminente llegada de un clima inclemente, la pregunta es, ¿qué se está haciendo para contener lo más posible los estragos de un Fenómeno El Niño que se preve catastrófico? El dengue, una gran amenaza Edward Pozo, jefe de inteligencia sanitaria de la red asistencial Piura de Essalud, conversó con El Comercio sobre cómo está la región norteña a semanas del Fenómeno de El Niño y tras esta lluvia que ha sido una especie de aviso de lo que podría venir. En los hospitales, habrá unidades de vigilancia intensiva para el dengue, lugares de atención con insumos médicos y medicamentos. Además, se contratará personal que se va a necesitar durante la emergencia. “Las lluvias han sido un aviso de que nos va a afectar bastante en la salud de Piura”. “Lo que se sabe del dengue, es que por lo menos después de dos semanas del periodo lluvioso, es que empiezan a presentarse ya los casos de dengue, en una situación endémica. Pero Piura ya viene con casos de dengue desde el mes de julio, con brotes activos. Y esto es debido al calor y las altas temperaturas. Estas lluvias recientes lo que hacen es agregar una variable más que va a aumentar el riesgo de mayo cantidad de casos (de dengue)” En cuanto a previsiones y cómo prepararse para lo que se pronostica como un FEN de magnitud “fuerte a extraordinaria”, el biólogo señaló que con la data histórica, se han puesto en el peor escenario posible. “El peor fue el del año 2023 con el ciclón Yaku. Essalud tuvo 35 mil casos de dengue. La OPS en su guía nos ha dicho que calculemos con una tasa de ataque de 4.5 a la población. Es decir, el 4.5% de la población se podría enfermar de dengue”. La vacunación como sistema de defensa “La Diresa da parte de esas vacunas a Essalud, pero quien monitorea esas cifras y avances son ellos. A nosotros, como red asistencial Piura - Essalud, se nos dotó de 2.500 vacunas. Ya más del 50% han sido administradas dentro de asegurados del grupo etario de 10 a 20 años. Y estamos haciendo campañas intensas en Morropón, el Bajo Piura y Sullana. Una vez que tengamos eso cubierto, vamos a solicitar más vacunas” Nancy Jiménez, corresponsal en Piura de América Noticias y Canal N, nos responde sobre la incidencia del dengue en la región: “Piura es una ciudad endémica, totalmente. Ahorita estamos en pleno brote. Hay más de 13 mil casos y 9 fallecidos. De ellos, 4 son menores de edad”. La región ante el Fenómeno El Niño y el dengue, una vez más ¿Qué va a pasar ahora que vienen las lluvias? La vulnerabilidad de zonas muy endémicas o de altas transmisión del dengue, como Chulucanas, Sullana, Piura o Castilla, es porque son las más pobladas y por esto, más propensas a desarrollar brotes de la enfermedad. “Los pueblos jóvenes de estas ciudades, que no tienen servicios básicos, van a tener muchos problemas por la acumulación de agua, y peor aún, para disponer de agua potable para su consumo y su higiene personal. Eso con las lluvias se va a agudizar muchísimo. La disponibilidad de agua potable va a ser bastante difícil. Son mucho más vulnerables a tener dengue y también enfermedades respiratorias, micosis o diarrea, por las mismas condiciones que genera este fenómeno”, señaló Edward Pozo. Así está Piura hoy Cuando estuvimos en Piura hace algunos meses, vimos que varias calles del centro histórico lucían rotas y sin avances visibles en las obras. La gente que transitaba por esa zona solo nos mencionaba “eso está así (roto y en un aparente abandono) desde hace tiempo”. Al respecto, nuestra colega Nancy Jiménez añade: “Piura está totalmente destruida, con las pistas que no se puede ni caminar y no solamente el centro de Piura, sino que en la región, en la ciudad, han iniciado una serie de obras ya al término de la gestión. Cierran una vía, la rompen, cierran otra, la rompen, sin ni siquiera restablecer la que rompieron anteriormente. Según la Cámara de Comercio de Piura, por lo menos el 80% de los negocios de la zona se han visto afectados”. Obras que ya debieron culminarse y que registran avances de menos del 40%, SARES (sistemas de recolección y evacuación de aguas de lluvia) del Ministerio de Vivienda que no han tenido la respuesta esperada por parte de las municipalidades, que debido al cierre de sus gestiones, han descuidado estas funciones. Y no, esto no es un “simulacro en seco” como diría el ministro de Defensa, Rafael Belaúnde, que visitó las zonas afectadas en Piura. La región norteña solo está avisando que no está lista y el tiempo sigue corriendo. El Fenómeno de El Niño y el dengue no esperan.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/una-lluvia-de-siete-milimetros-inundo-calles-y-obras-y-puso-a-piura-de-cabeza/</t>
+          <t>https://elcomercio.pe/peru/piura/piura-ante-una-tormenta-perfecta-el-nino-se-acerca-con-el-dengue-activo-y-obras-aun-inconclusas-apuesplan-noticia/</t>
         </is>
       </c>
     </row>
@@ -2064,17 +2070,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Se quedarán sin agua durante una semana por paralización temporal del pozo Los Algarrobos</t>
+          <t>Gobernador de Piura, Luis Neyra, arremete contra ministra de la Mujer: «Reciclada, habla cosas que no son»</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Vecinos de la urbanización Bello Horizonte, Educadores y partes altas del asentamiento humano Los Algarrobos y urbanización Ignacio Merino deberán tomar sus precauciones para abastecerse de agua potable. Y es que EPS Grau emitió ayer un comunicado anunciando la paralización temporal del pozo Los Algarrobos debido a una afectación tanto en el sistema eléctrico como en el equipo de bombeo de la referida fuente. Señalan que dada la emergencia que se presentó en dicho pozo han previsto realizar la reparación correspondiente y se prevé la culminación de la misma para el próximo miércoles 28 de octubre, luego de la cual “se restablecería de manera progresiva la normal distribución de agua potable desde la fuente”. En tanto, culminen los trabajos aseguran que abastecerán a la población con cisternas y un envío de mayor caudal a la zona de cobertura desde la Planta de Tratamiento de Curumuy. Protestan Mientras tanto, ayer un numeroso grupo de moradores del sector Los Médanos en el distrito de Castilla bloqueó la prolongación de la avenida Guardia Civil que conduce la vía Piura-Chulucanas para llamar la atención de la EPS Grau y exigir la continuidad del servicio de agua potable. Y es que señalan que en algunas zonas no cae agua y en otros sectores tienen que levantarse desde las 5:00 a.m para almacenar la poca agua que cae y por horas en sus viviendas.</t>
+          <t>El gobernador regional de Piura, Luis Neyra León , respondió a las críticas de la ministra de la Mujer por el estado de las calles de la ciudad después de las lluvias. Durante sus declaraciones, calificó a la ministra de la Mujer, Mara Seminario, de “reciclada” y la acusó de realizar afirmaciones que, según sostuvo, no corresponden a la realidad de las obras ejecutadas en la región. El intercambio se produce en medio de los cuestionamientos por la respuesta de las autoridades ante las precipitaciones y las dificultades que enfrentan los ciudadanos para transitar por diferentes sectores de la ciudad. Mientras la ministra responsabilizó al Gobierno Regional y a la Municipalidad Provincial de Piura, Neyra defendió los trabajos realizados en determinadas vías y cuestionó las motivaciones de las críticas. Luis Neyra califica de “reciclada” a ministra de la Mujer El gobernador regional no ocultó su molestia frente a las declaraciones de la ministra. Durante su intervención, cuestionó su trayectoria política y puso en duda las razones detrás de sus pronunciamientos sobre la situación de Piura. “Sale una ministra que ha sido ministra de Merino, reciclada en este gobierno y habla cosas que no son”, manifestó Neyra, quien también planteó interrogantes sobre los intereses que, a su juicio, podrían estar detrás de las críticas dirigidas contra su gestión. El titular del Gobierno Regional de Piura fue más allá y sostuvo que existiría una intención de perjudicar su imagen pública. Según afirmó, distintos sectores estarían actuando para dejar mal parada a la autoridad regional mediante cuestionamientos difundidos en redes sociales. ¿Qué dijo la ministra sobre las lluvias en Piura? La ministra cuestionó las condiciones en las que quedaron las calles de Piura después de las lluvias . En su pronunciamiento, describió problemas en las vías y responsabilizó tanto al alcalde provincial, Gabriel Madrid, como al gobernador regional, Luis Neyra León. “Ayer o ahora en la madrugada ha llovido en Piura y Piura está hecho un desastre. Las calles de Piura están en arena. Esto va a ser un lodazal hoy día. ¿Culpa de quién? De un alcalde llamado Gabriel Madrid y de un presidente regional llamado Luis Neyra León”, manifestó. La funcionaria también cuestionó el desempeño de las autoridades regionales y locales frente a los problemas que afronta la población durante la temporada de lluvias. En esa línea, señaló que el alcalde ya había dejado el cargo, pero que Neyra concluiría su gestión sin haber realizado el trabajo necesario, según su apreciación. Además, recordó que los gobiernos regionales tienen competencias vinculadas con distintos sectores y sostuvo que el Gobierno central viene ejecutando acciones frente a la problemática. Sus declaraciones colocaron nuevamente en el centro del debate la responsabilidad de las autoridades para prevenir inundaciones, mantener las vías en condiciones adecuadas y atender las consecuencias de las precipitaciones en la capital regional. Gobernador defiende obras en la avenida Grau y la calle Don Bosco Frente a los cuestionamientos, Luis Neyra defendió los trabajos realizados en la calle Don Bosco y la avenida Grau. Según explicó, ambas intervenciones cuentan con expedientes técnicos elaborados por el Gobierno Regional de Piura y habrían permitido que el agua discurra hacia los drenes naturales. ¿Por qué hubo problemas en el centro histórico de Piura? El gobernador señaló que las intervenciones en el centro histórico presentaron dificultades porque no se conocía con precisión qué infraestructura existía debajo de las superficies intervenidas. Según explicó, la empresa encargada de los trabajos no podía determinar de antemano todas las condiciones del subsuelo. Por ello, consideró necesario abrir las vías para identificar las estructuras existentes y definir cómo continuar con las labores. “Teníamos que abrir para ver qué es lo que había debajo del centro histórico. Nadie lo sabía”, sostuvo.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/se-quedaran-sin-agua-durante-una-semana-por-paralizacion-temporal-del-pozo-los-algarrobos/</t>
+          <t>https://eltiempo.pe/local/gobernador-de-piura-luis-neyra-arremete-contra-ministra-de-la-mujer-reciclada-y-hablas-cosas-que-no-son/</t>
         </is>
       </c>
     </row>
@@ -2089,17 +2095,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gobernador de Piura, Luis Neyra, arremete contra ministra de la Mujer: «Reciclada, habla cosas que no son»</t>
+          <t>Cuatro sicarios tras los pasos de alcalde electo de Veintiséis de Octubre, Percy Fiestas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>El gobernador regional de Piura, Luis Neyra León , respondió a las críticas de la ministra de la Mujer por el estado de las calles de la ciudad después de las lluvias. Durante sus declaraciones, calificó a la ministra de la Mujer, Mara Seminario, de “reciclada” y la acusó de realizar afirmaciones que, según sostuvo, no corresponden a la realidad de las obras ejecutadas en la región. El intercambio se produce en medio de los cuestionamientos por la respuesta de las autoridades ante las precipitaciones y las dificultades que enfrentan los ciudadanos para transitar por diferentes sectores de la ciudad. Mientras la ministra responsabilizó al Gobierno Regional y a la Municipalidad Provincial de Piura, Neyra defendió los trabajos realizados en determinadas vías y cuestionó las motivaciones de las críticas. Luis Neyra califica de “reciclada” a ministra de la Mujer El gobernador regional no ocultó su molestia frente a las declaraciones de la ministra. Durante su intervención, cuestionó su trayectoria política y puso en duda las razones detrás de sus pronunciamientos sobre la situación de Piura. “Sale una ministra que ha sido ministra de Merino, reciclada en este gobierno y habla cosas que no son”, manifestó Neyra, quien también planteó interrogantes sobre los intereses que, a su juicio, podrían estar detrás de las críticas dirigidas contra su gestión. El titular del Gobierno Regional de Piura fue más allá y sostuvo que existiría una intención de perjudicar su imagen pública. Según afirmó, distintos sectores estarían actuando para dejar mal parada a la autoridad regional mediante cuestionamientos difundidos en redes sociales. ¿Qué dijo la ministra sobre las lluvias en Piura? La ministra cuestionó las condiciones en las que quedaron las calles de Piura después de las lluvias . En su pronunciamiento, describió problemas en las vías y responsabilizó tanto al alcalde provincial, Gabriel Madrid, como al gobernador regional, Luis Neyra León. “Ayer o ahora en la madrugada ha llovido en Piura y Piura está hecho un desastre. Las calles de Piura están en arena. Esto va a ser un lodazal hoy día. ¿Culpa de quién? De un alcalde llamado Gabriel Madrid y de un presidente regional llamado Luis Neyra León”, manifestó. La funcionaria también cuestionó el desempeño de las autoridades regionales y locales frente a los problemas que afronta la población durante la temporada de lluvias. En esa línea, señaló que el alcalde ya había dejado el cargo, pero que Neyra concluiría su gestión sin haber realizado el trabajo necesario, según su apreciación. Además, recordó que los gobiernos regionales tienen competencias vinculadas con distintos sectores y sostuvo que el Gobierno central viene ejecutando acciones frente a la problemática. Sus declaraciones colocaron nuevamente en el centro del debate la responsabilidad de las autoridades para prevenir inundaciones, mantener las vías en condiciones adecuadas y atender las consecuencias de las precipitaciones en la capital regional. Gobernador defiende obras en la avenida Grau y la calle Don Bosco Frente a los cuestionamientos, Luis Neyra defendió los trabajos realizados en la calle Don Bosco y la avenida Grau. Según explicó, ambas intervenciones cuentan con expedientes técnicos elaborados por el Gobierno Regional de Piura y habrían permitido que el agua discurra hacia los drenes naturales. ¿Por qué hubo problemas en el centro histórico de Piura? El gobernador señaló que las intervenciones en el centro histórico presentaron dificultades porque no se conocía con precisión qué infraestructura existía debajo de las superficies intervenidas. Según explicó, la empresa encargada de los trabajos no podía determinar de antemano todas las condiciones del subsuelo. Por ello, consideró necesario abrir las vías para identificar las estructuras existentes y definir cómo continuar con las labores. “Teníamos que abrir para ver qué es lo que había debajo del centro histórico. Nadie lo sabía”, sostuvo.</t>
+          <t>Hace una semana, el alcalde electo de Veintiséis de Octubre, Percy Fiestas Aquino, fue blanco de mensajes extorsivos y de un video amenazante por parte de integrantes de la red criminal La Nueva Generación del Norte. Esta vez, cuatro presuntos sicarios estarían tras los pasos de la nueva autoridad municipal del distrito de Morropón. El maquiavélico plan habría sido detectado por un equipo de detectives de Lima y Piura, cuya labor se mantenía en estricta reserva. Sin embargo, las investigaciones se filtraron y se publicaron en una página de Facebook, lo cual generó preocupación en el Alto Piura. Equipo especial en Morropón Esta información fue confirmada ayer por Miguel Ángel Ruesta Carrasco, alcalde electo de Morropón, quien señaló que un equipo especial de investigadores se encuentra en la zona para poner en marcha un protocolo de seguridad. Se conoció que los agentes llegaron varias veces al inmueble de Miguel Ruesta, quien, por razones de seguridad, permaneció en un lugar desconocido. El objetivo de los custodios era activar inmediatamente un protocolo de rigor. Gatilleros foráneos Miguel Ruesta declaró brevemente que no ha recibido mensajes o llamadas extorsivas y la única fuente es la propia Policía Nacional, la misma que realiza una serie de diligencias y pesquisas en la ciudad de Morropón y rutas de acceso al distrito. Trascendió que serían cuatro gatilleros, dos de Tumbes y otros dos de Trujillo, que supuestamente arribaron al mencionado lugar para efectuar un riguroso seguimiento a la autoridad electa de Morropón, que asumirá funciones el próximo 1 de enero de 2027. La próxima autoridad municipal resaltó que no tiene problemas con nadie y solo queda que todos los vecinos del campo y la ciudad nos unamos para sacar adelante al distrito. Hijo de exalcalde Cabe resaltar que Miguel Ruesta es hijo del extinto profesor Guido Martin Ruesta Taboada, del movimiento político Región Para Todos, quien cumplió funciones de alcalde de Morropón en el período 2015-2018. Guido Ruesta perdió la vida en un accidente de tránsito.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/gobernador-de-piura-luis-neyra-arremete-contra-ministra-de-la-mujer-reciclada-y-hablas-cosas-que-no-son/</t>
+          <t>https://eltiempo.pe/local/cuatro-sicarios-tras-los-pasos-de-alcalde-electo-de-veintiseis-de-octubre-percy-fiestas/</t>
         </is>
       </c>
     </row>
@@ -2114,17 +2120,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Urbanizaciones, mercado y centro de Piura, en riesgo de inundación por dique de La Mariposa</t>
+          <t>Una lluvia de siete milímetros inundó calles y obras, y puso a Piura de cabeza</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>La presidenta Keiko Fujimori aseguró que con los trabajos de descolmatación, el río Piura podría soportar un caudal de 4,000 metros cúbicos por segundo (m3/s); sin embargo, el presidente de la Cámara de Comercio de Piura, Javier Bereche, informó que en el sector La Mariposa (Medio Piura) existe un dique de 700 metros aproximadamente que apenas soportó un caudal de 2,900 m3/s en el 2017, y advirtió que, de no tomarse preventivas, podría ocurrir una catástrofe. Informó que ese dique se construyó en un inicio para salvaguardar a la población de los caseríos de La Mariposa y Los Ejidos de Huan. Dijo que de registrarse un fuerte caudal en los próximos meses no solo estos sectores serían los afectados sino otros más que conforman el “antiguo brazo del río”. “No solo afectaría a los centros poblados, sino que el agua llegará al centro de Piura, porque era un antiguo brazo del río que iba por La Mariposa, salía por Quinta Ana María [...]. Sería inundada incluso la Country, va para el mercado hasta el centro de la ciudad. Lo que quiero decir que el centro de Piura se puede inundar por rebose [del río] y, si se rompe ese dique, ya ni siquiera aguanta los 2,900 m3/s”, indicó. Informó que el presidente del Proyecto Especial Chira Piura, Jorge Garrido Lecca, se ha comprometido a evaluar el caso. Agregó que urge realizar trabajos de reforzamiento y elevar el dique. Pérdida de más de S/15 mil millones En conferencia de prensa, el presidente de la Camco, Javier Bereche, también dio a conocer que a la fecha el Fenómeno El Niño ya va dejando pérdidas de 3 mil millones de soles, donde la agricultura, el sector agroexportación y la pesquería son los sectores más afectados. “En un Niño moderado, nos podría costar 8 mil millones, y si es un Niño extraordinario como lo ha anunciado la presidenta Keiko podría costar 15 mil millones a la región”, señaló. El empresario indicó que en el sector pesca, la afectación se viene dando por la ausencia de especies debido al calentamiento del mar; mientras que el mango y otros productos son afectados también por las altas temperaturas.</t>
+          <t>Piura soportó una precipitación de 7 milímetros (mm), según lo informó la jefa del Senamhi, Grinia Ávalos Roldán, y quedó demostrada una vez más la alta vulnerabilidad en que se encuentra la ciudad, que quedó convertida en un desastre con calles y avenidas inundadas, colegios afectados y sectores sin energía eléctrica a raíz de la caída de postes, como se evidenció en la avenida Santa Rosa, en el asentamiento del mismo nombre. Además, fueron reportados árboles caídos, el centro de abastos inundado y centenares de vecinos sin agua por la paralización de pozos, como fue el caso de Las Dalias, Santa Margarita, Néstor Martos, Nuevo Vicús y el reservorio Lourdes. ¿Se imagina qué pasará si el registro de lluvia llega a los 300 mm? Un pronóstico nada exagerado. Y es que el vocero del Senamhi, Nelson Quispe, ya alertó que las lluvias en la costa norte del Perú podrían alcanzar acumulados de hasta 300 milímetros en un solo día durante el verano de 2027, con lo cual urge que el Ejecutivo y las autoridades locales eviten una catástrofe más adelante y los proyectos realmente funcionen de forma oportuna, como el caso de los SARE, para salvaguardar a la población. Bajo el agua Precisamente ayer uno de los puntos críticos que se evidenció como todos los años fue el ingreso a la Urb. Ignacio Merino, el cual quedó totalmente inundado. Lo mismo se evidenció en la intersección de la avenida José Aguilar Santisteban con calle Azucenas. En este punto fue tanta la acumulación del agua que se cerró la zona por completo. Aquí el agua ingresó a algunas viviendas y negocios. Los sectores conocidos como Cinco Esquinas y los Dos Grifos en el distrito Veintiséis de Octubre fueron otros de los puntos más críticos por la acumulación del agua durante el día. Esta situación se hubiera evitado con el funcionamiento oportuno de los SARE (Sistema Alternativo de Recolección y Evacuación de Aguas de Lluvias), hecho que fue cuestionado por algunos dirigentes. Rechazan apertura de más calles en el centro Una comitiva de la Defensoría del Pueblo, encabezada por su jefe Walter Galecio, inspeccionó ayer los trabajos de reconstrucción en el Centro Histórico de Piura, luego de lo cual exhortó al Gobierno Regional y a la Municipalidad de Piura a suspender la apertura de nuevos frentes de trabajo en otras calles y avenidas, en tanto no se culminen las obras ya iniciadas. El defensor del pueblo también solicitó una reunión de emergencia con la plataforma regional de Defensa Civil para coordinar acciones de contingencia que mitiguen el impacto de El Niño. Entrega parcial Sobre las obras del centro de la ciudad, el asesor del GORE, Jesús Moreno, aseguró que ya no se intervendrá más calles. Adelantó que a fin de mes entregarán pavimentadas las calles Cusco y Libertad, y a fines de noviembre, otras 12. Sobre el caso de los puntos críticos de la Av. Sullana (cruce con Avifap y calle Jacaranda), indicó que ANIN los consideró como parte de su intervención. Truenos causan terror en Sullana Una ligera lluvia registrada durante la madrugada del martes sorprendió a la población de Sullana. La precipitación no generó aniegos en la ciudad; sin embargo, la situación fue diferente en Cieneguillo Sur, donde las lluvias estuvieron acompañadas de fuertes truenos que hicieron temer lo peor a los moradores. En esta zona rural, las precipitaciones continuaron hasta después de las nueve de la mañana, generando preocupación entre las familias. Algunos padres optaron por no enviar a sus hijos a los diferentes colegios ubicados en los centros poblados y caseríos que limitan con la provincia de Piura. Chulucanas Mientras tanto, en Chulucanas se registraron lluvias torrenciales. Esta situación obligó a los comerciantes a cerrar el Mercado Modelo. En tanto, varias calles quedaron inundadas por las precipitaciones. Sin agua y con aniegos La Heroica Villa empieza a sentir los efectos de las lluvias registradas, una situación que genera preocupación entre los vecinos ante la posibilidad de que se intensifiquen las precipitaciones por el anunciado fenómeno El Niño. Las primeras dificultades ya se evidencian en calles con problemas de transitabilidad debido a los aniegos que dejaron varios sectores inundados. A ello se suma, la paralización temporal de pozos de agua potable Cayetano Heredia y Monte Sullón por fallas eléctricas debido a las lluvias. Vecinos también reportaron ayer que varias calles donde aún no se ha repuesto el embloquetado presentan serias dificultades para el tránsito vehicular y peatonal. El agua acumulada tras las lluvias de regular intensidad causa complicaciones y vuelve a poner en evidencia la vulnerabilidad de algunas vías del distrito frente a las precipitaciones que perjudican a la población.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/urbanizaciones-mercado-y-centro-de-piura-en-riesgo-de-inundacion-por-dique-de-la-mariposa/</t>
+          <t>https://eltiempo.pe/local/una-lluvia-de-siete-milimetros-inundo-calles-y-obras-y-puso-a-piura-de-cabeza/</t>
         </is>
       </c>
     </row>
@@ -2139,17 +2145,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ministra de la Mujer: «Piura está hecha un desastre, las calles están en arena; culpa de Madrid y Neyra»</t>
+          <t>Urbanizaciones, mercado y centro de Piura, en riesgo de inundación por dique de La Mariposa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Las condiciones de las calles de Piura tras las lluvias volvieron al centro de la discusión política. La ministra de la Mujer, Mara Seminario, cuestionó el estado de las vías y responsabilizó al exalcalde Gabriel Madrid y al gobernador regional, Luis Neyra León, por la situación que, según sus declaraciones, enfrenta la ciudad. “Piura está hecha un desastre, las calles de Piura están en arena”, manifestó la funcionaria en Willax TV al referirse a las consecuencias de las precipitaciones. Durante su intervención, también cuestionó la actuación de las autoridades responsables de la gestión municipal y regional. Ministra cuestiona las calles de Piura tras las lluvias En su pronunciamiento, la ministra señaló que las precipitaciones registradas durante la noche o la madrugada dejaron en evidencia el estado de las vías. Según sus palabras, algunos sectores presentan acumulación de arena y condiciones que dificultan la circulación. “Esto debe ser un lodazal hoy día. ¿Culpa de quién? De un alcalde llamado Gabriel Madrid y de un presidente regional llamado Luis Neyra León”, expresó Mara Seminario. La funcionaria dirigió sus críticas a las autoridades que tienen o tuvieron responsabilidades en la administración pública de la provincia y la región. En particular, cuestionó la gestión de Madrid, exalcalde de Piura, y la de Neyra, quien ocupa el cargo de gobernador regional. Críticas a Gabriel Madrid y Luis Neyra León Durante su intervención, la ministra también hizo referencia a la salida de Gabriel Madrid de la Municipalidad Provincial de Piura y cuestionó la gestión del gobernador regional Luis Neyra León. “El Madrid ya se fue, pero Neyra se va a ir tranquilo a su casa sin haber hecho nada”, sostuvo la funcionaria, en una de las frases más críticas de su pronunciamiento. ¿Qué responsabilidades tienen el Gobierno Regional y la municipalidad? En su declaración, la ministra sostuvo que los gobiernos regionales tienen competencias delegadas de distintos sectores y cuestionó que, a su juicio, la intervención del Gobierno central esté asumiendo gran parte de las acciones necesarias. “La gente se olvida que los gobiernos regionales tienen competencias delegadas de todos los sectores. El Gobierno central está haciendo todo y más”, afirmó. La distribución de responsabilidades entre los niveles de gobierno depende de las competencias establecidas por las normas y de las características de cada intervención. Los municipios tienen funciones vinculadas con la gestión local, mientras que los gobiernos regionales conducen políticas, programas y proyectos dentro de sus atribuciones.</t>
+          <t>La presidenta Keiko Fujimori aseguró que con los trabajos de descolmatación, el río Piura podría soportar un caudal de 4,000 metros cúbicos por segundo (m3/s); sin embargo, el presidente de la Cámara de Comercio de Piura, Javier Bereche, informó que en el sector La Mariposa (Medio Piura) existe un dique de 700 metros aproximadamente que apenas soportó un caudal de 2,900 m3/s en el 2017, y advirtió que, de no tomarse preventivas, podría ocurrir una catástrofe. Informó que ese dique se construyó en un inicio para salvaguardar a la población de los caseríos de La Mariposa y Los Ejidos de Huan. Dijo que de registrarse un fuerte caudal en los próximos meses no solo estos sectores serían los afectados sino otros más que conforman el “antiguo brazo del río”. “No solo afectaría a los centros poblados, sino que el agua llegará al centro de Piura, porque era un antiguo brazo del río que iba por La Mariposa, salía por Quinta Ana María [...]. Sería inundada incluso la Country, va para el mercado hasta el centro de la ciudad. Lo que quiero decir que el centro de Piura se puede inundar por rebose [del río] y, si se rompe ese dique, ya ni siquiera aguanta los 2,900 m3/s”, indicó. Informó que el presidente del Proyecto Especial Chira Piura, Jorge Garrido Lecca, se ha comprometido a evaluar el caso. Agregó que urge realizar trabajos de reforzamiento y elevar el dique. Pérdida de más de S/15 mil millones En conferencia de prensa, el presidente de la Camco, Javier Bereche, también dio a conocer que a la fecha el Fenómeno El Niño ya va dejando pérdidas de 3 mil millones de soles, donde la agricultura, el sector agroexportación y la pesquería son los sectores más afectados. “En un Niño moderado, nos podría costar 8 mil millones, y si es un Niño extraordinario como lo ha anunciado la presidenta Keiko podría costar 15 mil millones a la región”, señaló. El empresario indicó que en el sector pesca, la afectación se viene dando por la ausencia de especies debido al calentamiento del mar; mientras que el mango y otros productos son afectados también por las altas temperaturas.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/ministra-de-la-mujer-piura-esta-hecha-un-desastre-las-calles-estan-en-arena-culpa-de-madrid-y-neyra/</t>
+          <t>https://eltiempo.pe/local/urbanizaciones-mercado-y-centro-de-piura-en-riesgo-de-inundacion-por-dique-de-la-mariposa/</t>
         </is>
       </c>
     </row>
@@ -2189,17 +2195,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cuatro sicarios tras los pasos de alcalde electo de Veintiséis de Octubre, Percy Fiestas</t>
+          <t>Se quedarán sin agua durante una semana por paralización temporal del pozo Los Algarrobos</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Hace una semana, el alcalde electo de Veintiséis de Octubre, Percy Fiestas Aquino, fue blanco de mensajes extorsivos y de un video amenazante por parte de integrantes de la red criminal La Nueva Generación del Norte. Esta vez, cuatro presuntos sicarios estarían tras los pasos de la nueva autoridad municipal del distrito de Morropón. El maquiavélico plan habría sido detectado por un equipo de detectives de Lima y Piura, cuya labor se mantenía en estricta reserva. Sin embargo, las investigaciones se filtraron y se publicaron en una página de Facebook, lo cual generó preocupación en el Alto Piura. Equipo especial en Morropón Esta información fue confirmada ayer por Miguel Ángel Ruesta Carrasco, alcalde electo de Morropón, quien señaló que un equipo especial de investigadores se encuentra en la zona para poner en marcha un protocolo de seguridad. Se conoció que los agentes llegaron varias veces al inmueble de Miguel Ruesta, quien, por razones de seguridad, permaneció en un lugar desconocido. El objetivo de los custodios era activar inmediatamente un protocolo de rigor. Gatilleros foráneos Miguel Ruesta declaró brevemente que no ha recibido mensajes o llamadas extorsivas y la única fuente es la propia Policía Nacional, la misma que realiza una serie de diligencias y pesquisas en la ciudad de Morropón y rutas de acceso al distrito. Trascendió que serían cuatro gatilleros, dos de Tumbes y otros dos de Trujillo, que supuestamente arribaron al mencionado lugar para efectuar un riguroso seguimiento a la autoridad electa de Morropón, que asumirá funciones el próximo 1 de enero de 2027. La próxima autoridad municipal resaltó que no tiene problemas con nadie y solo queda que todos los vecinos del campo y la ciudad nos unamos para sacar adelante al distrito. Hijo de exalcalde Cabe resaltar que Miguel Ruesta es hijo del extinto profesor Guido Martin Ruesta Taboada, del movimiento político Región Para Todos, quien cumplió funciones de alcalde de Morropón en el período 2015-2018. Guido Ruesta perdió la vida en un accidente de tránsito.</t>
+          <t>Vecinos de la urbanización Bello Horizonte, Educadores y partes altas del asentamiento humano Los Algarrobos y urbanización Ignacio Merino deberán tomar sus precauciones para abastecerse de agua potable. Y es que EPS Grau emitió ayer un comunicado anunciando la paralización temporal del pozo Los Algarrobos debido a una afectación tanto en el sistema eléctrico como en el equipo de bombeo de la referida fuente. Señalan que dada la emergencia que se presentó en dicho pozo han previsto realizar la reparación correspondiente y se prevé la culminación de la misma para el próximo miércoles 28 de octubre, luego de la cual “se restablecería de manera progresiva la normal distribución de agua potable desde la fuente”. En tanto, culminen los trabajos aseguran que abastecerán a la población con cisternas y un envío de mayor caudal a la zona de cobertura desde la Planta de Tratamiento de Curumuy. Protestan Mientras tanto, ayer un numeroso grupo de moradores del sector Los Médanos en el distrito de Castilla bloqueó la prolongación de la avenida Guardia Civil que conduce la vía Piura-Chulucanas para llamar la atención de la EPS Grau y exigir la continuidad del servicio de agua potable. Y es que señalan que en algunas zonas no cae agua y en otros sectores tienen que levantarse desde las 5:00 a.m para almacenar la poca agua que cae y por horas en sus viviendas.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/cuatro-sicarios-tras-los-pasos-de-alcalde-electo-de-veintiseis-de-octubre-percy-fiestas/</t>
+          <t>https://eltiempo.pe/local/se-quedaran-sin-agua-durante-una-semana-por-paralizacion-temporal-del-pozo-los-algarrobos/</t>
         </is>
       </c>
     </row>
@@ -2210,53 +2216,53 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vecinos de Ignacio Merino cuestionan demora en atención a los ministros de Defensa y Midagri que llegaron a Piura</t>
+          <t>Cámara de Comercio y Colegio de Ingenieros exigen intervención inmediata en Chutuque</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Los vecinos de la urbanización Ignacio Merino, en Piura , expresaron su malestar por la demora en los trabajos para retirar el agua acumulada en sus viviendas y calles tras las últimas lluvias registradas en la ciudad. Durante la visita de los ministros de Desarrollo Agrario y Riego, Marco Vinelli , y de Defensa, Rafael Belaúnde , los moradores pidieron una respuesta inmediata ante el riesgo de nuevas inundaciones. La preocupación de las familias se centra en las dificultades para evacuar el agua que permanece en distintos puntos de la urbanización, una situación que afecta sus actividades cotidianas y mantiene en alerta a quienes temen que nuevas precipitaciones vuelvan a ingresar a sus casas. “Es una cosa desesperante porque el agua se mete a nuestra casa”, manifestó uno de los vecinos durante la cobertura de Canal N, al describir los problemas que enfrentan los residentes de esta zona de Piura. Ignacio Merino: ministros anuncian acciones para retirar el agua acumulada Durante su recorrido por los sectores afectados, el ministro de Desarrollo Agrario y Riego, Marco Vinelli, explicó que las lluvias habían afectado seis puntos de la ciudad. Según indicó, Ignacio Merino todavía necesitaba trabajos adicionales para completar la evacuación del agua . El funcionario señaló que coordinaba con el Ministerio de Vivienda, Construcción y Saneamiento el envío de un equipo hidrojet para apoyar las labores de extracción. Este tipo de equipo permite succionar agua y facilitar la limpieza de zonas donde la acumulación dificulta el tránsito y afecta a las viviendas. Vinelli sostuvo que las autoridades estaban atendiendo los sectores perjudicados por las precipitaciones. Sin embargo, el reclamo de los vecinos evidenció la urgencia de acelerar las intervenciones para reducir las molestias y los riesgos que afrontan las familias. La situación también pone sobre la mesa la necesidad de contar con mecanismos de drenaje que permitan evacuar el agua con mayor rapidez, especialmente en zonas urbanas vulnerables a las lluvias. Defensa despliega personal y equipos para atender las inundaciones en Piura Por su parte, el ministro de Defensa, Rafael Belaúnde, informó que las Fuerzas Armadas desplegaron personal y equipos de trasvase para contribuir a disminuir la acumulación de agua en los puntos más afectados. El titular del Ministerio de Defensa reconoció que las precipitaciones habían ocasionado daños en viviendas y pertenencias. Además, sostuvo que uno de los objetivos de la intervención es mejorar la capacidad de respuesta de las autoridades frente a futuros episodios de lluvias. “Igual va a llover, igual algunas zonas se van a inundar. Lo importante es la velocidad y capacidad de respuesta”, expresó Belaúnde, al referirse a la necesidad de atender oportunamente las emergencias. La declaración se produjo en medio de los cuestionamientos de los residentes de Ignacio Merino, quienes esperan que las acciones anunciadas permitan retirar el agua que permanece en sus calles y viviendas. Ignacio Merino y El Chilcal son considerados puntos críticos El comandante de la Primera Región Militar, general Carlos Rabanal, informó que los equipos de trasvase permanecerían en dos sectores considerados críticos: Ignacio Merino y El Chilcal . De acuerdo con el oficial, se disponía de 480 efectivos para apoyar las labores de respuesta. También indicó que se coordinaría con los gobiernos locales el despliegue de motobombas de seis pulgadas y camionetas para trasladar los equipos con mayor rapidez. La intervención busca atender las zonas que presentan dificultades para evacuar el agua por la falta de un drenaje adecuado. En estos lugares, la acumulación de agua puede prolongarse cuando la infraestructura disponible resulta insuficiente para conducirla hacia otros puntos. La permanencia de los equipos militares en ambos sectores apunta a reforzar la atención de la emergencia. No obstante, los vecinos de Ignacio Merino esperan que las medidas se traduzcan en resultados concretos y que el retiro del agua no se prolongue mientras continúe el riesgo de nuevas lluvias. Ministro y reportera discrepan sobre la cantidad de lluvia registrada Durante la entrevista difundida por Canal N también surgieron diferencias respecto de la cantidad de lluvia que habría caído en la región. Marco Vinelli sostuvo que las precipitaciones habían superado los 50 a 60 milímetros en la ciudad de Piura. Sin embargo, la reportera señaló que, según la información del Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) que manejaba durante la transmisión, se habían registrado alrededor de seis milímetros en Piura y diez milímetros en Chulucanas. La discrepancia quedó planteada durante el intercambio y no fue resuelta en la entrevista. Para establecer el registro correspondiente, es necesario considerar los reportes oficiales del Senamhi, así como el periodo y la estación meteorológica utilizados para la medición. Las diferencias en los datos de precipitación son relevantes para evaluar el comportamiento de las lluvias y las condiciones que contribuyen a las inundaciones. Sin embargo, la cantidad de agua acumulada en una zona urbana también puede depender de la capacidad del drenaje, la topografía y el estado de los canales de evacuación. Autoridades piden evitar residuos en ríos y canales En medio de las labores de emergencia, Vinelli pidió la colaboración de la población para evitar arrojar residuos en ríos y canales. La acumulación de basura puede obstruir las vías de drenaje y dificultar la evacuación del agua durante las precipitaciones. El funcionario también remarcó la importancia de priorizar la protección de la vida ante posibles huaicos y desbordes. Mientras tanto, los residentes de Ignacio Merino esperan que las coordinaciones entre los ministerios, las Fuerzas Armadas y los gobiernos locales permitan atender los puntos afectados. La emergencia vuelve a poner en discusión la capacidad de respuesta de Piura frente a las lluvias y la necesidad de mejorar los sistemas de drenaje urbano. Para las familias afectadas, la prioridad inmediata es que el agua acumulada sea retirada y que se adopten medidas que reduzcan el riesgo de nuevas inundaciones.</t>
+          <t>El presidente de la Cámara de Comercio y Producción de Piura, Javier Bereche, lamentó que hasta la fecha no se inicien los trabajos en la ampliación del canal de Chutuque que pueda evitar una posible inundación y afectación a la población. Señaló que ya no hay tiempo para sacar el tapón rocoso de Chutuque, pero sí abrir el canal de derivación de Chutuque hacia lagunas. Indicó que de no ejecutarse la intervención se podría registrar una catástrofe más adelante. En tanto, el Colegio de Ingenieros emitió un pronunciamiento para exigir acciones concretas y obras urgentes frente al riesgo de inundaciones. Plantean acciones inmediatas en la intervención de Chutuque, reparación de las defensas ribereñas, evaluar la efectividad de los SARE y agilizar la culminación de las calles intervenidas en el centro de la ciudad, entre otras demandas.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/vecinos-de-ignacio-merino-cuestionan-demora-en-atencion-a-los-ministros-de-defensa-y-midagri-que-llegaron-a-piura/</t>
+          <t>https://eltiempo.pe/local/camara-de-comercio-y-colegio-de-ingenieros-exigen-intervencion-inmediata-en-chutuque/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lluvias en Piura inundan calles y dificultan el tránsito en varios sectores | FOTOS</t>
+          <t>Vecinos exigen motobombas: más de 6000 vecinos de la urb. Miraflores en riesgo de inundación</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Las intensas lluvias registradas el lunes 19 y el martes 20 de octubre dejaron calles anegadas en distintos sectores de Piura y complicaron el tránsito vehicular y peatonal. Las precipitaciones también se reportaron en localidades como Chulucanas y Tambogrande, en medio de las condiciones atmosféricas y oceánicas asociadas al fenómeno el niño. El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó que las lluvias estuvieron relacionadas con un núcleo convectivo ubicado en la zona media alta de Piura. Asimismo, su radar identificó precipitaciones de ligera a moderada intensidad en diversas zonas de la costa. En distritos como Castilla, el agua acumulada en las calles generó preocupación entre los vecinos y dificultó el desplazamiento de vehículos y peatones. El Senamhi informó que las altas temperaturas diurnas y nocturnas continuarán en la costa peruana hasta el 31 de octubre, debido a las condiciones atmosféricas y oceánicas vinculadas al Niño Costero. Durante este periodo, se prevé cielo nublado en las primeras horas de la mañana, menor cobertura nubosa hacia el mediodía y la tarde, y un posterior incremento de la nubosidad. También se esperan lluvias dispersas en sectores de la costa norte. De acuerdo con el pronóstico, las temperaturas máximas en Piura y Tumbes oscilarán entre los 32 °C y 38 °C. A las condiciones meteorológicas se suma la persistencia de temperaturas superficiales del mar superiores a los valores habituales frente al litoral de Piura. Según información de la Dirección de Hidrografía y Navegación (DHN), al 18 de octubre la temperatura superficial del mar alcanzó los 26,2 °C en Talara y los 25,9 °C en Paita. Las anomalías registradas fueron de +8,1 °C y +8,5 °C, respectivamente. Estas condiciones favorecen temperaturas del aire por encima de lo normal, tanto durante el día como en la noche. Según el reporte, mientras persistan las anomalías positivas de la temperatura del mar, se prevé que el calor continúe durante las próximas semanas.</t>
+          <t>Vecinos de la urbanización Miraflores, en el distrito de Castilla exigen a la municipalidad distrital el mantenimiento del Sistema de evacuación de aguas pluviales y la instalación de motobombas para su funcionamiento; de lo contrario, y de volver a registrarse lluvias como la de los días anteriores existe el riesgo de inundación en la zona. El presidente de la Junta Vecinal Comunal (Juveco) de Miraflores, Maximiliano Flores Cevallos, señaló que las bombas destinadas a este sector aún no han sido instaladas, pese a las reiteradas solicitudes presentadas desde hace varios meses. Por ello, exhortó al alcalde de Castilla, Julio Vásquez Alberca, a disponer las acciones necesarias y no se ponga en riesgo a los más de 6.000 vecinos de dicha urbanización. Agregó que durante las últimas lluvias la municipalidad llevó una bomba pequeña pero solo sirvió para salir de la emergencia.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/lluvias-en-piura-inundan-calles-y-dificultan-el-transito-en-varios-sectores-fotos-fenomeno-el-nino-apuesplan-ultimas-noticia/</t>
+          <t>https://eltiempo.pe/local/vecinos-exigen-motobombas-mas-de-6000-vecinos-de-la-urb-miraflores-en-riesgo-de-inundacion/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2264,24 +2270,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Piura lidera los contagios de dengue en el Perú con más de 13 mil casos y 9 fallecidos</t>
+          <t>Vecinos de Ignacio Merino cuestionan demora en atención a los ministros de Defensa y Midagri que llegaron a Piura</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>La Dirección Regional de Salud y el Centro Nacional de Epidemiología, Prevención y Control de Enfermedades informaron que la región de Piura encabeza la lista de contagios por dengue en el país con 13,025 infectados. Las entidades oficiales reportan además 9 fallecidos por la enfermedad en el departamento norteño. La Sala Situacional de la Diresa precisó que el 68% de los casos notificados contó con la debida confirmación de laboratorio. El reporte sanitario detalló la presencia del serotipo 3 del virus y advirtió sobre cuadros graves con necesidad de hospitalización en la zona. A nivel provincial, Piura acumula la cifra más alta de la región con 5,453 contagiados en sus diferentes distritos. Las provincias de Morropón y Sullana siguieron en la estadística oficial con 3,810 y 3,016 personas afectadas respectivamente. Los adultos de 30 a 59 años representan el 30,2% de los infectados en la región. Los niños de 0 a 11 años concentraron 3,414 infectados y cinco de los decesos registrados por las autoridades médicas. El Ministerio de Salud inició la aplicación de la vacuna Qdenga para personas entre los 10 y 20 años de edad para frenar el avance del dengue. La cobertura de la inmunización alcanza un 34,8% en la primera dosis y un 58% en la segunda aplicación dentro de los grupos prioritarios. El CDC del Minsa notificó 71,256 casos y 75 muertes por la epidemia a nivel nacional. En Lima se concentran aproximadamente unos 6,000 casos confirmados, mientras que se registran solo en Piura unos 1,000 contagios por semana desde hace varios días. El director general del Centro Nacional de Epidemiología, Prevención y Control de Enfermedades (CDC), César Munayco, informó a Canal N que las otras regiones que le siguen a Piura en número de contagios son La Libertad y Lambayeque. En esa línea, advirtió que las cifras seguirán incrementando si el calor y las lluvias persisten en la zona norte del país. Desde este lunes 19 de octubre se registran intensas lluvias que han inundados las calles y viviendas de Chulucanas en la provincia de Morropón, entre otros sectores vulnerables de Piura. El agua acumulada sobrepasó los 30 centímetros de altura en los mercados locales y provocó el colapso del sistema de alcantarillado. El fenómeno El Niño Costero originó lluvias continuas y elevadas temperaturas durante varios días consecutivos en la región. La acumulación de agua en recipientes inservibles multiplica los criaderos del mosquito Aedes aegypti y eleva el riesgo de nuevos contagios. La emergencia está siendo atendida con el despliegue de motobombas para disminuir el nivel del agua en las calles inundadas. Asimismo, se cuenta con el apoyo de miembros de las Fuerzas Armadas y la vigilancia de personal de la Defensoría del Pueblo para constatar la situación.</t>
+          <t>Los vecinos de la urbanización Ignacio Merino, en Piura , expresaron su malestar por la demora en los trabajos para retirar el agua acumulada en sus viviendas y calles tras las últimas lluvias registradas en la ciudad. Durante la visita de los ministros de Desarrollo Agrario y Riego, Marco Vinelli , y de Defensa, Rafael Belaúnde , los moradores pidieron una respuesta inmediata ante el riesgo de nuevas inundaciones. La preocupación de las familias se centra en las dificultades para evacuar el agua que permanece en distintos puntos de la urbanización, una situación que afecta sus actividades cotidianas y mantiene en alerta a quienes temen que nuevas precipitaciones vuelvan a ingresar a sus casas. “Es una cosa desesperante porque el agua se mete a nuestra casa”, manifestó uno de los vecinos durante la cobertura de Canal N, al describir los problemas que enfrentan los residentes de esta zona de Piura. Ignacio Merino: ministros anuncian acciones para retirar el agua acumulada Durante su recorrido por los sectores afectados, el ministro de Desarrollo Agrario y Riego, Marco Vinelli, explicó que las lluvias habían afectado seis puntos de la ciudad. Según indicó, Ignacio Merino todavía necesitaba trabajos adicionales para completar la evacuación del agua . El funcionario señaló que coordinaba con el Ministerio de Vivienda, Construcción y Saneamiento el envío de un equipo hidrojet para apoyar las labores de extracción. Este tipo de equipo permite succionar agua y facilitar la limpieza de zonas donde la acumulación dificulta el tránsito y afecta a las viviendas. Vinelli sostuvo que las autoridades estaban atendiendo los sectores perjudicados por las precipitaciones. Sin embargo, el reclamo de los vecinos evidenció la urgencia de acelerar las intervenciones para reducir las molestias y los riesgos que afrontan las familias. La situación también pone sobre la mesa la necesidad de contar con mecanismos de drenaje que permitan evacuar el agua con mayor rapidez, especialmente en zonas urbanas vulnerables a las lluvias. Defensa despliega personal y equipos para atender las inundaciones en Piura Por su parte, el ministro de Defensa, Rafael Belaúnde, informó que las Fuerzas Armadas desplegaron personal y equipos de trasvase para contribuir a disminuir la acumulación de agua en los puntos más afectados. El titular del Ministerio de Defensa reconoció que las precipitaciones habían ocasionado daños en viviendas y pertenencias. Además, sostuvo que uno de los objetivos de la intervención es mejorar la capacidad de respuesta de las autoridades frente a futuros episodios de lluvias. “Igual va a llover, igual algunas zonas se van a inundar. Lo importante es la velocidad y capacidad de respuesta”, expresó Belaúnde, al referirse a la necesidad de atender oportunamente las emergencias. La declaración se produjo en medio de los cuestionamientos de los residentes de Ignacio Merino, quienes esperan que las acciones anunciadas permitan retirar el agua que permanece en sus calles y viviendas. Ignacio Merino y El Chilcal son considerados puntos críticos El comandante de la Primera Región Militar, general Carlos Rabanal, informó que los equipos de trasvase permanecerían en dos sectores considerados críticos: Ignacio Merino y El Chilcal . De acuerdo con el oficial, se disponía de 480 efectivos para apoyar las labores de respuesta. También indicó que se coordinaría con los gobiernos locales el despliegue de motobombas de seis pulgadas y camionetas para trasladar los equipos con mayor rapidez. La intervención busca atender las zonas que presentan dificultades para evacuar el agua por la falta de un drenaje adecuado. En estos lugares, la acumulación de agua puede prolongarse cuando la infraestructura disponible resulta insuficiente para conducirla hacia otros puntos. La permanencia de los equipos militares en ambos sectores apunta a reforzar la atención de la emergencia. No obstante, los vecinos de Ignacio Merino esperan que las medidas se traduzcan en resultados concretos y que el retiro del agua no se prolongue mientras continúe el riesgo de nuevas lluvias. Ministro y reportera discrepan sobre la cantidad de lluvia registrada Durante la entrevista difundida por Canal N también surgieron diferencias respecto de la cantidad de lluvia que habría caído en la región. Marco Vinelli sostuvo que las precipitaciones habían superado los 50 a 60 milímetros en la ciudad de Piura. Sin embargo, la reportera señaló que, según la información del Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) que manejaba durante la transmisión, se habían registrado alrededor de seis milímetros en Piura y diez milímetros en Chulucanas. La discrepancia quedó planteada durante el intercambio y no fue resuelta en la entrevista. Para establecer el registro correspondiente, es necesario considerar los reportes oficiales del Senamhi, así como el periodo y la estación meteorológica utilizados para la medición. Las diferencias en los datos de precipitación son relevantes para evaluar el comportamiento de las lluvias y las condiciones que contribuyen a las inundaciones. Sin embargo, la cantidad de agua acumulada en una zona urbana también puede depender de la capacidad del drenaje, la topografía y el estado de los canales de evacuación. Autoridades piden evitar residuos en ríos y canales En medio de las labores de emergencia, Vinelli pidió la colaboración de la población para evitar arrojar residuos en ríos y canales. La acumulación de basura puede obstruir las vías de drenaje y dificultar la evacuación del agua durante las precipitaciones. El funcionario también remarcó la importancia de priorizar la protección de la vida ante posibles huaicos y desbordes. Mientras tanto, los residentes de Ignacio Merino esperan que las coordinaciones entre los ministerios, las Fuerzas Armadas y los gobiernos locales permitan atender los puntos afectados. La emergencia vuelve a poner en discusión la capacidad de respuesta de Piura frente a las lluvias y la necesidad de mejorar los sistemas de drenaje urbano. Para las familias afectadas, la prioridad inmediata es que el agua acumulada sea retirada y que se adopten medidas que reduzcan el riesgo de nuevas inundaciones.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/piura-lidera-los-contagios-de-dengue-en-el-peru-con-mas-de-13-mil-casos-y-nueve-fallecidos-apuesplan-ultimas-noticia/</t>
+          <t>https://eltiempo.pe/local/vecinos-de-ignacio-merino-cuestionan-demora-en-atencion-a-los-ministros-de-defensa-y-midagri-que-llegaron-a-piura/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Gestión</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -2289,24 +2295,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lluvias de fuerte intensidad se registran en diversas partes de Piura y Tumbes</t>
+          <t>Lluvias en Piura inundan calles y dificultan el tránsito en varios sectores | FOTOS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lluvias de fuerte intensidad se registraron desde la noche del 19 de octubre en distintos puntos de la región Piura y Tumbes, en el norte del país . De acuerdo con una publicación de la cuenta meteorológica Asismet, las imágenes satelitales mostraban precipitaciones también sobre la ciudad de Piura. El aeropuerto, en tanto, reportó un acumulado de 2 milímetros de agua hasta las 9 de la noche. En Chulucanas, la lluvia sorprendió a las personas que participaban en la procesión del Señor de los Milagros. Por su parte, un reporte en la cuenta de Abraham Levy informó sobre un foco lluvioso en la ciudad de Piura. Su reporte estuvo acompañado de una imagen satelital correspondiente a las 8:30 de la noche, donde se ve el fenómeno. Las lluvias registradas en Tumbes activaron quebradas y afectaron vías de acceso, principalmente en el distrito de Pampas de Hospital. Según lo reportado, las lluvias comenzaron alrededor de las 5:00 a. m. y evidenciaron la vulnerabilidad de la región. Según el Senamhi, las condiciones climáticas serán monitoreadas ante la posibilidad de que las precipitaciones aumenten en los próximos días. Cabe recordar que las lluvias en la costa norte del Perú podrían alcanzar acumulados de hasta 300 milímetros en un solo día durante el verano de 2027, mientras que diversas regiones de la sierra sur y otras zonas del país afrontarían un déficit de precipitaciones que podría comprometer la disponibilidad de agua para la agricultura y el abastecimiento de los reservorios. Según el vocero del Servicio Nacional de Meteorología e Hidrología (Senamhi), Nelson Quispe, la fase extraordinaria se prolongará hasta enero del próximo año y luego entrará a la etapa fuerte que se extenderá hasta el otoño. Tras la lluvia intensa que se registró, el fenómeno evidenció los problemas de drenaje en Piura. Pese a registrar solo 2.1 milímetros, provocó inundaciones y dejó vehículos atrapados. El Senamhi atribuyó las precipitaciones a un núcleo convectivo en la zona media alta de Piura, además de detectar lluvias de ligera a moderada intensidad en distintas zonas de la costa. Por otro lado, vecinos del distrito de Veintiséis de Octubre reportaron viviendas inundadas. Asimismo, ciudadanos del asentamiento humano 4 de Octubre informaron que sus calles quedaron inundadas por las precipitaciones. Por otro lado, en el sector de Los Tallanes, el agua ingresó a viviendas y afectó negocios, cuyos propietarios reportaron pérdidas de mercadería. A su vez, varios tramos de la avenida José Aguilar Santisteban se inundaron y algunos vehículos quedaron atrapados. En tanto, en el sector de Las Dalias, los residentes expresaron preocupación por las vías inconclusas tras los trabajos de pavimentación. Los vecinos señalaron que las lluvias convirtieron las calles en acumulaciones de agua y canales, dificultando el tránsito. En Tumbes, las lluvias afectaron a diversos puntos de la región, en especial al distrito de Pampas de Hosital. En ese distrito se activaron las quebradas Peña Blanca, Chacritas e Higuerón, lo que dificultó el tránsito de vehículos hacia zonas agrícolas. En la ciudad de Tumbes, en tanto, las precipitaciones dejaron aniegos en los alrededores del mercado, el barrio San José y el centro poblado Pampa Grande. El mar frente al litoral piurano mantiene temperaturas superficiales superiores a sus valores habituales. Según información de la Dirección de Hidrografía y Navegación (DHN), al 18 de octubre, el mar registró 26.2 °C en Talara y 25.9 °C en Paita, con anomalías de +8.1 °C y +8.5 °C, respectivamente. Las temperaturas elevadas del mar favorecen un aire más cálido de día y de noche, escenario que podría continuar durante las próximas semanas mientras persistan las anomalías. Las lluvias también afectaron otras localidades en la región Piura. El alcalde de Morropón, Richard Baca Palacios, advirtió este martes 20 de octubre que su jurisdicción ya sufre los efectos de lo que calificó como un “megafenómeno del Niño”. El funcionario informó que las precipitaciones en su jurisdicción provocaron inundaciones, la activación de una quebrada y un aumento del caudal del río. El alcalde solicitó a las autoridades regionales y nacionales maquinaria pesada para atender la emergencia. La autoridad precisó que las alcaldías afectadas en la región necesitan con urgencia combustible y bienes de ayuda humanitaria para responder a los daños. Según indicó, solicitó al gobierno demoler un antiguo puente al ingreso de Chulucanas, en riesgo de colapso por las lluvias, apenas Keiko Fujimori asumió la Presidencia. “Gracias a Dios que hace una semana y media empezó la demolición de este puente histórico, pero que, lamentablemente, por sus condiciones actuales, ya no servía y más bien podía caerse y eso podría afectar lo que es la estructura del otro puente”, indicó a RPP. La Defensoría del Pueblo en Piura, ante las lluvias intensas registradas el día de hoy que han provocado aniegos e inundaciones en numerosos sectores de esta ciudad, exhortó al gobernador regional y al alcalde provincial de Piura evaluar suspender de manera inmediata la apertura de nuevas zonas de intervención en las vías de la ciudad donde se vienen ejecutando diversas obras, en tanto no se culminen las labores pendientes en las avenidas y calles en las que actualmente puede verse zanjas y asfalto levantado. El pedido formó parte de un conjunto de recomendaciones que fueron dirigidas con carácter de urgencia por la sede defensorial con el fin de reducir los riesgos a la seguridad, integridad y libre tránsito de la población, principalmente en aquellas arterias en las que las fuertes precipitaciones provocó verdaderos lodazales que constituyen un serio riesgo para las personas que transitan diariamente. Como parte de las recomendaciones, se exhortó también a disponer acciones de coordinación y supervisión para que los contratistas cumplan con los plazos establecidos para la habilitación progresiva de las calles y avenidas actualmente intervenidas, que se ubican principalmente en el centro histórico de Piura. Asimismo, se pidió disponer la limpieza inmediata de las zonas intervenidas y de las calles afectadas por la acumulación de agua y lodo, garantizando el recojo de basura y residuos sólidos así como el retiro de desmontes, materiales excedentes y montículos de arena generados por las obras. Finalmente, entre otras medidas, también se requirió adoptar medidas urgentes para garantizar el tránsito peatonal y vehicular mediante la instalación de señalización preventiva, el acondicionamiento de rutas peatonales seguras y la identificación oportuna de puntos críticos, así como establecer una coordinación permanente con la Policía Nacional del Perú para el control del tránsito vehicular en las zonas afectadas. Cabe indicar que, tras las fuertes lluvias, la sede defensorial dirigió esta mañana un recorrido por las zonas más afectadas como los cruces de las calles Sullana con Bolognesi, sí como de la céntrica avenida Grau con la calle Junín y el Sistema Alternativo de Recolección y Evacuación de Aguas de Lluvia (SARE) ubicado cerca del parque Tres Culturas. El recorrido también comprendió las calles Ignacio Merino, la intersección de las avenidas Sullana y Blas de Atienza, así como el cruce de José Aguilar Santisteban con Azucena y la calle Los Dos Grifos, donde pudo comprobarse la falta de implementación de medidas de contingencia pese a la advertencia del grave impacto que tendrá el fenómeno El Niño actualmente en marcha.</t>
+          <t>Las intensas lluvias registradas el lunes 19 y el martes 20 de octubre dejaron calles anegadas en distintos sectores de Piura y complicaron el tránsito vehicular y peatonal. Las precipitaciones también se reportaron en localidades como Chulucanas y Tambogrande, en medio de las condiciones atmosféricas y oceánicas asociadas al fenómeno el niño. El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) informó que las lluvias estuvieron relacionadas con un núcleo convectivo ubicado en la zona media alta de Piura. Asimismo, su radar identificó precipitaciones de ligera a moderada intensidad en diversas zonas de la costa. En distritos como Castilla, el agua acumulada en las calles generó preocupación entre los vecinos y dificultó el desplazamiento de vehículos y peatones. El Senamhi informó que las altas temperaturas diurnas y nocturnas continuarán en la costa peruana hasta el 31 de octubre, debido a las condiciones atmosféricas y oceánicas vinculadas al Niño Costero. Durante este periodo, se prevé cielo nublado en las primeras horas de la mañana, menor cobertura nubosa hacia el mediodía y la tarde, y un posterior incremento de la nubosidad. También se esperan lluvias dispersas en sectores de la costa norte. De acuerdo con el pronóstico, las temperaturas máximas en Piura y Tumbes oscilarán entre los 32 °C y 38 °C. A las condiciones meteorológicas se suma la persistencia de temperaturas superficiales del mar superiores a los valores habituales frente al litoral de Piura. Según información de la Dirección de Hidrografía y Navegación (DHN), al 18 de octubre la temperatura superficial del mar alcanzó los 26,2 °C en Talara y los 25,9 °C en Paita. Las anomalías registradas fueron de +8,1 °C y +8,5 °C, respectivamente. Estas condiciones favorecen temperaturas del aire por encima de lo normal, tanto durante el día como en la noche. Según el reporte, mientras persistan las anomalías positivas de la temperatura del mar, se prevé que el calor continúe durante las próximas semanas.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://gestion.pe/peru/piura-lluvias-de-fuerte-intesidad-se-registran-en-diversas-partes-de-la-region-noticia/</t>
+          <t>https://elcomercio.pe/peru/piura/lluvias-en-piura-inundan-calles-y-dificultan-el-transito-en-varios-sectores-fotos-fenomeno-el-nino-apuesplan-ultimas-noticia/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2314,17 +2320,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>¿7 o 60 litros por metro cuadrado en Piura? Contradicciones sobre cuánto llovió en Piura este martes 20 de octubre</t>
+          <t>Piura evacúa el agua acumulada por las lluvias mediante sistemas de drenaje pluvial</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>¿Llovieron 7 o hasta 60 litros de agua por metro cuadrado en Piura? Esa es la duda que surgió tras las precipitaciones del martes 20 de octubre, luego de que el ministro de Desarrollo Agrario y Riego, Marco Vinelli, mencionara una cantidad considerablemente mayor a la cifra del Senamhi citada durante una entrevista de Canal N. La diferencia llamó la atención en medio de los reclamos de vecinos de la urbanización Ignacio Merino, quienes denunciaron que el agua permanecía acumulada en sus viviendas y calles. Mientras las familias pedían una solución urgente para evitar nuevas inundaciones, las declaraciones de las autoridades abrieron interrogantes sobre cuánta lluvia cayó realmente en la ciudad. ¿Cuánto llovió en Piura el martes 20 de octubre? Durante su visita a las zonas afectadas, el ministro Marco Vinelli sostuvo que las precipitaciones habían superado los 50 a 60 milímetros en Piura. Sin embargo, según la información del Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) que manejaba, el registro era de aproximadamente 7 milímetros en Piura y 10 milímetros en Chulucanas. La diferencia entre ambas cifras es importante. Una lluvia de 7 milímetros equivale a 7 litros de agua por metro cuadrado, mientras que 60 milímetros representan 60 litros por metro cuadrado. Es decir, la cantidad mencionada por el ministro podría ser hasta diez veces mayor que el registro atribuido al Senamhi durante la entrevista. No obstante, para establecer cuál de las cifras corresponde a la medición oficial, es necesario verificar la estación meteorológica, el periodo de observación y el reporte correspondiente al martes 20 de octubre. Durante el intercambio televisivo, la discrepancia quedó planteada, pero no se aclaró si ambas cantidades correspondían al mismo intervalo de tiempo o a puntos de medición comparables. Los registros meteorológicos oficiales pueden consultarse en el portal del Senamhi , entidad encargada de monitorear las condiciones del tiempo y las precipitaciones en el territorio peruano. Vecinos de Ignacio Merino reclaman por el agua dentro de sus casas Mientras surgían las dudas sobre la cantidad de lluvia, los residentes de la urbanización Ignacio Merino expresaron su indignación por la demora en retirar el agua acumulada en sus viviendas y calles. Durante la visita de los ministros Marco Vinelli, de Desarrollo Agrario y Riego, y Rafael Belaúnde, de Defensa, los vecinos solicitaron apoyo inmediato ante el riesgo de que nuevas precipitaciones volvieran a inundar sus hogares. “Es una cosa desesperante porque el agua se mete a nuestra casa”, manifestó uno de los moradores, quien describió las dificultades que enfrentaban las familias afectadas. El reclamo puso nuevamente en evidencia los problemas que afrontan determinados sectores de Piura para evacuar el agua después de las lluvias. Para los vecinos, la preocupación no se limita a las precipitaciones, sino también al tiempo que demora el retiro del agua y a la posibilidad de que vuelva a ingresar a sus viviendas. Ministro anuncia equipo hidrojet para retirar el agua acumulada Marco Vinelli explicó que las lluvias habían afectado seis puntos de la ciudad y reconoció que Ignacio Merino todavía necesitaba trabajos para completar la evacuación del agua. Según declaró a Canal N, coordinaba con el Ministerio de Vivienda, Construcción y Saneamiento el envío de un equipo hidrojet para reforzar las labores en la zona. La intervención buscaba retirar el agua estancada y atender a las familias perjudicadas. Por su parte, el ministro de Defensa, Rafael Belaúnde, informó que las Fuerzas Armadas desplegaron personal y equipos de trasvase para reducir la acumulación de agua en los sectores afectados. “Igual va a llover, igual algunas zonas se van a inundar. Lo importante es la velocidad y capacidad de respuesta”, expresó el titular del Ministerio de Defensa al referirse a las acciones que se deben implementar frente a futuras precipitaciones. Despliegan 480 efectivos en Ignacio Merino y El Chilcal El comandante de la Primera Región Militar, general Carlos Rabanal, informó que los equipos de trasvase permanecerían en dos puntos considerados críticos: Ignacio Merino y El Chilcal. De acuerdo con el oficial, se disponía de 480 efectivos para apoyar las labores. Además, se coordinaría con los gobiernos locales el despliegue de motobombas de seis pulgadas y camionetas para trasladar los equipos hacia los sectores que requirieran atención. Las acciones están orientadas a retirar el agua acumulada en las zonas con dificultades de drenaje. Sin embargo, los reclamos de los vecinos reflejan la urgencia de contar con una respuesta oportuna cuando se producen aniegos y de reducir el riesgo de que las viviendas vuelvan a resultar afectadas.</t>
+          <t>La región Piura logró evacuar el agua acumulada por las inundaciones registradas en distintos distritos debido a las fuertes lluvias, mediante sistemas de drenaje pluvial instalados en los puntos más críticos. Las labores concluyeron esta tarde, informó Renato Ameri Moreno, jefe de Seguridad y Defensa Nacional del Ministerio de Vivienda, Construcción y Saneamiento (MVCS). En declaraciones a TVPerú Noticias, el funcionario señaló que los sistemas alternativos de recolección de agua de lluvia permitieron atender las zonas afectadas por las precipitaciones. “Hoy, debido a las lluvias, Piura se ha visto afectada por inundaciones en distintos distritos. Sin embargo, nuestros equipos de los sistemas alternativos de recolección de agua de lluvia han funcionado en los puntos más críticos, donde hemos instalado estos sistemas”, declaró. Ameri Moreno explicó que los mecanismos de drenaje se implementaron mediante tuberías subterráneas que conducen el agua acumulada hacia zonas seguras, como canales, drenes o ríos. Precisó que estos sistemas permiten recolectar el agua de lluvia en las denominadas cuencas ciegas, áreas donde el líquido se concentra y que no cuentan con una vía natural de evacuación. El representante del MVCS destacó que las medidas de prevención implementadas en Piura ante el fenómeno El Niño (FEN) facilitaron las labores de drenaje. Según indicó, la región cuenta con 20 sistemas de drenaje, de los cuales nueve son administrados por el Ministerio de Vivienda. Además, hace aproximadamente un mes se desplegaron 20 motobombas en distintos distritos. El funcionario también señaló que se dispone de un almacén de emergencia para distribuir equipos según las necesidades y que se entregaron unidades a los municipios para atender las cuencas ciegas. Asimismo, detalló que cuentan con camiones de alta potencia equipados con electrobombas y mangueras de casi dos kilómetros, con capacidad para evacuar entre 400 y 450 litros de agua por segundo.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/7-o-60-litros-por-metro-cuadrado-en-piura-dudas-sobre-cuanto-llovio-en-piura-este-martes-20-de-octubre/</t>
+          <t>https://elcomercio.pe/peru/piura/lluvias-en-piura-evacuan-el-agua-acumulada-mediante-sistemas-de-drenaje-pluvial-fenomeno-el-nino-apuesplan-ultimas-noticia/</t>
         </is>
       </c>
     </row>
@@ -2339,17 +2345,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Piura: ministros anuncian despliegue de motobombas tras inundaciones en Ignacio Merino</t>
+          <t>Lluvias de fuerte intensidad se registran en diversas partes de Piura y Tumbes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>La urbanización Ignacio Merino, en Piura, fue uno de los sectores más afectados por las lluvias registradas el martes. Hasta esta zona llegaron los ministros de Defensa, Rafael Belaunde, y de Desarrollo Agrario y Riego, Marco Vinelli, para coordinar acciones destinadas a evacuar el agua acumulada y atender a las familias damnificadas. Durante la visita, los funcionarios se reunieron con personal técnico y vecinos, quienes exigieron soluciones inmediatas ante las inundaciones que afectaron sus viviendas. Los pobladores advirtieron que el agua ingresó a sus casas y provocó daños en sus pertenencias, además de comprometer el sistema de desagüe. “Lo que se está observando es un porcentaje, será un 10% de lo que verdaderamente representa el peligro de la cantidad de agua. Se nos mete a la casa”, manifestó uno de los residentes, quien pidió a las autoridades apoyo para aliviar la situación de las familias. El ministro Marco Vinelli informó que las lluvias inundaron seis puntos de la ciudad de Piura y que el Ministerio de Defensa dispuso el despliegue de personal militar para atender las emergencias. “Nos está faltando sacar esta agua que está acá en esta zona. En este momento estamos hablando con el ministro de Vivienda para que traiga un hidrojet y empiece a evacuar el agua que ha quedado acá”, señaló. El titular del Midagri sostuvo que Ignacio Merino era uno de los puntos que todavía requerían atención y aseguró que los ministros habían acudido para resolver los problemas pendientes. También indicó que las acciones se realizarían de manera coordinada entre los distintos niveles de gobierno. Por su parte, el ministro Rafael Belaunde explicó que, tras conocer la emergencia, se comunicó con el comandante de la Primera Región Militar para disponer la salida de personal y equipos del Ejército, incluidas máquinas trasvasadoras para retirar el agua acumulada. Además, anunció que se trabaja en un convenio para desplegar rápidamente motobombas del Ministerio de Vivienda con apoyo del personal militar. El objetivo es mejorar la capacidad de respuesta ante futuras lluvias y reducir los daños en las viviendas. “Lo importante acá es la velocidad de la capacidad de respuesta. No podemos evitar que llueva y que caiga el agua. Lo que tenemos que estar es en las mejores condiciones posibles para agarrar esa agua y drenarla, y secar las calles, y evitar tener el menor impacto posible en las viviendas”, afirmó Belaunde. El comandante de la Primera Región Militar, general Carlos Rabanal, indicó que las labores de drenaje se concentrarán principalmente en Ignacio Merino y el sector de El Chilcal, donde las máquinas trasvasadoras permanecerán de manera permanente. El oficial señaló que dispone de 480 efectivos para estas tareas y que la región cuenta con cerca de 6,000 militares. Asimismo, explicó que se coordinará con los gobiernos locales para disponer de motobombas de seis pulgadas y camionetas que permitan trasladar e instalar los equipos en los puntos críticos en el menor tiempo posible. Según Rabanal, estas acciones buscan atender los sectores que presentan acumulación de agua y carecen de sistemas adecuados de drenaje. Añadió que la emergencia permitirá revisar y mejorar los procedimientos de respuesta y la coordinación entre las instituciones. Consultado sobre las inundaciones recurrentes en Piura, el ministro de Desarrollo Agrario y Riego sostuvo que la magnitud de los impactos dependerá de la cantidad de agua que se registre y advirtió sobre las condiciones asociadas al fenómeno El Niño. Vinelli afirmó que los indicadores de temperatura se encuentran por encima de los registrados durante los eventos de 1997 y 1982. También señaló que, desde el inicio de la actual gestión, se han realizado trabajos de descolmatación a cargo de los sectores de Agricultura, Defensa y Vivienda. Finalmente, Vinelli reconoció el malestar de los vecinos y reiteró que se continuará trabajando para retirar el agua acumulada. También pidió la participación de la ciudadanía en la prevención de emergencias, mediante el cuidado de sus pertenencias y evitando arrojar residuos a ríos y canales.</t>
+          <t>Lluvias de fuerte intensidad se registraron desde la noche del 19 de octubre en distintos puntos de la región Piura y Tumbes, en el norte del país . De acuerdo con una publicación de la cuenta meteorológica Asismet, las imágenes satelitales mostraban precipitaciones también sobre la ciudad de Piura. El aeropuerto, en tanto, reportó un acumulado de 2 milímetros de agua hasta las 9 de la noche. En Chulucanas, la lluvia sorprendió a las personas que participaban en la procesión del Señor de los Milagros. Por su parte, un reporte en la cuenta de Abraham Levy informó sobre un foco lluvioso en la ciudad de Piura. Su reporte estuvo acompañado de una imagen satelital correspondiente a las 8:30 de la noche, donde se ve el fenómeno. Las lluvias registradas en Tumbes activaron quebradas y afectaron vías de acceso, principalmente en el distrito de Pampas de Hospital. Según lo reportado, las lluvias comenzaron alrededor de las 5:00 a. m. y evidenciaron la vulnerabilidad de la región. Según el Senamhi, las condiciones climáticas serán monitoreadas ante la posibilidad de que las precipitaciones aumenten en los próximos días. Cabe recordar que las lluvias en la costa norte del Perú podrían alcanzar acumulados de hasta 300 milímetros en un solo día durante el verano de 2027, mientras que diversas regiones de la sierra sur y otras zonas del país afrontarían un déficit de precipitaciones que podría comprometer la disponibilidad de agua para la agricultura y el abastecimiento de los reservorios. Según el vocero del Servicio Nacional de Meteorología e Hidrología (Senamhi), Nelson Quispe, la fase extraordinaria se prolongará hasta enero del próximo año y luego entrará a la etapa fuerte que se extenderá hasta el otoño. Tras la lluvia intensa que se registró, el fenómeno evidenció los problemas de drenaje en Piura. Pese a registrar solo 2.1 milímetros, provocó inundaciones y dejó vehículos atrapados. El Senamhi atribuyó las precipitaciones a un núcleo convectivo en la zona media alta de Piura, además de detectar lluvias de ligera a moderada intensidad en distintas zonas de la costa. Por otro lado, vecinos del distrito de Veintiséis de Octubre reportaron viviendas inundadas. Asimismo, ciudadanos del asentamiento humano 4 de Octubre informaron que sus calles quedaron inundadas por las precipitaciones. Por otro lado, en el sector de Los Tallanes, el agua ingresó a viviendas y afectó negocios, cuyos propietarios reportaron pérdidas de mercadería. A su vez, varios tramos de la avenida José Aguilar Santisteban se inundaron y algunos vehículos quedaron atrapados. En tanto, en el sector de Las Dalias, los residentes expresaron preocupación por las vías inconclusas tras los trabajos de pavimentación. Los vecinos señalaron que las lluvias convirtieron las calles en acumulaciones de agua y canales, dificultando el tránsito. En Tumbes, las lluvias afectaron a diversos puntos de la región, en especial al distrito de Pampas de Hosital. En ese distrito se activaron las quebradas Peña Blanca, Chacritas e Higuerón, lo que dificultó el tránsito de vehículos hacia zonas agrícolas. En la ciudad de Tumbes, en tanto, las precipitaciones dejaron aniegos en los alrededores del mercado, el barrio San José y el centro poblado Pampa Grande. El mar frente al litoral piurano mantiene temperaturas superficiales superiores a sus valores habituales. Según información de la Dirección de Hidrografía y Navegación (DHN), al 18 de octubre, el mar registró 26.2 °C en Talara y 25.9 °C en Paita, con anomalías de +8.1 °C y +8.5 °C, respectivamente. Las temperaturas elevadas del mar favorecen un aire más cálido de día y de noche, escenario que podría continuar durante las próximas semanas mientras persistan las anomalías. Las lluvias también afectaron otras localidades en la región Piura. El alcalde de Morropón, Richard Baca Palacios, advirtió este martes 20 de octubre que su jurisdicción ya sufre los efectos de lo que calificó como un “megafenómeno del Niño”. El funcionario informó que las precipitaciones en su jurisdicción provocaron inundaciones, la activación de una quebrada y un aumento del caudal del río. El alcalde solicitó a las autoridades regionales y nacionales maquinaria pesada para atender la emergencia. La autoridad precisó que las alcaldías afectadas en la región necesitan con urgencia combustible y bienes de ayuda humanitaria para responder a los daños. Según indicó, solicitó al gobierno demoler un antiguo puente al ingreso de Chulucanas, en riesgo de colapso por las lluvias, apenas Keiko Fujimori asumió la Presidencia. “Gracias a Dios que hace una semana y media empezó la demolición de este puente histórico, pero que, lamentablemente, por sus condiciones actuales, ya no servía y más bien podía caerse y eso podría afectar lo que es la estructura del otro puente”, indicó a RPP. La Defensoría del Pueblo en Piura, ante las lluvias intensas registradas el día de hoy que han provocado aniegos e inundaciones en numerosos sectores de esta ciudad, exhortó al gobernador regional y al alcalde provincial de Piura evaluar suspender de manera inmediata la apertura de nuevas zonas de intervención en las vías de la ciudad donde se vienen ejecutando diversas obras, en tanto no se culminen las labores pendientes en las avenidas y calles en las que actualmente puede verse zanjas y asfalto levantado. El pedido formó parte de un conjunto de recomendaciones que fueron dirigidas con carácter de urgencia por la sede defensorial con el fin de reducir los riesgos a la seguridad, integridad y libre tránsito de la población, principalmente en aquellas arterias en las que las fuertes precipitaciones provocó verdaderos lodazales que constituyen un serio riesgo para las personas que transitan diariamente. Como parte de las recomendaciones, se exhortó también a disponer acciones de coordinación y supervisión para que los contratistas cumplan con los plazos establecidos para la habilitación progresiva de las calles y avenidas actualmente intervenidas, que se ubican principalmente en el centro histórico de Piura. Asimismo, se pidió disponer la limpieza inmediata de las zonas intervenidas y de las calles afectadas por la acumulación de agua y lodo, garantizando el recojo de basura y residuos sólidos así como el retiro de desmontes, materiales excedentes y montículos de arena generados por las obras. Finalmente, entre otras medidas, también se requirió adoptar medidas urgentes para garantizar el tránsito peatonal y vehicular mediante la instalación de señalización preventiva, el acondicionamiento de rutas peatonales seguras y la identificación oportuna de puntos críticos, así como establecer una coordinación permanente con la Policía Nacional del Perú para el control del tránsito vehicular en las zonas afectadas. Cabe indicar que, tras las fuertes lluvias, la sede defensorial dirigió esta mañana un recorrido por las zonas más afectadas como los cruces de las calles Sullana con Bolognesi, sí como de la céntrica avenida Grau con la calle Junín y el Sistema Alternativo de Recolección y Evacuación de Aguas de Lluvia (SARE) ubicado cerca del parque Tres Culturas. El recorrido también comprendió las calles Ignacio Merino, la intersección de las avenidas Sullana y Blas de Atienza, así como el cruce de José Aguilar Santisteban con Azucena y la calle Los Dos Grifos, donde pudo comprobarse la falta de implementación de medidas de contingencia pese a la advertencia del grave impacto que tendrá el fenómeno El Niño actualmente en marcha.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://gestion.pe/peru/piura-ministros-anuncian-despliegue-de-motobombas-tras-inundaciones-en-ignacio-merino-noticia/</t>
+          <t>https://gestion.pe/peru/piura-lluvias-de-fuerte-intesidad-se-registran-en-diversas-partes-de-la-region-noticia/</t>
         </is>
       </c>
     </row>
@@ -2364,24 +2370,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lote 207: 7 empresas compiten para adjudicarse lote petrolero en Talara por 30 años</t>
+          <t>Piura: ministros anuncian despliegue de motobombas tras inundaciones en Ignacio Merino</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Siete empresas se encuentran en carrera para obtener la explotación de un lote petrolero ubicado en la cuenca Talara, en Piura. El proceso permitirá adjudicar un contrato de licencia por 30 años, con el objetivo de atraer nuevas inversiones e incrementar la producción de hidrocarburos en el noroeste del país. Se trata del Lote 207, conformado por la sección A del actual Lote XIII, cuyo contrato vence en diciembre de 2026. El área comprende 21,911.453 hectáreas y registra una producción promedio de 750 barriles diarios de petróleo. Perupetro informó que las siete empresas habilitadas y calificadas presentaron este miércoles 21 de octubre sus ofertas técnicas y económicas ante la comisión de selección, como parte del proceso de convocatoria para adjudicar el nuevo contrato de licencia. Durante el acto público se recibieron los documentos de admisibilidad y las propuestas de los participantes. Sin embargo, las ofertas todavía no han sido evaluadas, por lo que el ganador se conocerá el próximo lunes 26 de octubre. De acuerdo con Perupetro, los siete postores que presentaron sus propuestas son: Las empresas participantes deberán competir mediante sus compromisos de inversión para desarrollar las actividades de explotación y exploración contempladas en el proceso. La adjudicación del Lote 207 no dependerá únicamente del cumplimiento de los requisitos establecidos por Perupetro, sino también de las inversiones adicionales que los postores estén dispuestos a asumir. Según las bases del proceso, la buena pro se otorgará al participante que presente el mejor programa de trabajo, considerando los mayores compromisos de inversión destinados al reacondicionamiento y perforación de pozos, tanto de desarrollo como exploratorios. Estas inversiones deberán ser adicionales al Programa de Trabajo de Desarrollo y Exploratorio establecido previamente por Perupetro. El próximo 26 de octubre se realizará la apertura de las ofertas y su evaluación en acto público. Ese mismo día, la comisión de selección tiene previsto definir al adjudicatario. El nuevo contrato de licencia tendrá una vigencia de 30 años y busca garantizar la continuidad de las operaciones en el área, además de promover nuevas inversiones para incrementar la producción petrolera. Actualmente, el Lote 207 registra una producción promedio de 750 barriles diarios. Con la adjudicación, Perupetro espera impulsar el reacondicionamiento de pozos existentes y la perforación de nuevos pozos de desarrollo y exploración. La empresa estatal también señaló que el proceso busca generar mayores ingresos para el Estado mediante el aprovechamiento de los recursos de hidrocarburos. Por el momento, no se ha informado el monto de las inversiones que comprometerán los participantes. Este aspecto se conocerá con la apertura y evaluación de las propuestas programada para el próximo lunes.</t>
+          <t>La urbanización Ignacio Merino, en Piura, fue uno de los sectores más afectados por las lluvias registradas el martes. Hasta esta zona llegaron los ministros de Defensa, Rafael Belaunde, y de Desarrollo Agrario y Riego, Marco Vinelli, para coordinar acciones destinadas a evacuar el agua acumulada y atender a las familias damnificadas. Durante la visita, los funcionarios se reunieron con personal técnico y vecinos, quienes exigieron soluciones inmediatas ante las inundaciones que afectaron sus viviendas. Los pobladores advirtieron que el agua ingresó a sus casas y provocó daños en sus pertenencias, además de comprometer el sistema de desagüe. “Lo que se está observando es un porcentaje, será un 10% de lo que verdaderamente representa el peligro de la cantidad de agua. Se nos mete a la casa”, manifestó uno de los residentes, quien pidió a las autoridades apoyo para aliviar la situación de las familias. El ministro Marco Vinelli informó que las lluvias inundaron seis puntos de la ciudad de Piura y que el Ministerio de Defensa dispuso el despliegue de personal militar para atender las emergencias. “Nos está faltando sacar esta agua que está acá en esta zona. En este momento estamos hablando con el ministro de Vivienda para que traiga un hidrojet y empiece a evacuar el agua que ha quedado acá”, señaló. El titular del Midagri sostuvo que Ignacio Merino era uno de los puntos que todavía requerían atención y aseguró que los ministros habían acudido para resolver los problemas pendientes. También indicó que las acciones se realizarían de manera coordinada entre los distintos niveles de gobierno. Por su parte, el ministro Rafael Belaunde explicó que, tras conocer la emergencia, se comunicó con el comandante de la Primera Región Militar para disponer la salida de personal y equipos del Ejército, incluidas máquinas trasvasadoras para retirar el agua acumulada. Además, anunció que se trabaja en un convenio para desplegar rápidamente motobombas del Ministerio de Vivienda con apoyo del personal militar. El objetivo es mejorar la capacidad de respuesta ante futuras lluvias y reducir los daños en las viviendas. “Lo importante acá es la velocidad de la capacidad de respuesta. No podemos evitar que llueva y que caiga el agua. Lo que tenemos que estar es en las mejores condiciones posibles para agarrar esa agua y drenarla, y secar las calles, y evitar tener el menor impacto posible en las viviendas”, afirmó Belaunde. El comandante de la Primera Región Militar, general Carlos Rabanal, indicó que las labores de drenaje se concentrarán principalmente en Ignacio Merino y el sector de El Chilcal, donde las máquinas trasvasadoras permanecerán de manera permanente. El oficial señaló que dispone de 480 efectivos para estas tareas y que la región cuenta con cerca de 6,000 militares. Asimismo, explicó que se coordinará con los gobiernos locales para disponer de motobombas de seis pulgadas y camionetas que permitan trasladar e instalar los equipos en los puntos críticos en el menor tiempo posible. Según Rabanal, estas acciones buscan atender los sectores que presentan acumulación de agua y carecen de sistemas adecuados de drenaje. Añadió que la emergencia permitirá revisar y mejorar los procedimientos de respuesta y la coordinación entre las instituciones. Consultado sobre las inundaciones recurrentes en Piura, el ministro de Desarrollo Agrario y Riego sostuvo que la magnitud de los impactos dependerá de la cantidad de agua que se registre y advirtió sobre las condiciones asociadas al fenómeno El Niño. Vinelli afirmó que los indicadores de temperatura se encuentran por encima de los registrados durante los eventos de 1997 y 1982. También señaló que, desde el inicio de la actual gestión, se han realizado trabajos de descolmatación a cargo de los sectores de Agricultura, Defensa y Vivienda. Finalmente, Vinelli reconoció el malestar de los vecinos y reiteró que se continuará trabajando para retirar el agua acumulada. También pidió la participación de la ciudadanía en la prevención de emergencias, mediante el cuidado de sus pertenencias y evitando arrojar residuos a ríos y canales.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://gestion.pe/economia/lote-207-7-empresas-compiten-para-adjudicarse-el-lote-petrolero-en-talara-por-30-anos-noticia/</t>
+          <t>https://gestion.pe/peru/piura-ministros-anuncian-despliegue-de-motobombas-tras-inundaciones-en-ignacio-merino-noticia/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Gestión</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -2389,17 +2395,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sechura no se va a inundar si el río Piura logra salir por lo que fue una parte de su desfogue natural, señala especialista</t>
+          <t>Lote 207: 7 empresas compiten para adjudicarse lote petrolero en Talara por 30 años</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sobre el tema el ingeniero con más de 50 años de experiencia y experto en temas de hidráulica, Eduardo Zegarra, señaló que no hay riesgo para Sechura si el río logra salir por lo que fue una parte de su desfogue natural. “La salida del río Piura está a la vuelta de la esquina y a un precio menor al lado de tanto dinero que se sigue botando en hacer descolmataciones. Aquí el gran descolmatador es el mismo río Piura, pero cuando salga por donde debe salir [...] Si el río sale por río Loco ya no tienes que hacer más porque ya tienes un cauce más grande en la ciudad de Piura. Mientras en Piura pasa todo el caudal del río, por Sechura no va a llegar todo, ya que el caudal se va a dividir. Una parte se va a seguir yendo hacia Pampa de las Salinas pasando por Chutuque”, consideró. Dos salidas Estimó que si llega un caudal de 4000 metros cúbicos por segundo, hacia Sechura se irán unos 2 mil y el resto se va por el otro lado. “En 1983 todo se fue por Sechura. Llegaron unos 3.200 m3/seg y así estuvo saliendo el agua por Sechura y no hubo ningún ahogado. Ahora si alguien se ha metido al cauce, ya es su problema. Además, Sechura tiene un puente de casi 180 metros de longitud, mientras que en Piura ningún puente llega a 110 metros”, manifestó. Relató que lamentablemente después de 1983 la ruta que se le impuso al río no fue hacia Sechura sino hacia la laguna Ramón, la cual se ubica cerca de la zona de Chutuque, Pampa de Las Salinas y luego sale por la bocana de Virrilá. En años de lluvias fuertes, el río rompe la carretera hacia Bayóvar y forma La Niña. Sedimentos Consideró que el gran problema de esta ruta son los sedimentos que harán desaparecer las lagunas incluso la laguna de Ñapique, asegura. “En el año 1998 vinieron 4 mil metros cúbicos por segundo y el río no se desbordó en la ciudad porque todavía no había tanto sedimento dentro del cauce. Los sedimentos no saldrán mientras no se desatore el desfogue. La descolmatación que están haciendo ayuda muy poco, porque el trabajo serio y que va a solucionar el problema es cuando comience a salir el agua por río Loco y salga al mar”, afirmó. Puntualizó que las llegadas de las avenidas del río son progresivas y se agudizan después de diciembre con el inicio de las lluvias de mayor intensidad. “Una vez que ya se haya establecido el flujo del río Piura por su ruta más corta, comienza a jalar [los sedimentos] porque tiene velocidad. La otra alternativa es una salida al mar después de una vuelta olímpica. Lo que por Sechura sería un aproximado de 20 kilómetros por el otro lado serían más de 100 kilómetros, así es la proporción”, manifestó. Maricultores En relación a los plazos, el especialista consideró que si se contrata una empresa seria con gran cantidad de maquinaria y con varios turnos de trabajo al día, se podría lograr intervenir en un plazo de hasta dos meses. Finalmente, Zegarra señaló que la actividad de maricultores podría sufrir un impacto, al igual que el resto de actividades productivas del país. Sin embargo, la salida del río por Sechura podría beneficiar a las especies marinas debido a la gran cantidad de nutrientes que llegaría con el agua del río, mencionó.</t>
+          <t>Siete empresas se encuentran en carrera para obtener la explotación de un lote petrolero ubicado en la cuenca Talara, en Piura. El proceso permitirá adjudicar un contrato de licencia por 30 años, con el objetivo de atraer nuevas inversiones e incrementar la producción de hidrocarburos en el noroeste del país. Se trata del Lote 207, conformado por la sección A del actual Lote XIII, cuyo contrato vence en diciembre de 2026. El área comprende 21,911.453 hectáreas y registra una producción promedio de 750 barriles diarios de petróleo. Perupetro informó que las siete empresas habilitadas y calificadas presentaron este miércoles 21 de octubre sus ofertas técnicas y económicas ante la comisión de selección, como parte del proceso de convocatoria para adjudicar el nuevo contrato de licencia. Durante el acto público se recibieron los documentos de admisibilidad y las propuestas de los participantes. Sin embargo, las ofertas todavía no han sido evaluadas, por lo que el ganador se conocerá el próximo lunes 26 de octubre. De acuerdo con Perupetro, los siete postores que presentaron sus propuestas son: Las empresas participantes deberán competir mediante sus compromisos de inversión para desarrollar las actividades de explotación y exploración contempladas en el proceso. La adjudicación del Lote 207 no dependerá únicamente del cumplimiento de los requisitos establecidos por Perupetro, sino también de las inversiones adicionales que los postores estén dispuestos a asumir. Según las bases del proceso, la buena pro se otorgará al participante que presente el mejor programa de trabajo, considerando los mayores compromisos de inversión destinados al reacondicionamiento y perforación de pozos, tanto de desarrollo como exploratorios. Estas inversiones deberán ser adicionales al Programa de Trabajo de Desarrollo y Exploratorio establecido previamente por Perupetro. El próximo 26 de octubre se realizará la apertura de las ofertas y su evaluación en acto público. Ese mismo día, la comisión de selección tiene previsto definir al adjudicatario. El nuevo contrato de licencia tendrá una vigencia de 30 años y busca garantizar la continuidad de las operaciones en el área, además de promover nuevas inversiones para incrementar la producción petrolera. Actualmente, el Lote 207 registra una producción promedio de 750 barriles diarios. Con la adjudicación, Perupetro espera impulsar el reacondicionamiento de pozos existentes y la perforación de nuevos pozos de desarrollo y exploración. La empresa estatal también señaló que el proceso busca generar mayores ingresos para el Estado mediante el aprovechamiento de los recursos de hidrocarburos. Por el momento, no se ha informado el monto de las inversiones que comprometerán los participantes. Este aspecto se conocerá con la apertura y evaluación de las propuestas programada para el próximo lunes.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sechura-no-se-va-a-inundar-si-el-rio-piura-logra-salir-por-lo-que-fue-una-parte-de-su-desfogue-natural-senala-especialista/</t>
+          <t>https://gestion.pe/economia/lote-207-7-empresas-compiten-para-adjudicarse-el-lote-petrolero-en-talara-por-30-anos-noticia/</t>
         </is>
       </c>
     </row>
@@ -2414,17 +2420,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Piura evacúa el agua acumulada por las lluvias mediante sistemas de drenaje pluvial</t>
+          <t>Piura lidera los contagios de dengue en el Perú con más de 13 mil casos y 9 fallecidos</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>La región Piura logró evacuar el agua acumulada por las inundaciones registradas en distintos distritos debido a las fuertes lluvias, mediante sistemas de drenaje pluvial instalados en los puntos más críticos. Las labores concluyeron esta tarde, informó Renato Ameri Moreno, jefe de Seguridad y Defensa Nacional del Ministerio de Vivienda, Construcción y Saneamiento (MVCS). En declaraciones a TVPerú Noticias, el funcionario señaló que los sistemas alternativos de recolección de agua de lluvia permitieron atender las zonas afectadas por las precipitaciones. “Hoy, debido a las lluvias, Piura se ha visto afectada por inundaciones en distintos distritos. Sin embargo, nuestros equipos de los sistemas alternativos de recolección de agua de lluvia han funcionado en los puntos más críticos, donde hemos instalado estos sistemas”, declaró. Ameri Moreno explicó que los mecanismos de drenaje se implementaron mediante tuberías subterráneas que conducen el agua acumulada hacia zonas seguras, como canales, drenes o ríos. Precisó que estos sistemas permiten recolectar el agua de lluvia en las denominadas cuencas ciegas, áreas donde el líquido se concentra y que no cuentan con una vía natural de evacuación. El representante del MVCS destacó que las medidas de prevención implementadas en Piura ante el fenómeno El Niño (FEN) facilitaron las labores de drenaje. Según indicó, la región cuenta con 20 sistemas de drenaje, de los cuales nueve son administrados por el Ministerio de Vivienda. Además, hace aproximadamente un mes se desplegaron 20 motobombas en distintos distritos. El funcionario también señaló que se dispone de un almacén de emergencia para distribuir equipos según las necesidades y que se entregaron unidades a los municipios para atender las cuencas ciegas. Asimismo, detalló que cuentan con camiones de alta potencia equipados con electrobombas y mangueras de casi dos kilómetros, con capacidad para evacuar entre 400 y 450 litros de agua por segundo.</t>
+          <t>La Dirección Regional de Salud y el Centro Nacional de Epidemiología, Prevención y Control de Enfermedades informaron que la región de Piura encabeza la lista de contagios por dengue en el país con 13,025 infectados. Las entidades oficiales reportan además 9 fallecidos por la enfermedad en el departamento norteño. La Sala Situacional de la Diresa precisó que el 68% de los casos notificados contó con la debida confirmación de laboratorio. El reporte sanitario detalló la presencia del serotipo 3 del virus y advirtió sobre cuadros graves con necesidad de hospitalización en la zona. A nivel provincial, Piura acumula la cifra más alta de la región con 5,453 contagiados en sus diferentes distritos. Las provincias de Morropón y Sullana siguieron en la estadística oficial con 3,810 y 3,016 personas afectadas respectivamente. Los adultos de 30 a 59 años representan el 30,2% de los infectados en la región. Los niños de 0 a 11 años concentraron 3,414 infectados y cinco de los decesos registrados por las autoridades médicas. El Ministerio de Salud inició la aplicación de la vacuna Qdenga para personas entre los 10 y 20 años de edad para frenar el avance del dengue. La cobertura de la inmunización alcanza un 34,8% en la primera dosis y un 58% en la segunda aplicación dentro de los grupos prioritarios. El CDC del Minsa notificó 71,256 casos y 75 muertes por la epidemia a nivel nacional. En Lima se concentran aproximadamente unos 6,000 casos confirmados, mientras que se registran solo en Piura unos 1,000 contagios por semana desde hace varios días. El director general del Centro Nacional de Epidemiología, Prevención y Control de Enfermedades (CDC), César Munayco, informó a Canal N que las otras regiones que le siguen a Piura en número de contagios son La Libertad y Lambayeque. En esa línea, advirtió que las cifras seguirán incrementando si el calor y las lluvias persisten en la zona norte del país. Desde este lunes 19 de octubre se registran intensas lluvias que han inundados las calles y viviendas de Chulucanas en la provincia de Morropón, entre otros sectores vulnerables de Piura. El agua acumulada sobrepasó los 30 centímetros de altura en los mercados locales y provocó el colapso del sistema de alcantarillado. El fenómeno El Niño Costero originó lluvias continuas y elevadas temperaturas durante varios días consecutivos en la región. La acumulación de agua en recipientes inservibles multiplica los criaderos del mosquito Aedes aegypti y eleva el riesgo de nuevos contagios. La emergencia está siendo atendida con el despliegue de motobombas para disminuir el nivel del agua en las calles inundadas. Asimismo, se cuenta con el apoyo de miembros de las Fuerzas Armadas y la vigilancia de personal de la Defensoría del Pueblo para constatar la situación.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/lluvias-en-piura-evacuan-el-agua-acumulada-mediante-sistemas-de-drenaje-pluvial-fenomeno-el-nino-apuesplan-ultimas-noticia/</t>
+          <t>https://elcomercio.pe/peru/piura/piura-lidera-los-contagios-de-dengue-en-el-peru-con-mas-de-13-mil-casos-y-nueve-fallecidos-apuesplan-ultimas-noticia/</t>
         </is>
       </c>
     </row>
@@ -2489,17 +2495,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fenómeno El Niño: Lluvias en Piura y Tumbes continuarán en las próximas horas</t>
+          <t>Ejército utiliza bombas de transvase para evacuar agua acumulada en urbanizaciones de Piura</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) advirtió que las lluvias registradas en las primeras horas de este martes 20 de octubre en Piura y Tumbes continuarán durante las próximas horas y podrían prolongarse en los siguientes días. La especialista del Senamhi, Noelia Goicochea, dijo en TV Perú que se mantiene vigente un aviso meteorológico para la costa norte del país respecto a nuevas precipitaciones. La especialista indicó que entre hoy y mañana miércoles 21 se podrían registrar nuevas precipitaciones en Tumbes y Piura, por lo que se mantiene un periodo lluvioso en ambas regiones. “Para los próximos días también esperamos todavía que se puedan presentar lluvias de moderada a fuerte intensidad para lo que es el sector de la costa norte”, señaló. Goicochea informó que durante la noche del lunes 19 y la madrugada de hoy martes 20 se reportaron precipitaciones en distintos sectores de ambas regiones, con acumulados importantes en localidades próximas a la frontera con Ecuador. Uno de los mayores registros se presentó en Matapalo, Tumbes, donde se acumularon entre 56 y 57 milímetros de lluvia. En sectores del interior de Piura y zonas cercanas a la cordillera se reportaron valores de entre 16 y 18 milímetros hasta las 07:00 horas. Durante las primeras horas de la mañana, las lluvias se reactivaron en estas localidades y posteriormente continuaron de manera intermitente, con una disminución de su intensidad en algunos sectores. Según detalló Andina, la especialista del Senamhi afirmó que las precipitaciones también alcanzaron las provincias de Sullana, Morropón y Piura, así como sectores de Sechura. En ese contexto, el Senamhi informó, a través de sus canales oficiales, que se presentan lluvias en la costa de Tumbes y Piura, y que estas podrían continuar durante las próximas horas, de acuerdo con el aviso meteorológico vigente.</t>
+          <t>El Ejército del Perú desplegó dos bombas de transvase para evacuar el agua acumulada en las urbanizaciones Ignacio Merino y Chilcal, en Piura, afectadas por las intensas lluvias registradas en la región. Los equipos trasladan el agua empozada hacia drenes que desembocan en el río Piura, como parte de las acciones de atención ante las inundaciones asociadas al fenómeno El Niño. El general de División EP Carlos Rabanal, comandante del Comando Operacional del Norte, explicó que las máquinas, de 12 pulgadas, fueron trasladadas por personal militar hasta los sectores afectados para facilitar la evacuación del agua acumulada. Una de las bombas fue destinada a la urbanización Ignacio Merino y la otra a Chilcal. Según informó el Ejército, los equipos se utilizan en apoyo a los Sistemas Alternativos de Recolección y Evacuación de Aguas de Lluvia (SARES), con el objetivo de retirar el agua empozada y reducir las anegaciones. Estas labores se realizan con personal militar capacitado por el Ministerio de Vivienda, Construcción y Saneamiento para operar los equipos de transvase y conducir el agua hacia los drenes que desembocan en el río Piura. Como parte de las medidas preventivas frente al fenómeno El Niño, el Ejército del Perú también verificó el funcionamiento de sus sistemas de comunicación en Piura, Tumbes y Amazonas, con el propósito de fortalecer su capacidad de respuesta ante posibles emergencias en zonas vulnerables. Las comunicaciones permitirán mantener el contacto con las Compañías de Intervención Rápida para Desastres (CIRD), especialmente en comunidades que podrían quedar aisladas. De esta manera, se busca agilizar la toma de decisiones y facilitar el desplazamiento de personal, equipos y ayuda humanitaria hacia las zonas afectadas. Las pruebas estuvieron a cargo de la I División de Ejército y el Batallón de Comunicaciones N.° 111, que estableció enlaces con cuatro organizaciones militares: el Cuartel General de la I División de Ejército y el Agrupamiento de Artillería Inclán, en Piura; la 9.ª Brigada Blindada, en Tumbes; y la 1.ª Brigada de Protección de la Amazonía, en Amazonas. Para los ejercicios se emplearon equipos de radiocomunicación Hytera y plataformas tecnológicas que permiten intercambiar información entre las unidades militares. Las pruebas permitieron comprobar el funcionamiento de los sistemas y evaluar la continuidad y confiabilidad de las comunicaciones ante posibles situaciones de emergencia. Asimismo, se evaluó la coordinación entre los mandos militares y las unidades encargadas de intervenir ante desastres, a fin de identificar posibles dificultades y optimizar el uso de los equipos disponibles. Estas acciones forman parte de las medidas impulsadas por el Ministerio de Defensa para fortalecer la capacidad operativa de las Fuerzas Armadas frente al fenómeno El Niño y facilitar la coordinación de intervenciones y el despliegue de recursos en las zonas afectadas.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/lluvias-en-piura-y-tumbes-continuaran-en-las-proximas-horas-advierte-el-senamhi-fenomeno-el-nino-apuesplan-ultimas-noticia/</t>
+          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-ejercito-utiliza-bombas-de-transvase-para-evacuar-agua-acumulada-en-urbanizaciones-de-piura-apuesplan-ultimas-noticia/</t>
         </is>
       </c>
     </row>
@@ -2589,17 +2595,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ejército utiliza bombas de transvase para evacuar agua acumulada en urbanizaciones de Piura</t>
+          <t>Piura: primeras lluvias dejan al menos nueve puntos afectados mientras continúan obras de prevención</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>El Ejército del Perú desplegó dos bombas de transvase para evacuar el agua acumulada en las urbanizaciones Ignacio Merino y Chilcal, en Piura, afectadas por las intensas lluvias registradas en la región. Los equipos trasladan el agua empozada hacia drenes que desembocan en el río Piura, como parte de las acciones de atención ante las inundaciones asociadas al fenómeno El Niño. El general de División EP Carlos Rabanal, comandante del Comando Operacional del Norte, explicó que las máquinas, de 12 pulgadas, fueron trasladadas por personal militar hasta los sectores afectados para facilitar la evacuación del agua acumulada. Una de las bombas fue destinada a la urbanización Ignacio Merino y la otra a Chilcal. Según informó el Ejército, los equipos se utilizan en apoyo a los Sistemas Alternativos de Recolección y Evacuación de Aguas de Lluvia (SARES), con el objetivo de retirar el agua empozada y reducir las anegaciones. Estas labores se realizan con personal militar capacitado por el Ministerio de Vivienda, Construcción y Saneamiento para operar los equipos de transvase y conducir el agua hacia los drenes que desembocan en el río Piura. Como parte de las medidas preventivas frente al fenómeno El Niño, el Ejército del Perú también verificó el funcionamiento de sus sistemas de comunicación en Piura, Tumbes y Amazonas, con el propósito de fortalecer su capacidad de respuesta ante posibles emergencias en zonas vulnerables. Las comunicaciones permitirán mantener el contacto con las Compañías de Intervención Rápida para Desastres (CIRD), especialmente en comunidades que podrían quedar aisladas. De esta manera, se busca agilizar la toma de decisiones y facilitar el desplazamiento de personal, equipos y ayuda humanitaria hacia las zonas afectadas. Las pruebas estuvieron a cargo de la I División de Ejército y el Batallón de Comunicaciones N.° 111, que estableció enlaces con cuatro organizaciones militares: el Cuartel General de la I División de Ejército y el Agrupamiento de Artillería Inclán, en Piura; la 9.ª Brigada Blindada, en Tumbes; y la 1.ª Brigada de Protección de la Amazonía, en Amazonas. Para los ejercicios se emplearon equipos de radiocomunicación Hytera y plataformas tecnológicas que permiten intercambiar información entre las unidades militares. Las pruebas permitieron comprobar el funcionamiento de los sistemas y evaluar la continuidad y confiabilidad de las comunicaciones ante posibles situaciones de emergencia. Asimismo, se evaluó la coordinación entre los mandos militares y las unidades encargadas de intervenir ante desastres, a fin de identificar posibles dificultades y optimizar el uso de los equipos disponibles. Estas acciones forman parte de las medidas impulsadas por el Ministerio de Defensa para fortalecer la capacidad operativa de las Fuerzas Armadas frente al fenómeno El Niño y facilitar la coordinación de intervenciones y el despliegue de recursos en las zonas afectadas.</t>
+          <t>Por segunda vez en menos de un mes, Piura registró lluvias que provocaron aniegos en calles, avenidas y viviendas, además de dificultades para el tránsito vehicular. Según el Servicio Nacional de Meteorología e Hidrología (Senamhi), estas precipitaciones corresponden a los primeros episodios de lluvias asociados al fenómeno El Niño. Entre la noche del lunes 19 y la mañana del martes 20 de octubre, las precipitaciones de baja intensidad afectaron al menos nueve puntos de la región, a pocos meses del periodo de mayor intensidad previsto por el organismo. En distintos puntos de la región se reportaron aniegos en las urbanizaciones Ignacio Merino y Santa Margarita, el asentamiento humano Las Dalias, así como en las zonas de Dos Grifos, Santa Rosa, Piura y el centro histórico. A estos lugares se suman la avenida Los Algarrobos, donde se registraron dificultades para el tránsito vehicular, y el Mercado Modelo de Chulucanas, donde el agua ingresó a los establecimientos comerciales. También se reportaron afectaciones en Castilla, Catacaos y otros sectores de la región. Las precipitaciones afectaron casas, avenidas, centros educativos y tiendas comerciales en distintos puntos de la región. En Ignacio Merino, el agua llegó a ingresar a viviendas, mientras que en el Mercado Modelo de Chulucanas se reportaron acumulaciones de hasta 30 centímetros que perjudicaron las actividades comerciales. Asimismo, en algunas vías se registraron dificultades para el tránsito vehicular debido a la acumulación de agua. La ingeniera Grinia Ávalos, jefa institucional del Senamhi, explicó en entrevista con El Comercio que las precipitaciones corresponden al segundo episodio de lluvias asociado al fenómeno El Niño, luego de que el 24 de septiembre se registrara un adelanto de la temporada en la costa norte. Según precisó, las lluvias acumuladas en la parte baja de Piura alcanzaron entre 6 y 7 milímetros. Aunque se trata de precipitaciones ligeras, su persistencia ha sido suficiente para provocar aniegos. “No son lluvias importantes, no son lluvias fuertes, digamos, pero la acumulación, la persistencia de estas lluvias sí empieza a generar aniegos en la parte baja”, explicó. Ávalos señaló que Piura presenta deficiencias en sus mecanismos de evacuación de aguas pluviales. Recordó que una situación similar ocurrió semanas atrás en Máncora, donde precipitaciones acumuladas de aproximadamente 16 milímetros provocaron aniegos. Obras de prevención todavía en ejecución Las primeras precipitaciones encuentran a Piura con intervenciones de drenaje y descolmatación que todavía no han concluido. Uno de los proyectos pendientes es el drenaje pluvial del centro histórico, a cargo del Gobierno Regional de Piura. Ralph Zapata, periodista y director de Norte Sostenible, señaló a El Comercio que esta obra, cuya inversión bordea los S/130 millones, acumula retrasos, ampliaciones de plazo y adicionales presupuestales. Según indicó, su culminación se habría postergado hasta 2027. El periodista también cuestionó la experiencia de la empresa contratista. La ausencia de una solución integral de drenaje constituye otro de los problemas señalados por Zapata. Explicó que varios de los sectores afectados corresponden a cuencas ciegas, zonas bajas donde el agua se acumula y que históricamente han registrado inundaciones. “Piura no tiene drenaje pluvial y por eso es que ves que Ignacio Merino, 26 de Octubre, Piura y Castilla están inundados”, señaló. A diferencia del drenaje urbano, los trabajos de descolmatación buscan retirar sedimentos y otros materiales acumulados en los cauces de los ríos para mejorar su capacidad de conducción del agua. Tan solo el fin de semana pasado, durante su visita a Piura el 16 de octubre, la presidenta Keiko Fujimori supervisó estas intervenciones junto con los ministros de Desarrollo Agrario y Riego, Marco Vinelli, y de Defensa, Rafael Belaúnde. De acuerdo con la información oficial, en Piura se programaron 21 intervenciones que comprenden 49.35 kilómetros de cauces de ríos y quebradas. En el tramo Los Ejidos–Puente Bolognesi, los trabajos registraban un avance físico del 100%, mientras que el volumen de descolmatación alcanzaba el 85,30%. Sin embargo, los avances reportados no eran uniformes en todos los sectores. Las intervenciones en El Milagro–La Encantada y Piedra Negra registraban avances de 27,59% y 20,73%, respectivamente, según la información difundida durante la supervisión presidencial. Zapata advirtió que, mientras los trabajos habían avanzado en el tramo urbano del río Piura, persistían retrasos en el Bajo Piura, donde todavía se observaban sectores con acumulación de sedimentos y vegetación. El Gobierno anunció el traslado de maquinaria hacia esta zona a partir del 18 de octubre, con el objetivo de continuar las intervenciones en el aliviadero Chutuque y el río Loco. También estableció como plazo de referencia el 30 de noviembre para culminar los trabajos de preparación del río. “De esta manera, quiero decirle a todos los piuranos que aquí, en el río Piura, se ha trabajado y se ha logrado la máxima capacidad del río. Más de esto no puede hacerse porque, como ustedes pueden ver, está el agua”, declaró Fujimori durante su visita. Respuesta ante los primeros aniegos Frente a las precipitaciones registradas, el Ministerio de Vivienda informó que cinco de sus ocho sistemas alternativos de recolección y evacuación de aguas pluviales se encontraban operando en Cinco Esquinas, El Chilcal, Ignacio Merino, La Molina II y Dos Grifos. Asimismo, reportó el despliegue de dos equipos trasvasadores para atender la acumulación de agua en los sectores afectados, en tanto trabajan con el apoyo del Ejercito y coordinan con el Gobierno Regional de Piura, asi como con los municipios afectados para estimar el desplazamiento de las motobombas a puntos más críticos. En riesgo crítico La situación de la infraestructura de servicios básicos constituye otro factor de riesgo. La Superintendencia Nacional de Servicios de Saneamiento (Sunass) identificó 101 infraestructuras de agua potable y saneamiento en riesgo crítico, de un total de 135 evaluadas en cinco regiones del norte del país. Según el organismo regulador, Piura concentra una población expuesta de aproximadamente 1,3 millones de personas ante posibles afectaciones a estos servicios por eventos climáticos extremos como el fenómeno El Niño. Ante este escenario, la Sunass recomendó a las empresas prestadoras de agua potable y saneamiento activar sus planes de gestión reactiva, garantizar la disponibilidad de grupos electrógenos y equipos de respaldo, así como adoptar medidas de protección de la infraestructura crítica frente a posibles lluvias e inundaciones Por su parte, el Gobierno anunció la preparación de albergues temporales con capacidad para atender a cerca de 30.000 personas que deban abandonar sus viviendas en caso de emergencia en las regiones vulnerables del país. El Comercio solicitó al Gobierno Regional de Piura una entrevista con un vocero para conocer el estado actual del proyecto de drenaje pluvial del centro histórico, así como las acciones implementadas ante los recientes aniegos y las medidas previstas frente a las próximas lluvias. Sin embargo, hasta el cierre de esta edición, la entidad no atendió el requerimiento. Lluvias más intensas hacia el verano La jefa institucional del Senamhi advirtió que las precipitaciones actuales forman parte de episodios que se presentan de manera intermitente y cuya frecuencia e intensidad aumentarán durante los próximos meses. El episodio de lluvias iniciado esta semana se extendería hasta el 23 o 24 de octubre. Posteriormente, se espera un periodo de mejores condiciones meteorológicas antes de que los eventos de lluvia se vuelvan más frecuentes hacia noviembre y diciembre. Ávalos explicó que las temperaturas del mar bordean actualmente los 26 grados, un valor inusual para esta época del año. Según indicó, el calentamiento observado supera las condiciones registradas durante los eventos extraordinarios de El Niño de las décadas de 1980 y 1990. Los pronósticos extendidos del Senamhi contemplan un escenario de precipitaciones superiores a lo normal durante el verano de 2027. En la costa norte podrían registrarse acumulados progresivos de 100, 150 y 200 milímetros, con un periodo de mayor intensidad entre febrero y marzo. La especialista señaló que en Piura y Tumbes podrían alcanzarse acumulados de hasta 250 milímetros, principalmente en esta última región, por su cercanía al golfo de Guayaquil. Tampoco descartó que se alcancen o superen los máximos históricos cercanos a los 270 milímetros registrados en Tumbes. Además de los aniegos que ya se presentan en zonas urbanas, Ávalos advirtió que las primeras precipitaciones pueden contribuir a la saturación del suelo y aumentar las afectaciones cuando lleguen las lluvias más intensas. “Sí van a generar aniegos, digamos, en la zona baja, va a saturar el suelo de manera que cuando ya tengamos las lluvias fuertes verdaderas, asociadas a El Niño, entre diciembre sobre todo, ya puede haber afectación en las cuencas”, explicó.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-ejercito-utiliza-bombas-de-transvase-para-evacuar-agua-acumulada-en-urbanizaciones-de-piura-apuesplan-ultimas-noticia/</t>
+          <t>https://elcomercio.pe/peru/piura/piura-primeras-lluvias-dejan-al-menos-nueve-puntos-afectados-mientras-continuan-obras-de-prevencion-apuesplan-noticia/</t>
         </is>
       </c>
     </row>
@@ -2614,17 +2620,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Piura: primeras lluvias dejan al menos nueve puntos afectados mientras continúan obras de prevención</t>
+          <t>Fenómeno El Niño: Lluvias en Piura y Tumbes continuarán en las próximas horas</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Por segunda vez en menos de un mes, Piura registró lluvias que provocaron aniegos en calles, avenidas y viviendas, además de dificultades para el tránsito vehicular. Según el Servicio Nacional de Meteorología e Hidrología (Senamhi), estas precipitaciones corresponden a los primeros episodios de lluvias asociados al fenómeno El Niño. Entre la noche del lunes 19 y la mañana del martes 20 de octubre, las precipitaciones de baja intensidad afectaron al menos nueve puntos de la región, a pocos meses del periodo de mayor intensidad previsto por el organismo. En distintos puntos de la región se reportaron aniegos en las urbanizaciones Ignacio Merino y Santa Margarita, el asentamiento humano Las Dalias, así como en las zonas de Dos Grifos, Santa Rosa, Piura y el centro histórico. A estos lugares se suman la avenida Los Algarrobos, donde se registraron dificultades para el tránsito vehicular, y el Mercado Modelo de Chulucanas, donde el agua ingresó a los establecimientos comerciales. También se reportaron afectaciones en Castilla, Catacaos y otros sectores de la región. Las precipitaciones afectaron casas, avenidas, centros educativos y tiendas comerciales en distintos puntos de la región. En Ignacio Merino, el agua llegó a ingresar a viviendas, mientras que en el Mercado Modelo de Chulucanas se reportaron acumulaciones de hasta 30 centímetros que perjudicaron las actividades comerciales. Asimismo, en algunas vías se registraron dificultades para el tránsito vehicular debido a la acumulación de agua. La ingeniera Grinia Ávalos, jefa institucional del Senamhi, explicó en entrevista con El Comercio que las precipitaciones corresponden al segundo episodio de lluvias asociado al fenómeno El Niño, luego de que el 24 de septiembre se registrara un adelanto de la temporada en la costa norte. Según precisó, las lluvias acumuladas en la parte baja de Piura alcanzaron entre 6 y 7 milímetros. Aunque se trata de precipitaciones ligeras, su persistencia ha sido suficiente para provocar aniegos. “No son lluvias importantes, no son lluvias fuertes, digamos, pero la acumulación, la persistencia de estas lluvias sí empieza a generar aniegos en la parte baja”, explicó. Ávalos señaló que Piura presenta deficiencias en sus mecanismos de evacuación de aguas pluviales. Recordó que una situación similar ocurrió semanas atrás en Máncora, donde precipitaciones acumuladas de aproximadamente 16 milímetros provocaron aniegos. Obras de prevención todavía en ejecución Las primeras precipitaciones encuentran a Piura con intervenciones de drenaje y descolmatación que todavía no han concluido. Uno de los proyectos pendientes es el drenaje pluvial del centro histórico, a cargo del Gobierno Regional de Piura. Ralph Zapata, periodista y director de Norte Sostenible, señaló a El Comercio que esta obra, cuya inversión bordea los S/130 millones, acumula retrasos, ampliaciones de plazo y adicionales presupuestales. Según indicó, su culminación se habría postergado hasta 2027. El periodista también cuestionó la experiencia de la empresa contratista. La ausencia de una solución integral de drenaje constituye otro de los problemas señalados por Zapata. Explicó que varios de los sectores afectados corresponden a cuencas ciegas, zonas bajas donde el agua se acumula y que históricamente han registrado inundaciones. “Piura no tiene drenaje pluvial y por eso es que ves que Ignacio Merino, 26 de Octubre, Piura y Castilla están inundados”, señaló. A diferencia del drenaje urbano, los trabajos de descolmatación buscan retirar sedimentos y otros materiales acumulados en los cauces de los ríos para mejorar su capacidad de conducción del agua. Tan solo el fin de semana pasado, durante su visita a Piura el 16 de octubre, la presidenta Keiko Fujimori supervisó estas intervenciones junto con los ministros de Desarrollo Agrario y Riego, Marco Vinelli, y de Defensa, Rafael Belaúnde. De acuerdo con la información oficial, en Piura se programaron 21 intervenciones que comprenden 49.35 kilómetros de cauces de ríos y quebradas. En el tramo Los Ejidos–Puente Bolognesi, los trabajos registraban un avance físico del 100%, mientras que el volumen de descolmatación alcanzaba el 85,30%. Sin embargo, los avances reportados no eran uniformes en todos los sectores. Las intervenciones en El Milagro–La Encantada y Piedra Negra registraban avances de 27,59% y 20,73%, respectivamente, según la información difundida durante la supervisión presidencial. Zapata advirtió que, mientras los trabajos habían avanzado en el tramo urbano del río Piura, persistían retrasos en el Bajo Piura, donde todavía se observaban sectores con acumulación de sedimentos y vegetación. El Gobierno anunció el traslado de maquinaria hacia esta zona a partir del 18 de octubre, con el objetivo de continuar las intervenciones en el aliviadero Chutuque y el río Loco. También estableció como plazo de referencia el 30 de noviembre para culminar los trabajos de preparación del río. “De esta manera, quiero decirle a todos los piuranos que aquí, en el río Piura, se ha trabajado y se ha logrado la máxima capacidad del río. Más de esto no puede hacerse porque, como ustedes pueden ver, está el agua”, declaró Fujimori durante su visita. Respuesta ante los primeros aniegos Frente a las precipitaciones registradas, el Ministerio de Vivienda informó que cinco de sus ocho sistemas alternativos de recolección y evacuación de aguas pluviales se encontraban operando en Cinco Esquinas, El Chilcal, Ignacio Merino, La Molina II y Dos Grifos. Asimismo, reportó el despliegue de dos equipos trasvasadores para atender la acumulación de agua en los sectores afectados, en tanto trabajan con el apoyo del Ejercito y coordinan con el Gobierno Regional de Piura, asi como con los municipios afectados para estimar el desplazamiento de las motobombas a puntos más críticos. En riesgo crítico La situación de la infraestructura de servicios básicos constituye otro factor de riesgo. La Superintendencia Nacional de Servicios de Saneamiento (Sunass) identificó 101 infraestructuras de agua potable y saneamiento en riesgo crítico, de un total de 135 evaluadas en cinco regiones del norte del país. Según el organismo regulador, Piura concentra una población expuesta de aproximadamente 1,3 millones de personas ante posibles afectaciones a estos servicios por eventos climáticos extremos como el fenómeno El Niño. Ante este escenario, la Sunass recomendó a las empresas prestadoras de agua potable y saneamiento activar sus planes de gestión reactiva, garantizar la disponibilidad de grupos electrógenos y equipos de respaldo, así como adoptar medidas de protección de la infraestructura crítica frente a posibles lluvias e inundaciones Por su parte, el Gobierno anunció la preparación de albergues temporales con capacidad para atender a cerca de 30.000 personas que deban abandonar sus viviendas en caso de emergencia en las regiones vulnerables del país. El Comercio solicitó al Gobierno Regional de Piura una entrevista con un vocero para conocer el estado actual del proyecto de drenaje pluvial del centro histórico, así como las acciones implementadas ante los recientes aniegos y las medidas previstas frente a las próximas lluvias. Sin embargo, hasta el cierre de esta edición, la entidad no atendió el requerimiento. Lluvias más intensas hacia el verano La jefa institucional del Senamhi advirtió que las precipitaciones actuales forman parte de episodios que se presentan de manera intermitente y cuya frecuencia e intensidad aumentarán durante los próximos meses. El episodio de lluvias iniciado esta semana se extendería hasta el 23 o 24 de octubre. Posteriormente, se espera un periodo de mejores condiciones meteorológicas antes de que los eventos de lluvia se vuelvan más frecuentes hacia noviembre y diciembre. Ávalos explicó que las temperaturas del mar bordean actualmente los 26 grados, un valor inusual para esta época del año. Según indicó, el calentamiento observado supera las condiciones registradas durante los eventos extraordinarios de El Niño de las décadas de 1980 y 1990. Los pronósticos extendidos del Senamhi contemplan un escenario de precipitaciones superiores a lo normal durante el verano de 2027. En la costa norte podrían registrarse acumulados progresivos de 100, 150 y 200 milímetros, con un periodo de mayor intensidad entre febrero y marzo. La especialista señaló que en Piura y Tumbes podrían alcanzarse acumulados de hasta 250 milímetros, principalmente en esta última región, por su cercanía al golfo de Guayaquil. Tampoco descartó que se alcancen o superen los máximos históricos cercanos a los 270 milímetros registrados en Tumbes. Además de los aniegos que ya se presentan en zonas urbanas, Ávalos advirtió que las primeras precipitaciones pueden contribuir a la saturación del suelo y aumentar las afectaciones cuando lleguen las lluvias más intensas. “Sí van a generar aniegos, digamos, en la zona baja, va a saturar el suelo de manera que cuando ya tengamos las lluvias fuertes verdaderas, asociadas a El Niño, entre diciembre sobre todo, ya puede haber afectación en las cuencas”, explicó.</t>
+          <t>El Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) advirtió que las lluvias registradas en las primeras horas de este martes 20 de octubre en Piura y Tumbes continuarán durante las próximas horas y podrían prolongarse en los siguientes días. La especialista del Senamhi, Noelia Goicochea, dijo en TV Perú que se mantiene vigente un aviso meteorológico para la costa norte del país respecto a nuevas precipitaciones. La especialista indicó que entre hoy y mañana miércoles 21 se podrían registrar nuevas precipitaciones en Tumbes y Piura, por lo que se mantiene un periodo lluvioso en ambas regiones. “Para los próximos días también esperamos todavía que se puedan presentar lluvias de moderada a fuerte intensidad para lo que es el sector de la costa norte”, señaló. Goicochea informó que durante la noche del lunes 19 y la madrugada de hoy martes 20 se reportaron precipitaciones en distintos sectores de ambas regiones, con acumulados importantes en localidades próximas a la frontera con Ecuador. Uno de los mayores registros se presentó en Matapalo, Tumbes, donde se acumularon entre 56 y 57 milímetros de lluvia. En sectores del interior de Piura y zonas cercanas a la cordillera se reportaron valores de entre 16 y 18 milímetros hasta las 07:00 horas. Durante las primeras horas de la mañana, las lluvias se reactivaron en estas localidades y posteriormente continuaron de manera intermitente, con una disminución de su intensidad en algunos sectores. Según detalló Andina, la especialista del Senamhi afirmó que las precipitaciones también alcanzaron las provincias de Sullana, Morropón y Piura, así como sectores de Sechura. En ese contexto, el Senamhi informó, a través de sus canales oficiales, que se presentan lluvias en la costa de Tumbes y Piura, y que estas podrían continuar durante las próximas horas, de acuerdo con el aviso meteorológico vigente.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/peru/piura/piura-primeras-lluvias-dejan-al-menos-nueve-puntos-afectados-mientras-continuan-obras-de-prevencion-apuesplan-noticia/</t>
+          <t>https://elcomercio.pe/peru/piura/lluvias-en-piura-y-tumbes-continuaran-en-las-proximas-horas-advierte-el-senamhi-fenomeno-el-nino-apuesplan-ultimas-noticia/</t>
         </is>
       </c>
     </row>
